--- a/Config/TalentConfig.xlsx
+++ b/Config/TalentConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1477" uniqueCount="626">
   <si>
     <t>##var</t>
   </si>
@@ -55,12 +55,12 @@
     <t>TalentLevel</t>
   </si>
   <si>
+    <t>TalentEntry</t>
+  </si>
+  <si>
     <t>Desc</t>
   </si>
   <si>
-    <t>TalentEntry</t>
-  </si>
-  <si>
     <t>##</t>
   </si>
   <si>
@@ -88,12 +88,12 @@
     <t>天赋等级</t>
   </si>
   <si>
+    <t>天赋机制</t>
+  </si>
+  <si>
     <t>描述</t>
   </si>
   <si>
-    <t>天赋机制</t>
-  </si>
-  <si>
     <t>10101</t>
   </si>
   <si>
@@ -106,12 +106,12 @@
     <t>1</t>
   </si>
   <si>
+    <t>101</t>
+  </si>
+  <si>
     <t>数字牌2提供的攻击力+1</t>
   </si>
   <si>
-    <t>101</t>
-  </si>
-  <si>
     <t>10102</t>
   </si>
   <si>
@@ -199,12 +199,12 @@
     <t>3点精通</t>
   </si>
   <si>
+    <t>102</t>
+  </si>
+  <si>
     <t>数字牌3提供的攻击力+1</t>
   </si>
   <si>
-    <t>102</t>
-  </si>
-  <si>
     <t>10202</t>
   </si>
   <si>
@@ -265,12 +265,12 @@
     <t>4点精通</t>
   </si>
   <si>
+    <t>103</t>
+  </si>
+  <si>
     <t>数字牌4提供的攻击力+1</t>
   </si>
   <si>
-    <t>103</t>
-  </si>
-  <si>
     <t>10302</t>
   </si>
   <si>
@@ -331,12 +331,12 @@
     <t>5点精通</t>
   </si>
   <si>
+    <t>104</t>
+  </si>
+  <si>
     <t>数字牌5提供的攻击力+1</t>
   </si>
   <si>
-    <t>104</t>
-  </si>
-  <si>
     <t>10402</t>
   </si>
   <si>
@@ -397,12 +397,12 @@
     <t>6点精通</t>
   </si>
   <si>
+    <t>105</t>
+  </si>
+  <si>
     <t>数字牌6提供的攻击力+1</t>
   </si>
   <si>
-    <t>105</t>
-  </si>
-  <si>
     <t>10502</t>
   </si>
   <si>
@@ -896,6 +896,1020 @@
   </si>
   <si>
     <t>英雄的基础攻击力+10</t>
+  </si>
+  <si>
+    <t>20101</t>
+  </si>
+  <si>
+    <t>人头精通</t>
+  </si>
+  <si>
+    <t>Rare</t>
+  </si>
+  <si>
+    <t>人头牌提供的攻击力+1</t>
+  </si>
+  <si>
+    <t>20102</t>
+  </si>
+  <si>
+    <t>人头牌提供的攻击力+2</t>
+  </si>
+  <si>
+    <t>20103</t>
+  </si>
+  <si>
+    <t>人头牌提供的攻击力+3</t>
+  </si>
+  <si>
+    <t>20104</t>
+  </si>
+  <si>
+    <t>人头牌提供的攻击力+4</t>
+  </si>
+  <si>
+    <t>20105</t>
+  </si>
+  <si>
+    <t>人头牌提供的攻击力+5</t>
+  </si>
+  <si>
+    <t>20106</t>
+  </si>
+  <si>
+    <t>人头牌提供的攻击力+6</t>
+  </si>
+  <si>
+    <t>20107</t>
+  </si>
+  <si>
+    <t>人头牌提供的攻击力+7</t>
+  </si>
+  <si>
+    <t>20108</t>
+  </si>
+  <si>
+    <t>人头牌提供的攻击力+8</t>
+  </si>
+  <si>
+    <t>20109</t>
+  </si>
+  <si>
+    <t>人头牌提供的攻击力+9</t>
+  </si>
+  <si>
+    <t>20110</t>
+  </si>
+  <si>
+    <t>人头牌提供的攻击力+10</t>
+  </si>
+  <si>
+    <t>20201</t>
+  </si>
+  <si>
+    <t>强力打击</t>
+  </si>
+  <si>
+    <t>英雄暴击率+0.5%</t>
+  </si>
+  <si>
+    <t>20202</t>
+  </si>
+  <si>
+    <t>英雄暴击率+1%</t>
+  </si>
+  <si>
+    <t>20203</t>
+  </si>
+  <si>
+    <t>英雄暴击率+1.5%</t>
+  </si>
+  <si>
+    <t>20204</t>
+  </si>
+  <si>
+    <t>英雄暴击率+2%</t>
+  </si>
+  <si>
+    <t>20205</t>
+  </si>
+  <si>
+    <t>英雄暴击率+2.5%</t>
+  </si>
+  <si>
+    <t>20206</t>
+  </si>
+  <si>
+    <t>英雄暴击率+3%</t>
+  </si>
+  <si>
+    <t>20207</t>
+  </si>
+  <si>
+    <t>英雄暴击率+3.5%</t>
+  </si>
+  <si>
+    <t>20208</t>
+  </si>
+  <si>
+    <t>英雄暴击率+4%</t>
+  </si>
+  <si>
+    <t>20209</t>
+  </si>
+  <si>
+    <t>英雄暴击率+4.5%</t>
+  </si>
+  <si>
+    <t>20210</t>
+  </si>
+  <si>
+    <t>英雄暴击率+5%</t>
+  </si>
+  <si>
+    <t>20301</t>
+  </si>
+  <si>
+    <t>巨人杀手</t>
+  </si>
+  <si>
+    <t>对BOSS的伤害+0.5%</t>
+  </si>
+  <si>
+    <t>20302</t>
+  </si>
+  <si>
+    <t>对BOSS的伤害+1%</t>
+  </si>
+  <si>
+    <t>20303</t>
+  </si>
+  <si>
+    <t>对BOSS的伤害+1.5%</t>
+  </si>
+  <si>
+    <t>20304</t>
+  </si>
+  <si>
+    <t>对BOSS的伤害+2%</t>
+  </si>
+  <si>
+    <t>20305</t>
+  </si>
+  <si>
+    <t>对BOSS的伤害+2.5%</t>
+  </si>
+  <si>
+    <t>20306</t>
+  </si>
+  <si>
+    <t>对BOSS的伤害+3%</t>
+  </si>
+  <si>
+    <t>20307</t>
+  </si>
+  <si>
+    <t>对BOSS的伤害+3.5%</t>
+  </si>
+  <si>
+    <t>20308</t>
+  </si>
+  <si>
+    <t>对BOSS的伤害+4%</t>
+  </si>
+  <si>
+    <t>20309</t>
+  </si>
+  <si>
+    <t>对BOSS的伤害+4.5%</t>
+  </si>
+  <si>
+    <t>20310</t>
+  </si>
+  <si>
+    <t>对BOSS的伤害+5%</t>
+  </si>
+  <si>
+    <t>20401</t>
+  </si>
+  <si>
+    <t>好兆头</t>
+  </si>
+  <si>
+    <t>每关的首次亮牌,倍率+0.2</t>
+  </si>
+  <si>
+    <t>20402</t>
+  </si>
+  <si>
+    <t>每关的首次亮牌,倍率+0.4</t>
+  </si>
+  <si>
+    <t>20403</t>
+  </si>
+  <si>
+    <t>每关的首次亮牌,倍率+0.6</t>
+  </si>
+  <si>
+    <t>20404</t>
+  </si>
+  <si>
+    <t>每关的首次亮牌,倍率+0.8</t>
+  </si>
+  <si>
+    <t>20405</t>
+  </si>
+  <si>
+    <t>每关的首次亮牌,倍率+1</t>
+  </si>
+  <si>
+    <t>20406</t>
+  </si>
+  <si>
+    <t>每关的首次亮牌,倍率+1.2</t>
+  </si>
+  <si>
+    <t>20407</t>
+  </si>
+  <si>
+    <t>每关的首次亮牌,倍率+1.4</t>
+  </si>
+  <si>
+    <t>20408</t>
+  </si>
+  <si>
+    <t>每关的首次亮牌,倍率+1.6</t>
+  </si>
+  <si>
+    <t>20409</t>
+  </si>
+  <si>
+    <t>每关的首次亮牌,倍率+1.8</t>
+  </si>
+  <si>
+    <t>20410</t>
+  </si>
+  <si>
+    <t>每关的首次亮牌,倍率+2</t>
+  </si>
+  <si>
+    <t>20501</t>
+  </si>
+  <si>
+    <t>侩子手</t>
+  </si>
+  <si>
+    <t>攻击血量低于10%的非BOSS敌人时,有0.5%概率斩杀</t>
+  </si>
+  <si>
+    <t>20502</t>
+  </si>
+  <si>
+    <t>攻击血量低于10%的非BOSS敌人时,有1%概率斩杀</t>
+  </si>
+  <si>
+    <t>20503</t>
+  </si>
+  <si>
+    <t>攻击血量低于10%的非BOSS敌人时,有1.5%概率斩杀</t>
+  </si>
+  <si>
+    <t>20504</t>
+  </si>
+  <si>
+    <t>攻击血量低于10%的非BOSS敌人时,有2%概率斩杀</t>
+  </si>
+  <si>
+    <t>20505</t>
+  </si>
+  <si>
+    <t>攻击血量低于10%的非BOSS敌人时,有2.5%概率斩杀</t>
+  </si>
+  <si>
+    <t>20506</t>
+  </si>
+  <si>
+    <t>攻击血量低于10%的非BOSS敌人时,有3%概率斩杀</t>
+  </si>
+  <si>
+    <t>20507</t>
+  </si>
+  <si>
+    <t>攻击血量低于10%的非BOSS敌人时,有3.5%概率斩杀</t>
+  </si>
+  <si>
+    <t>20508</t>
+  </si>
+  <si>
+    <t>攻击血量低于10%的非BOSS敌人时,有4%概率斩杀</t>
+  </si>
+  <si>
+    <t>20509</t>
+  </si>
+  <si>
+    <t>攻击血量低于10%的非BOSS敌人时,有4.5%概率斩杀</t>
+  </si>
+  <si>
+    <t>20510</t>
+  </si>
+  <si>
+    <t>攻击血量低于10%的非BOSS敌人时,有5%概率斩杀</t>
+  </si>
+  <si>
+    <t>20601</t>
+  </si>
+  <si>
+    <t>逢凶化吉</t>
+  </si>
+  <si>
+    <t>当血量低于20%以下时,击杀敌人会回复0.5%的血量</t>
+  </si>
+  <si>
+    <t>20602</t>
+  </si>
+  <si>
+    <t>当血量低于20%以下时,击杀敌人会回复1%的血量</t>
+  </si>
+  <si>
+    <t>20603</t>
+  </si>
+  <si>
+    <t>当血量低于20%以下时,击杀敌人会回复1.5%的血量</t>
+  </si>
+  <si>
+    <t>20604</t>
+  </si>
+  <si>
+    <t>当血量低于20%以下时,击杀敌人会回复2%的血量</t>
+  </si>
+  <si>
+    <t>20605</t>
+  </si>
+  <si>
+    <t>当血量低于20%以下时,击杀敌人会回复2.5%的血量</t>
+  </si>
+  <si>
+    <t>20606</t>
+  </si>
+  <si>
+    <t>当血量低于20%以下时,击杀敌人会回复3%的血量</t>
+  </si>
+  <si>
+    <t>20607</t>
+  </si>
+  <si>
+    <t>当血量低于20%以下时,击杀敌人会回复3.5%的血量</t>
+  </si>
+  <si>
+    <t>20608</t>
+  </si>
+  <si>
+    <t>当血量低于20%以下时,击杀敌人会回复4%的血量</t>
+  </si>
+  <si>
+    <t>20609</t>
+  </si>
+  <si>
+    <t>当血量低于20%以下时,击杀敌人会回复4.5%的血量</t>
+  </si>
+  <si>
+    <t>20610</t>
+  </si>
+  <si>
+    <t>当血量低于20%以下时,击杀敌人会回复5%的血量</t>
+  </si>
+  <si>
+    <t>20701</t>
+  </si>
+  <si>
+    <t>人多势众</t>
+  </si>
+  <si>
+    <t>当敌人数量大于1时,造成的伤害+0.5%</t>
+  </si>
+  <si>
+    <t>20702</t>
+  </si>
+  <si>
+    <t>当敌人数量大于1时,造成的伤害+1%</t>
+  </si>
+  <si>
+    <t>20703</t>
+  </si>
+  <si>
+    <t>当敌人数量大于1时,造成的伤害+1.5%</t>
+  </si>
+  <si>
+    <t>20704</t>
+  </si>
+  <si>
+    <t>当敌人数量大于1时,造成的伤害+2%</t>
+  </si>
+  <si>
+    <t>20705</t>
+  </si>
+  <si>
+    <t>当敌人数量大于1时,造成的伤害+2.5%</t>
+  </si>
+  <si>
+    <t>20706</t>
+  </si>
+  <si>
+    <t>当敌人数量大于1时,造成的伤害+3%</t>
+  </si>
+  <si>
+    <t>20707</t>
+  </si>
+  <si>
+    <t>当敌人数量大于1时,造成的伤害+3.5%</t>
+  </si>
+  <si>
+    <t>20708</t>
+  </si>
+  <si>
+    <t>当敌人数量大于1时,造成的伤害+4%</t>
+  </si>
+  <si>
+    <t>20709</t>
+  </si>
+  <si>
+    <t>当敌人数量大于1时,造成的伤害+4.5%</t>
+  </si>
+  <si>
+    <t>20710</t>
+  </si>
+  <si>
+    <t>当敌人数量大于1时,造成的伤害+5%</t>
+  </si>
+  <si>
+    <t>20801</t>
+  </si>
+  <si>
+    <t>搓牌高手</t>
+  </si>
+  <si>
+    <t>亮牌前,只要使用过搓牌,结算时就提供1点攻击力</t>
+  </si>
+  <si>
+    <t>20802</t>
+  </si>
+  <si>
+    <t>亮牌前,只要使用过搓牌,结算时就提供2点攻击力</t>
+  </si>
+  <si>
+    <t>20803</t>
+  </si>
+  <si>
+    <t>亮牌前,只要使用过搓牌,结算时就提供3点攻击力</t>
+  </si>
+  <si>
+    <t>20804</t>
+  </si>
+  <si>
+    <t>亮牌前,只要使用过搓牌,结算时就提供4点攻击力</t>
+  </si>
+  <si>
+    <t>20805</t>
+  </si>
+  <si>
+    <t>亮牌前,只要使用过搓牌,结算时就提供5点攻击力</t>
+  </si>
+  <si>
+    <t>20806</t>
+  </si>
+  <si>
+    <t>亮牌前,只要使用过搓牌,结算时就提供6点攻击力</t>
+  </si>
+  <si>
+    <t>20807</t>
+  </si>
+  <si>
+    <t>亮牌前,只要使用过搓牌,结算时就提供7点攻击力</t>
+  </si>
+  <si>
+    <t>20808</t>
+  </si>
+  <si>
+    <t>亮牌前,只要使用过搓牌,结算时就提供8点攻击力</t>
+  </si>
+  <si>
+    <t>20809</t>
+  </si>
+  <si>
+    <t>亮牌前,只要使用过搓牌,结算时就提供9点攻击力</t>
+  </si>
+  <si>
+    <t>20810</t>
+  </si>
+  <si>
+    <t>亮牌前,只要使用过搓牌,结算时就提供10点攻击力</t>
+  </si>
+  <si>
+    <t>30101</t>
+  </si>
+  <si>
+    <t>回复</t>
+  </si>
+  <si>
+    <t>Epic</t>
+  </si>
+  <si>
+    <t>每回结束后,回复0.5%的血量</t>
+  </si>
+  <si>
+    <t>30102</t>
+  </si>
+  <si>
+    <t>每回结束后,回复1%的血量</t>
+  </si>
+  <si>
+    <t>30103</t>
+  </si>
+  <si>
+    <t>每回结束后,回复1.5%的血量</t>
+  </si>
+  <si>
+    <t>30104</t>
+  </si>
+  <si>
+    <t>每回结束后,回复2%的血量</t>
+  </si>
+  <si>
+    <t>30105</t>
+  </si>
+  <si>
+    <t>每回结束后,回复2.5%的血量</t>
+  </si>
+  <si>
+    <t>30106</t>
+  </si>
+  <si>
+    <t>每回结束后,回复3%的血量</t>
+  </si>
+  <si>
+    <t>30107</t>
+  </si>
+  <si>
+    <t>每回结束后,回复3.5%的血量</t>
+  </si>
+  <si>
+    <t>30108</t>
+  </si>
+  <si>
+    <t>每回结束后,回复4%的血量</t>
+  </si>
+  <si>
+    <t>30109</t>
+  </si>
+  <si>
+    <t>每回结束后,回复4.5%的血量</t>
+  </si>
+  <si>
+    <t>30110</t>
+  </si>
+  <si>
+    <t>每回结束后,回复5%的血量</t>
+  </si>
+  <si>
+    <t>30201</t>
+  </si>
+  <si>
+    <t>资本家</t>
+  </si>
+  <si>
+    <t>每回合结算时,有1%概率获得1资金</t>
+  </si>
+  <si>
+    <t>30202</t>
+  </si>
+  <si>
+    <t>每回合结算时,有2%概率获得1资金</t>
+  </si>
+  <si>
+    <t>30203</t>
+  </si>
+  <si>
+    <t>每回合结算时,有3%概率获得1资金</t>
+  </si>
+  <si>
+    <t>30204</t>
+  </si>
+  <si>
+    <t>每回合结算时,有4%概率获得1资金</t>
+  </si>
+  <si>
+    <t>30205</t>
+  </si>
+  <si>
+    <t>每回合结算时,有5%概率获得1资金</t>
+  </si>
+  <si>
+    <t>30206</t>
+  </si>
+  <si>
+    <t>每回合结算时,有6%概率获得1资金</t>
+  </si>
+  <si>
+    <t>30207</t>
+  </si>
+  <si>
+    <t>每回合结算时,有7%概率获得1资金</t>
+  </si>
+  <si>
+    <t>30208</t>
+  </si>
+  <si>
+    <t>每回合结算时,有8%概率获得1资金</t>
+  </si>
+  <si>
+    <t>30209</t>
+  </si>
+  <si>
+    <t>每回合结算时,有9%概率获得1资金</t>
+  </si>
+  <si>
+    <t>30210</t>
+  </si>
+  <si>
+    <t>每回合结算时,有10%概率获得1资金</t>
+  </si>
+  <si>
+    <t>30301</t>
+  </si>
+  <si>
+    <t>A点精通</t>
+  </si>
+  <si>
+    <t>A牌提供的攻击力+2</t>
+  </si>
+  <si>
+    <t>30302</t>
+  </si>
+  <si>
+    <t>A牌提供的攻击力+4</t>
+  </si>
+  <si>
+    <t>30303</t>
+  </si>
+  <si>
+    <t>A牌提供的攻击力+6</t>
+  </si>
+  <si>
+    <t>30304</t>
+  </si>
+  <si>
+    <t>A牌提供的攻击力+8</t>
+  </si>
+  <si>
+    <t>30305</t>
+  </si>
+  <si>
+    <t>A牌提供的攻击力+10</t>
+  </si>
+  <si>
+    <t>30306</t>
+  </si>
+  <si>
+    <t>A牌提供的攻击力+12</t>
+  </si>
+  <si>
+    <t>30307</t>
+  </si>
+  <si>
+    <t>A牌提供的攻击力+14</t>
+  </si>
+  <si>
+    <t>30308</t>
+  </si>
+  <si>
+    <t>A牌提供的攻击力+16</t>
+  </si>
+  <si>
+    <t>30309</t>
+  </si>
+  <si>
+    <t>A牌提供的攻击力+18</t>
+  </si>
+  <si>
+    <t>30310</t>
+  </si>
+  <si>
+    <t>A牌提供的攻击力+20</t>
+  </si>
+  <si>
+    <t>30401</t>
+  </si>
+  <si>
+    <t>孤立无援</t>
+  </si>
+  <si>
+    <t>只剩下1名敌人时,对其造成的伤害+0.5%</t>
+  </si>
+  <si>
+    <t>30402</t>
+  </si>
+  <si>
+    <t>只剩下1名敌人时,对其造成的伤害+1%</t>
+  </si>
+  <si>
+    <t>30403</t>
+  </si>
+  <si>
+    <t>只剩下1名敌人时,对其造成的伤害+1.5%</t>
+  </si>
+  <si>
+    <t>30404</t>
+  </si>
+  <si>
+    <t>只剩下1名敌人时,对其造成的伤害+2%</t>
+  </si>
+  <si>
+    <t>30405</t>
+  </si>
+  <si>
+    <t>只剩下1名敌人时,对其造成的伤害+2.5%</t>
+  </si>
+  <si>
+    <t>30406</t>
+  </si>
+  <si>
+    <t>只剩下1名敌人时,对其造成的伤害+3%</t>
+  </si>
+  <si>
+    <t>30407</t>
+  </si>
+  <si>
+    <t>只剩下1名敌人时,对其造成的伤害+3.5%</t>
+  </si>
+  <si>
+    <t>30408</t>
+  </si>
+  <si>
+    <t>只剩下1名敌人时,对其造成的伤害+4%</t>
+  </si>
+  <si>
+    <t>30409</t>
+  </si>
+  <si>
+    <t>只剩下1名敌人时,对其造成的伤害+4.5%</t>
+  </si>
+  <si>
+    <t>30410</t>
+  </si>
+  <si>
+    <t>只剩下1名敌人时,对其造成的伤害+5%</t>
+  </si>
+  <si>
+    <t>30501</t>
+  </si>
+  <si>
+    <t>触底反弹</t>
+  </si>
+  <si>
+    <t>当血量低于20%以下时,造成的伤害+0.5%</t>
+  </si>
+  <si>
+    <t>30502</t>
+  </si>
+  <si>
+    <t>当血量低于20%以下时,造成的伤害+1%</t>
+  </si>
+  <si>
+    <t>30503</t>
+  </si>
+  <si>
+    <t>当血量低于20%以下时,造成的伤害+1.5%</t>
+  </si>
+  <si>
+    <t>30504</t>
+  </si>
+  <si>
+    <t>当血量低于20%以下时,造成的伤害+2%</t>
+  </si>
+  <si>
+    <t>30505</t>
+  </si>
+  <si>
+    <t>当血量低于20%以下时,造成的伤害+2.5%</t>
+  </si>
+  <si>
+    <t>30506</t>
+  </si>
+  <si>
+    <t>当血量低于20%以下时,造成的伤害+3%</t>
+  </si>
+  <si>
+    <t>30507</t>
+  </si>
+  <si>
+    <t>当血量低于20%以下时,造成的伤害+3.5%</t>
+  </si>
+  <si>
+    <t>30508</t>
+  </si>
+  <si>
+    <t>当血量低于20%以下时,造成的伤害+4%</t>
+  </si>
+  <si>
+    <t>30509</t>
+  </si>
+  <si>
+    <t>当血量低于20%以下时,造成的伤害+4.5%</t>
+  </si>
+  <si>
+    <t>30510</t>
+  </si>
+  <si>
+    <t>当血量低于20%以下时,造成的伤害+5%</t>
+  </si>
+  <si>
+    <t>30601</t>
+  </si>
+  <si>
+    <t>点金手</t>
+  </si>
+  <si>
+    <t>击杀敌人时,有1%概率获得1资金</t>
+  </si>
+  <si>
+    <t>30602</t>
+  </si>
+  <si>
+    <t>击杀敌人时,有2%概率获得1资金</t>
+  </si>
+  <si>
+    <t>30603</t>
+  </si>
+  <si>
+    <t>击杀敌人时,有3%概率获得1资金</t>
+  </si>
+  <si>
+    <t>30604</t>
+  </si>
+  <si>
+    <t>击杀敌人时,有4%概率获得1资金</t>
+  </si>
+  <si>
+    <t>30605</t>
+  </si>
+  <si>
+    <t>击杀敌人时,有5%概率获得1资金</t>
+  </si>
+  <si>
+    <t>30606</t>
+  </si>
+  <si>
+    <t>击杀敌人时,有6%概率获得1资金</t>
+  </si>
+  <si>
+    <t>30607</t>
+  </si>
+  <si>
+    <t>击杀敌人时,有7%概率获得1资金</t>
+  </si>
+  <si>
+    <t>30608</t>
+  </si>
+  <si>
+    <t>击杀敌人时,有8%概率获得1资金</t>
+  </si>
+  <si>
+    <t>30609</t>
+  </si>
+  <si>
+    <t>击杀敌人时,有9%概率获得1资金</t>
+  </si>
+  <si>
+    <t>30610</t>
+  </si>
+  <si>
+    <t>击杀敌人时,有10%概率获得1资金</t>
+  </si>
+  <si>
+    <t>30701</t>
+  </si>
+  <si>
+    <t>富裕</t>
+  </si>
+  <si>
+    <t>初始拥有1资金</t>
+  </si>
+  <si>
+    <t>30702</t>
+  </si>
+  <si>
+    <t>初始拥有2资金</t>
+  </si>
+  <si>
+    <t>30703</t>
+  </si>
+  <si>
+    <t>初始拥有3资金</t>
+  </si>
+  <si>
+    <t>30704</t>
+  </si>
+  <si>
+    <t>初始拥有4资金</t>
+  </si>
+  <si>
+    <t>30705</t>
+  </si>
+  <si>
+    <t>初始拥有5资金</t>
+  </si>
+  <si>
+    <t>30706</t>
+  </si>
+  <si>
+    <t>初始拥有6资金</t>
+  </si>
+  <si>
+    <t>30707</t>
+  </si>
+  <si>
+    <t>初始拥有7资金</t>
+  </si>
+  <si>
+    <t>30708</t>
+  </si>
+  <si>
+    <t>初始拥有8资金</t>
+  </si>
+  <si>
+    <t>30709</t>
+  </si>
+  <si>
+    <t>初始拥有9资金</t>
+  </si>
+  <si>
+    <t>30710</t>
+  </si>
+  <si>
+    <t>初始拥有10资金</t>
+  </si>
+  <si>
+    <t>30801</t>
+  </si>
+  <si>
+    <t>追击</t>
+  </si>
+  <si>
+    <t>攻击敌人时,有1%概率额外造成1次原伤害10%的攻击</t>
+  </si>
+  <si>
+    <t>30802</t>
+  </si>
+  <si>
+    <t>攻击敌人时,有2%概率额外造成1次原伤害10%的攻击</t>
+  </si>
+  <si>
+    <t>30803</t>
+  </si>
+  <si>
+    <t>攻击敌人时,有3%概率额外造成1次原伤害10%的攻击</t>
+  </si>
+  <si>
+    <t>30804</t>
+  </si>
+  <si>
+    <t>攻击敌人时,有4%概率额外造成1次原伤害10%的攻击</t>
+  </si>
+  <si>
+    <t>30805</t>
+  </si>
+  <si>
+    <t>攻击敌人时,有5%概率额外造成1次原伤害10%的攻击</t>
+  </si>
+  <si>
+    <t>30806</t>
+  </si>
+  <si>
+    <t>攻击敌人时,有6%概率额外造成1次原伤害10%的攻击</t>
+  </si>
+  <si>
+    <t>30807</t>
+  </si>
+  <si>
+    <t>攻击敌人时,有7%概率额外造成1次原伤害10%的攻击</t>
+  </si>
+  <si>
+    <t>30808</t>
+  </si>
+  <si>
+    <t>攻击敌人时,有8%概率额外造成1次原伤害10%的攻击</t>
+  </si>
+  <si>
+    <t>30809</t>
+  </si>
+  <si>
+    <t>攻击敌人时,有9%概率额外造成1次原伤害10%的攻击</t>
+  </si>
+  <si>
+    <t>30810</t>
+  </si>
+  <si>
+    <t>攻击敌人时,有10%概率额外造成1次原伤害10%的攻击</t>
   </si>
 </sst>
 </file>
@@ -1869,19 +2883,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I135"/>
+  <dimension ref="A1:I311"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.54166666666667" style="1" customWidth="1"/>
     <col min="2" max="2" width="5.85833333333333" style="1" customWidth="1"/>
     <col min="3" max="3" width="8.36666666666667" style="2" customWidth="1"/>
-    <col min="4" max="4" width="7.06666666666667" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.03333333333333" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.6166666666667" style="1" customWidth="1"/>
     <col min="6" max="6" width="6.3" style="1" customWidth="1"/>
     <col min="7" max="7" width="11.5083333333333" style="1" customWidth="1"/>
-    <col min="8" max="8" width="21.1916666666667" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12.4916666666667" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1"/>
+    <col min="8" max="8" width="12.4916666666667" style="1" customWidth="1"/>
+    <col min="9" max="9" width="22.0666666666667" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1936,10 +2950,10 @@
         <v>10</v>
       </c>
       <c r="H2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2015,10 +3029,10 @@
         <v>27</v>
       </c>
       <c r="H6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="7" customFormat="1" spans="1:9">
@@ -2040,10 +3054,10 @@
         <v>30</v>
       </c>
       <c r="H7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="8" customFormat="1" spans="1:9">
@@ -2065,10 +3079,10 @@
         <v>33</v>
       </c>
       <c r="H8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="9" customFormat="1" spans="1:9">
@@ -2090,10 +3104,10 @@
         <v>36</v>
       </c>
       <c r="H9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="10" customFormat="1" spans="1:9">
@@ -2115,10 +3129,10 @@
         <v>39</v>
       </c>
       <c r="H10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="11" customFormat="1" spans="1:9">
@@ -2140,10 +3154,10 @@
         <v>42</v>
       </c>
       <c r="H11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="12" customFormat="1" spans="1:9">
@@ -2165,10 +3179,10 @@
         <v>45</v>
       </c>
       <c r="H12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="13" customFormat="1" spans="1:9">
@@ -2190,10 +3204,10 @@
         <v>48</v>
       </c>
       <c r="H13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="14" customFormat="1" spans="1:9">
@@ -2215,10 +3229,10 @@
         <v>51</v>
       </c>
       <c r="H14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:9">
@@ -2276,10 +3290,10 @@
         <v>27</v>
       </c>
       <c r="H17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I17" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="18" customFormat="1" spans="1:9">
@@ -2301,10 +3315,10 @@
         <v>30</v>
       </c>
       <c r="H18" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I18" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="19" customFormat="1" spans="1:9">
@@ -2326,10 +3340,10 @@
         <v>33</v>
       </c>
       <c r="H19" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I19" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="20" customFormat="1" spans="1:9">
@@ -2351,10 +3365,10 @@
         <v>36</v>
       </c>
       <c r="H20" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I20" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="21" customFormat="1" spans="1:9">
@@ -2376,10 +3390,10 @@
         <v>39</v>
       </c>
       <c r="H21" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I21" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:9">
@@ -2401,10 +3415,10 @@
         <v>42</v>
       </c>
       <c r="H22" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I22" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="23" customFormat="1" spans="1:9">
@@ -2426,10 +3440,10 @@
         <v>45</v>
       </c>
       <c r="H23" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I23" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="24" customFormat="1" spans="1:9">
@@ -2451,10 +3465,10 @@
         <v>48</v>
       </c>
       <c r="H24" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I24" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="25" customFormat="1" spans="1:9">
@@ -2476,10 +3490,10 @@
         <v>51</v>
       </c>
       <c r="H25" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I25" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="27" customFormat="1" spans="1:9">
@@ -2526,10 +3540,10 @@
         <v>27</v>
       </c>
       <c r="H28" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I28" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="29" customFormat="1" spans="1:9">
@@ -2551,10 +3565,10 @@
         <v>30</v>
       </c>
       <c r="H29" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I29" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="30" customFormat="1" spans="1:9">
@@ -2576,10 +3590,10 @@
         <v>33</v>
       </c>
       <c r="H30" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I30" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="31" customFormat="1" spans="1:9">
@@ -2601,10 +3615,10 @@
         <v>36</v>
       </c>
       <c r="H31" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I31" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="32" customFormat="1" spans="1:9">
@@ -2626,10 +3640,10 @@
         <v>39</v>
       </c>
       <c r="H32" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I32" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="1:9">
@@ -2651,10 +3665,10 @@
         <v>42</v>
       </c>
       <c r="H33" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I33" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="34" customFormat="1" spans="1:9">
@@ -2676,10 +3690,10 @@
         <v>45</v>
       </c>
       <c r="H34" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I34" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="35" customFormat="1" spans="1:9">
@@ -2701,10 +3715,10 @@
         <v>48</v>
       </c>
       <c r="H35" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I35" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="36" customFormat="1" spans="1:9">
@@ -2726,10 +3740,10 @@
         <v>51</v>
       </c>
       <c r="H36" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I36" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="38" customFormat="1" spans="1:9">
@@ -2776,10 +3790,10 @@
         <v>27</v>
       </c>
       <c r="H39" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I39" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="I39" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="40" customFormat="1" spans="1:9">
@@ -2801,10 +3815,10 @@
         <v>30</v>
       </c>
       <c r="H40" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I40" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="41" customFormat="1" spans="1:9">
@@ -2826,10 +3840,10 @@
         <v>33</v>
       </c>
       <c r="H41" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I41" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="42" customFormat="1" spans="1:9">
@@ -2851,10 +3865,10 @@
         <v>36</v>
       </c>
       <c r="H42" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I42" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="43" customFormat="1" spans="1:9">
@@ -2876,10 +3890,10 @@
         <v>39</v>
       </c>
       <c r="H43" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I43" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="44" customFormat="1" spans="1:9">
@@ -2901,10 +3915,10 @@
         <v>42</v>
       </c>
       <c r="H44" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I44" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="45" customFormat="1" spans="1:9">
@@ -2926,10 +3940,10 @@
         <v>45</v>
       </c>
       <c r="H45" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I45" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="46" customFormat="1" spans="1:9">
@@ -2951,10 +3965,10 @@
         <v>48</v>
       </c>
       <c r="H46" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I46" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="47" customFormat="1" spans="1:9">
@@ -2976,10 +3990,10 @@
         <v>51</v>
       </c>
       <c r="H47" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I47" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="I47" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="49" customFormat="1" spans="1:9">
@@ -3026,10 +4040,10 @@
         <v>27</v>
       </c>
       <c r="H50" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I50" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="I50" s="1" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:9">
@@ -3051,10 +4065,10 @@
         <v>30</v>
       </c>
       <c r="H51" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I51" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="I51" s="1" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="52" customFormat="1" spans="1:9">
@@ -3076,10 +4090,10 @@
         <v>33</v>
       </c>
       <c r="H52" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I52" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="I52" s="1" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="53" customFormat="1" spans="1:9">
@@ -3101,10 +4115,10 @@
         <v>36</v>
       </c>
       <c r="H53" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I53" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="I53" s="1" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="54" customFormat="1" spans="1:9">
@@ -3126,10 +4140,10 @@
         <v>39</v>
       </c>
       <c r="H54" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I54" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="I54" s="1" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="55" customFormat="1" spans="1:9">
@@ -3151,10 +4165,10 @@
         <v>42</v>
       </c>
       <c r="H55" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I55" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="I55" s="1" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="56" customFormat="1" spans="1:9">
@@ -3176,10 +4190,10 @@
         <v>45</v>
       </c>
       <c r="H56" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I56" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="I56" s="1" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="57" customFormat="1" spans="1:9">
@@ -3201,10 +4215,10 @@
         <v>48</v>
       </c>
       <c r="H57" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I57" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="I57" s="1" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="58" customFormat="1" spans="1:9">
@@ -3226,10 +4240,10 @@
         <v>51</v>
       </c>
       <c r="H58" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I58" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="I58" s="1" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="60" customFormat="1" spans="1:9">
@@ -3250,11 +4264,11 @@
       <c r="G60" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H60" s="1" t="s">
+      <c r="H60" s="2">
+        <v>106</v>
+      </c>
+      <c r="I60" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="I60" s="2">
-        <v>106</v>
       </c>
     </row>
     <row r="61" customFormat="1" spans="1:9">
@@ -3275,11 +4289,11 @@
       <c r="G61" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H61" s="1" t="s">
+      <c r="H61" s="2">
+        <v>106</v>
+      </c>
+      <c r="I61" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="I61" s="2">
-        <v>106</v>
       </c>
     </row>
     <row r="62" customFormat="1" spans="1:9">
@@ -3300,11 +4314,11 @@
       <c r="G62" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H62" s="1" t="s">
+      <c r="H62" s="2">
+        <v>106</v>
+      </c>
+      <c r="I62" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="I62" s="2">
-        <v>106</v>
       </c>
     </row>
     <row r="63" customFormat="1" spans="1:9">
@@ -3325,11 +4339,11 @@
       <c r="G63" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H63" s="1" t="s">
+      <c r="H63" s="2">
+        <v>106</v>
+      </c>
+      <c r="I63" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="I63" s="2">
-        <v>106</v>
       </c>
     </row>
     <row r="64" customFormat="1" spans="1:9">
@@ -3350,11 +4364,11 @@
       <c r="G64" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H64" s="1" t="s">
+      <c r="H64" s="2">
+        <v>106</v>
+      </c>
+      <c r="I64" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="I64" s="2">
-        <v>106</v>
       </c>
     </row>
     <row r="65" customFormat="1" spans="1:9">
@@ -3375,11 +4389,11 @@
       <c r="G65" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H65" s="1" t="s">
+      <c r="H65" s="2">
+        <v>106</v>
+      </c>
+      <c r="I65" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="I65" s="2">
-        <v>106</v>
       </c>
     </row>
     <row r="66" customFormat="1" spans="1:9">
@@ -3400,11 +4414,11 @@
       <c r="G66" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H66" s="1" t="s">
+      <c r="H66" s="2">
+        <v>106</v>
+      </c>
+      <c r="I66" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="I66" s="2">
-        <v>106</v>
       </c>
     </row>
     <row r="67" customFormat="1" spans="1:9">
@@ -3425,11 +4439,11 @@
       <c r="G67" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="H67" s="1" t="s">
+      <c r="H67" s="2">
+        <v>106</v>
+      </c>
+      <c r="I67" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="I67" s="2">
-        <v>106</v>
       </c>
     </row>
     <row r="68" customFormat="1" spans="1:9">
@@ -3450,11 +4464,11 @@
       <c r="G68" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="H68" s="1" t="s">
+      <c r="H68" s="2">
+        <v>106</v>
+      </c>
+      <c r="I68" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="I68" s="2">
-        <v>106</v>
       </c>
     </row>
     <row r="69" customFormat="1" spans="1:9">
@@ -3475,11 +4489,11 @@
       <c r="G69" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H69" s="1" t="s">
+      <c r="H69" s="2">
+        <v>106</v>
+      </c>
+      <c r="I69" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="I69" s="2">
-        <v>106</v>
       </c>
     </row>
     <row r="71" customFormat="1" spans="1:9">
@@ -3500,11 +4514,11 @@
       <c r="G71" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H71" s="1" t="s">
+      <c r="H71" s="2">
+        <v>107</v>
+      </c>
+      <c r="I71" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="I71" s="2">
-        <v>107</v>
       </c>
     </row>
     <row r="72" customFormat="1" spans="1:9">
@@ -3525,11 +4539,11 @@
       <c r="G72" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H72" s="1" t="s">
+      <c r="H72" s="2">
+        <v>107</v>
+      </c>
+      <c r="I72" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="I72" s="2">
-        <v>107</v>
       </c>
     </row>
     <row r="73" customFormat="1" spans="1:9">
@@ -3550,11 +4564,11 @@
       <c r="G73" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H73" s="1" t="s">
+      <c r="H73" s="2">
+        <v>107</v>
+      </c>
+      <c r="I73" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="I73" s="2">
-        <v>107</v>
       </c>
     </row>
     <row r="74" customFormat="1" spans="1:9">
@@ -3575,11 +4589,11 @@
       <c r="G74" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H74" s="1" t="s">
+      <c r="H74" s="2">
+        <v>107</v>
+      </c>
+      <c r="I74" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="I74" s="2">
-        <v>107</v>
       </c>
     </row>
     <row r="75" customFormat="1" spans="1:9">
@@ -3600,11 +4614,11 @@
       <c r="G75" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H75" s="1" t="s">
+      <c r="H75" s="2">
+        <v>107</v>
+      </c>
+      <c r="I75" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="I75" s="2">
-        <v>107</v>
       </c>
     </row>
     <row r="76" customFormat="1" spans="1:9">
@@ -3625,11 +4639,11 @@
       <c r="G76" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H76" s="1" t="s">
+      <c r="H76" s="2">
+        <v>107</v>
+      </c>
+      <c r="I76" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="I76" s="2">
-        <v>107</v>
       </c>
     </row>
     <row r="77" customFormat="1" spans="1:9">
@@ -3650,11 +4664,11 @@
       <c r="G77" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H77" s="1" t="s">
+      <c r="H77" s="2">
+        <v>107</v>
+      </c>
+      <c r="I77" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="I77" s="2">
-        <v>107</v>
       </c>
     </row>
     <row r="78" customFormat="1" spans="1:9">
@@ -3675,11 +4689,11 @@
       <c r="G78" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="H78" s="1" t="s">
+      <c r="H78" s="2">
+        <v>107</v>
+      </c>
+      <c r="I78" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="I78" s="2">
-        <v>107</v>
       </c>
     </row>
     <row r="79" customFormat="1" spans="1:9">
@@ -3700,11 +4714,11 @@
       <c r="G79" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="H79" s="1" t="s">
+      <c r="H79" s="2">
+        <v>107</v>
+      </c>
+      <c r="I79" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="I79" s="2">
-        <v>107</v>
       </c>
     </row>
     <row r="80" customFormat="1" spans="1:9">
@@ -3725,11 +4739,11 @@
       <c r="G80" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H80" s="1" t="s">
+      <c r="H80" s="2">
+        <v>107</v>
+      </c>
+      <c r="I80" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="I80" s="2">
-        <v>107</v>
       </c>
     </row>
     <row r="82" customFormat="1" spans="1:9">
@@ -3750,11 +4764,11 @@
       <c r="G82" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H82" s="1" t="s">
+      <c r="H82" s="2">
+        <v>108</v>
+      </c>
+      <c r="I82" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="I82" s="2">
-        <v>108</v>
       </c>
     </row>
     <row r="83" customFormat="1" spans="1:9">
@@ -3775,11 +4789,11 @@
       <c r="G83" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H83" s="1" t="s">
+      <c r="H83" s="2">
+        <v>108</v>
+      </c>
+      <c r="I83" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="I83" s="2">
-        <v>108</v>
       </c>
     </row>
     <row r="84" customFormat="1" spans="1:9">
@@ -3800,11 +4814,11 @@
       <c r="G84" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H84" s="1" t="s">
+      <c r="H84" s="2">
+        <v>108</v>
+      </c>
+      <c r="I84" s="1" t="s">
         <v>189</v>
-      </c>
-      <c r="I84" s="2">
-        <v>108</v>
       </c>
     </row>
     <row r="85" customFormat="1" spans="1:9">
@@ -3825,11 +4839,11 @@
       <c r="G85" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H85" s="1" t="s">
+      <c r="H85" s="2">
+        <v>108</v>
+      </c>
+      <c r="I85" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="I85" s="2">
-        <v>108</v>
       </c>
     </row>
     <row r="86" customFormat="1" spans="1:9">
@@ -3850,11 +4864,11 @@
       <c r="G86" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H86" s="1" t="s">
+      <c r="H86" s="2">
+        <v>108</v>
+      </c>
+      <c r="I86" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="I86" s="2">
-        <v>108</v>
       </c>
     </row>
     <row r="87" customFormat="1" spans="1:9">
@@ -3875,11 +4889,11 @@
       <c r="G87" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H87" s="1" t="s">
+      <c r="H87" s="2">
+        <v>108</v>
+      </c>
+      <c r="I87" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="I87" s="2">
-        <v>108</v>
       </c>
     </row>
     <row r="88" customFormat="1" spans="1:9">
@@ -3900,11 +4914,11 @@
       <c r="G88" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H88" s="1" t="s">
+      <c r="H88" s="2">
+        <v>108</v>
+      </c>
+      <c r="I88" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="I88" s="2">
-        <v>108</v>
       </c>
     </row>
     <row r="89" customFormat="1" spans="1:9">
@@ -3925,11 +4939,11 @@
       <c r="G89" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="H89" s="1" t="s">
+      <c r="H89" s="2">
+        <v>108</v>
+      </c>
+      <c r="I89" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="I89" s="2">
-        <v>108</v>
       </c>
     </row>
     <row r="90" customFormat="1" spans="1:9">
@@ -3950,11 +4964,11 @@
       <c r="G90" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="H90" s="1" t="s">
+      <c r="H90" s="2">
+        <v>108</v>
+      </c>
+      <c r="I90" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="I90" s="2">
-        <v>108</v>
       </c>
     </row>
     <row r="91" customFormat="1" spans="1:9">
@@ -3975,11 +4989,11 @@
       <c r="G91" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H91" s="1" t="s">
+      <c r="H91" s="2">
+        <v>108</v>
+      </c>
+      <c r="I91" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="I91" s="2">
-        <v>108</v>
       </c>
     </row>
     <row r="93" customFormat="1" spans="1:9">
@@ -4000,11 +5014,11 @@
       <c r="G93" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H93" s="1" t="s">
+      <c r="H93" s="2">
+        <v>109</v>
+      </c>
+      <c r="I93" s="1" t="s">
         <v>206</v>
-      </c>
-      <c r="I93" s="2">
-        <v>109</v>
       </c>
     </row>
     <row r="94" customFormat="1" spans="1:9">
@@ -4025,11 +5039,11 @@
       <c r="G94" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H94" s="1" t="s">
+      <c r="H94" s="2">
+        <v>109</v>
+      </c>
+      <c r="I94" s="1" t="s">
         <v>208</v>
-      </c>
-      <c r="I94" s="2">
-        <v>109</v>
       </c>
     </row>
     <row r="95" customFormat="1" spans="1:9">
@@ -4050,11 +5064,11 @@
       <c r="G95" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H95" s="1" t="s">
+      <c r="H95" s="2">
+        <v>109</v>
+      </c>
+      <c r="I95" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="I95" s="2">
-        <v>109</v>
       </c>
     </row>
     <row r="96" customFormat="1" spans="1:9">
@@ -4075,11 +5089,11 @@
       <c r="G96" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H96" s="1" t="s">
+      <c r="H96" s="2">
+        <v>109</v>
+      </c>
+      <c r="I96" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="I96" s="2">
-        <v>109</v>
       </c>
     </row>
     <row r="97" customFormat="1" spans="1:9">
@@ -4100,11 +5114,11 @@
       <c r="G97" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H97" s="1" t="s">
+      <c r="H97" s="2">
+        <v>109</v>
+      </c>
+      <c r="I97" s="1" t="s">
         <v>214</v>
-      </c>
-      <c r="I97" s="2">
-        <v>109</v>
       </c>
     </row>
     <row r="98" customFormat="1" spans="1:9">
@@ -4125,11 +5139,11 @@
       <c r="G98" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H98" s="1" t="s">
+      <c r="H98" s="2">
+        <v>109</v>
+      </c>
+      <c r="I98" s="1" t="s">
         <v>216</v>
-      </c>
-      <c r="I98" s="2">
-        <v>109</v>
       </c>
     </row>
     <row r="99" customFormat="1" spans="1:9">
@@ -4150,11 +5164,11 @@
       <c r="G99" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H99" s="1" t="s">
+      <c r="H99" s="2">
+        <v>109</v>
+      </c>
+      <c r="I99" s="1" t="s">
         <v>218</v>
-      </c>
-      <c r="I99" s="2">
-        <v>109</v>
       </c>
     </row>
     <row r="100" customFormat="1" spans="1:9">
@@ -4175,11 +5189,11 @@
       <c r="G100" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="H100" s="1" t="s">
+      <c r="H100" s="2">
+        <v>109</v>
+      </c>
+      <c r="I100" s="1" t="s">
         <v>220</v>
-      </c>
-      <c r="I100" s="2">
-        <v>109</v>
       </c>
     </row>
     <row r="101" customFormat="1" spans="1:9">
@@ -4200,11 +5214,11 @@
       <c r="G101" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="H101" s="1" t="s">
+      <c r="H101" s="2">
+        <v>109</v>
+      </c>
+      <c r="I101" s="1" t="s">
         <v>222</v>
-      </c>
-      <c r="I101" s="2">
-        <v>109</v>
       </c>
     </row>
     <row r="102" customFormat="1" spans="1:9">
@@ -4225,11 +5239,11 @@
       <c r="G102" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H102" s="1" t="s">
+      <c r="H102" s="2">
+        <v>109</v>
+      </c>
+      <c r="I102" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="I102" s="2">
-        <v>109</v>
       </c>
     </row>
     <row r="104" customFormat="1" spans="1:9">
@@ -4250,11 +5264,11 @@
       <c r="G104" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H104" s="1" t="s">
+      <c r="H104" s="2">
+        <v>110</v>
+      </c>
+      <c r="I104" s="1" t="s">
         <v>227</v>
-      </c>
-      <c r="I104" s="2">
-        <v>110</v>
       </c>
     </row>
     <row r="105" customFormat="1" spans="1:9">
@@ -4275,11 +5289,11 @@
       <c r="G105" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H105" s="1" t="s">
+      <c r="H105" s="2">
+        <v>110</v>
+      </c>
+      <c r="I105" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="I105" s="2">
-        <v>110</v>
       </c>
     </row>
     <row r="106" customFormat="1" spans="1:9">
@@ -4300,11 +5314,11 @@
       <c r="G106" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H106" s="1" t="s">
+      <c r="H106" s="2">
+        <v>110</v>
+      </c>
+      <c r="I106" s="1" t="s">
         <v>231</v>
-      </c>
-      <c r="I106" s="2">
-        <v>110</v>
       </c>
     </row>
     <row r="107" customFormat="1" spans="1:9">
@@ -4325,11 +5339,11 @@
       <c r="G107" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H107" s="1" t="s">
+      <c r="H107" s="2">
+        <v>110</v>
+      </c>
+      <c r="I107" s="1" t="s">
         <v>233</v>
-      </c>
-      <c r="I107" s="2">
-        <v>110</v>
       </c>
     </row>
     <row r="108" customFormat="1" spans="1:9">
@@ -4350,11 +5364,11 @@
       <c r="G108" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H108" s="1" t="s">
+      <c r="H108" s="2">
+        <v>110</v>
+      </c>
+      <c r="I108" s="1" t="s">
         <v>235</v>
-      </c>
-      <c r="I108" s="2">
-        <v>110</v>
       </c>
     </row>
     <row r="109" customFormat="1" spans="1:9">
@@ -4375,11 +5389,11 @@
       <c r="G109" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H109" s="1" t="s">
+      <c r="H109" s="2">
+        <v>110</v>
+      </c>
+      <c r="I109" s="1" t="s">
         <v>237</v>
-      </c>
-      <c r="I109" s="2">
-        <v>110</v>
       </c>
     </row>
     <row r="110" customFormat="1" spans="1:9">
@@ -4400,11 +5414,11 @@
       <c r="G110" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H110" s="1" t="s">
+      <c r="H110" s="2">
+        <v>110</v>
+      </c>
+      <c r="I110" s="1" t="s">
         <v>239</v>
-      </c>
-      <c r="I110" s="2">
-        <v>110</v>
       </c>
     </row>
     <row r="111" customFormat="1" spans="1:9">
@@ -4425,11 +5439,11 @@
       <c r="G111" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="H111" s="1" t="s">
+      <c r="H111" s="2">
+        <v>110</v>
+      </c>
+      <c r="I111" s="1" t="s">
         <v>241</v>
-      </c>
-      <c r="I111" s="2">
-        <v>110</v>
       </c>
     </row>
     <row r="112" customFormat="1" spans="1:9">
@@ -4450,11 +5464,11 @@
       <c r="G112" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="H112" s="1" t="s">
+      <c r="H112" s="2">
+        <v>110</v>
+      </c>
+      <c r="I112" s="1" t="s">
         <v>243</v>
-      </c>
-      <c r="I112" s="2">
-        <v>110</v>
       </c>
     </row>
     <row r="113" customFormat="1" spans="1:9">
@@ -4475,11 +5489,11 @@
       <c r="G113" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H113" s="1" t="s">
+      <c r="H113" s="2">
+        <v>110</v>
+      </c>
+      <c r="I113" s="1" t="s">
         <v>245</v>
-      </c>
-      <c r="I113" s="2">
-        <v>110</v>
       </c>
     </row>
     <row r="115" customFormat="1" spans="1:9">
@@ -4500,11 +5514,11 @@
       <c r="G115" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H115" s="1" t="s">
+      <c r="H115" s="2">
+        <v>111</v>
+      </c>
+      <c r="I115" s="1" t="s">
         <v>248</v>
-      </c>
-      <c r="I115" s="2">
-        <v>111</v>
       </c>
     </row>
     <row r="116" customFormat="1" spans="1:9">
@@ -4525,11 +5539,11 @@
       <c r="G116" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H116" s="1" t="s">
+      <c r="H116" s="2">
+        <v>111</v>
+      </c>
+      <c r="I116" s="1" t="s">
         <v>250</v>
-      </c>
-      <c r="I116" s="2">
-        <v>111</v>
       </c>
     </row>
     <row r="117" customFormat="1" spans="1:9">
@@ -4550,11 +5564,11 @@
       <c r="G117" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H117" s="1" t="s">
+      <c r="H117" s="2">
+        <v>111</v>
+      </c>
+      <c r="I117" s="1" t="s">
         <v>252</v>
-      </c>
-      <c r="I117" s="2">
-        <v>111</v>
       </c>
     </row>
     <row r="118" customFormat="1" spans="1:9">
@@ -4575,11 +5589,11 @@
       <c r="G118" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H118" s="1" t="s">
+      <c r="H118" s="2">
+        <v>111</v>
+      </c>
+      <c r="I118" s="1" t="s">
         <v>254</v>
-      </c>
-      <c r="I118" s="2">
-        <v>111</v>
       </c>
     </row>
     <row r="119" customFormat="1" spans="1:9">
@@ -4600,11 +5614,11 @@
       <c r="G119" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H119" s="1" t="s">
+      <c r="H119" s="2">
+        <v>111</v>
+      </c>
+      <c r="I119" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="I119" s="2">
-        <v>111</v>
       </c>
     </row>
     <row r="120" customFormat="1" spans="1:9">
@@ -4625,11 +5639,11 @@
       <c r="G120" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H120" s="1" t="s">
+      <c r="H120" s="2">
+        <v>111</v>
+      </c>
+      <c r="I120" s="1" t="s">
         <v>258</v>
-      </c>
-      <c r="I120" s="2">
-        <v>111</v>
       </c>
     </row>
     <row r="121" customFormat="1" spans="1:9">
@@ -4650,11 +5664,11 @@
       <c r="G121" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H121" s="1" t="s">
+      <c r="H121" s="2">
+        <v>111</v>
+      </c>
+      <c r="I121" s="1" t="s">
         <v>260</v>
-      </c>
-      <c r="I121" s="2">
-        <v>111</v>
       </c>
     </row>
     <row r="122" customFormat="1" spans="1:9">
@@ -4675,11 +5689,11 @@
       <c r="G122" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="H122" s="1" t="s">
+      <c r="H122" s="2">
+        <v>111</v>
+      </c>
+      <c r="I122" s="1" t="s">
         <v>262</v>
-      </c>
-      <c r="I122" s="2">
-        <v>111</v>
       </c>
     </row>
     <row r="123" customFormat="1" spans="1:9">
@@ -4700,11 +5714,11 @@
       <c r="G123" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="H123" s="1" t="s">
+      <c r="H123" s="2">
+        <v>111</v>
+      </c>
+      <c r="I123" s="1" t="s">
         <v>264</v>
-      </c>
-      <c r="I123" s="2">
-        <v>111</v>
       </c>
     </row>
     <row r="124" customFormat="1" spans="1:9">
@@ -4725,11 +5739,11 @@
       <c r="G124" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H124" s="1" t="s">
+      <c r="H124" s="2">
+        <v>111</v>
+      </c>
+      <c r="I124" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="I124" s="2">
-        <v>111</v>
       </c>
     </row>
     <row r="126" customFormat="1" spans="1:9">
@@ -4750,11 +5764,11 @@
       <c r="G126" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H126" s="1" t="s">
+      <c r="H126" s="2">
+        <v>112</v>
+      </c>
+      <c r="I126" s="1" t="s">
         <v>269</v>
-      </c>
-      <c r="I126" s="2">
-        <v>112</v>
       </c>
     </row>
     <row r="127" customFormat="1" spans="1:9">
@@ -4775,11 +5789,11 @@
       <c r="G127" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H127" s="1" t="s">
+      <c r="H127" s="2">
+        <v>112</v>
+      </c>
+      <c r="I127" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="I127" s="2">
-        <v>112</v>
       </c>
     </row>
     <row r="128" customFormat="1" spans="1:9">
@@ -4800,11 +5814,11 @@
       <c r="G128" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H128" s="1" t="s">
+      <c r="H128" s="2">
+        <v>112</v>
+      </c>
+      <c r="I128" s="1" t="s">
         <v>273</v>
-      </c>
-      <c r="I128" s="2">
-        <v>112</v>
       </c>
     </row>
     <row r="129" customFormat="1" spans="1:9">
@@ -4825,11 +5839,11 @@
       <c r="G129" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H129" s="1" t="s">
+      <c r="H129" s="2">
+        <v>112</v>
+      </c>
+      <c r="I129" s="1" t="s">
         <v>275</v>
-      </c>
-      <c r="I129" s="2">
-        <v>112</v>
       </c>
     </row>
     <row r="130" customFormat="1" spans="1:9">
@@ -4850,11 +5864,11 @@
       <c r="G130" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H130" s="1" t="s">
+      <c r="H130" s="2">
+        <v>112</v>
+      </c>
+      <c r="I130" s="1" t="s">
         <v>277</v>
-      </c>
-      <c r="I130" s="2">
-        <v>112</v>
       </c>
     </row>
     <row r="131" customFormat="1" spans="1:9">
@@ -4875,11 +5889,11 @@
       <c r="G131" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H131" s="1" t="s">
+      <c r="H131" s="2">
+        <v>112</v>
+      </c>
+      <c r="I131" s="1" t="s">
         <v>279</v>
-      </c>
-      <c r="I131" s="2">
-        <v>112</v>
       </c>
     </row>
     <row r="132" customFormat="1" spans="1:9">
@@ -4900,11 +5914,11 @@
       <c r="G132" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H132" s="1" t="s">
+      <c r="H132" s="2">
+        <v>112</v>
+      </c>
+      <c r="I132" s="1" t="s">
         <v>281</v>
-      </c>
-      <c r="I132" s="2">
-        <v>112</v>
       </c>
     </row>
     <row r="133" customFormat="1" spans="1:9">
@@ -4925,11 +5939,11 @@
       <c r="G133" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="H133" s="1" t="s">
+      <c r="H133" s="2">
+        <v>112</v>
+      </c>
+      <c r="I133" s="1" t="s">
         <v>283</v>
-      </c>
-      <c r="I133" s="2">
-        <v>112</v>
       </c>
     </row>
     <row r="134" customFormat="1" spans="1:9">
@@ -4950,11 +5964,11 @@
       <c r="G134" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="H134" s="1" t="s">
+      <c r="H134" s="2">
+        <v>112</v>
+      </c>
+      <c r="I134" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="I134" s="2">
-        <v>112</v>
       </c>
     </row>
     <row r="135" customFormat="1" spans="1:9">
@@ -4975,11 +5989,4014 @@
       <c r="G135" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H135" s="1" t="s">
+      <c r="H135" s="2">
+        <v>112</v>
+      </c>
+      <c r="I135" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="I135" s="2">
-        <v>112</v>
+    </row>
+    <row r="137" customFormat="1" spans="1:9">
+      <c r="A137" s="1"/>
+      <c r="B137" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C137" s="2">
+        <v>201</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F137" s="1"/>
+      <c r="G137" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H137" s="2">
+        <v>201</v>
+      </c>
+      <c r="I137" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="138" customFormat="1" spans="1:9">
+      <c r="A138" s="1"/>
+      <c r="B138" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C138" s="2">
+        <v>201</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F138" s="1"/>
+      <c r="G138" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H138" s="2">
+        <v>201</v>
+      </c>
+      <c r="I138" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="139" customFormat="1" spans="1:9">
+      <c r="A139" s="1"/>
+      <c r="B139" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C139" s="2">
+        <v>201</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F139" s="1"/>
+      <c r="G139" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H139" s="2">
+        <v>201</v>
+      </c>
+      <c r="I139" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="140" customFormat="1" spans="1:9">
+      <c r="A140" s="1"/>
+      <c r="B140" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C140" s="2">
+        <v>201</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F140" s="1"/>
+      <c r="G140" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H140" s="2">
+        <v>201</v>
+      </c>
+      <c r="I140" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="141" customFormat="1" spans="1:9">
+      <c r="A141" s="1"/>
+      <c r="B141" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C141" s="2">
+        <v>201</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F141" s="1"/>
+      <c r="G141" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H141" s="2">
+        <v>201</v>
+      </c>
+      <c r="I141" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="142" customFormat="1" spans="1:9">
+      <c r="A142" s="1"/>
+      <c r="B142" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C142" s="2">
+        <v>201</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F142" s="1"/>
+      <c r="G142" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H142" s="2">
+        <v>201</v>
+      </c>
+      <c r="I142" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="143" customFormat="1" spans="1:9">
+      <c r="A143" s="1"/>
+      <c r="B143" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C143" s="2">
+        <v>201</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F143" s="1"/>
+      <c r="G143" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H143" s="2">
+        <v>201</v>
+      </c>
+      <c r="I143" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="144" customFormat="1" spans="1:9">
+      <c r="A144" s="1"/>
+      <c r="B144" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C144" s="2">
+        <v>201</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F144" s="1"/>
+      <c r="G144" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H144" s="2">
+        <v>201</v>
+      </c>
+      <c r="I144" s="1" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="145" customFormat="1" spans="1:9">
+      <c r="A145" s="1"/>
+      <c r="B145" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C145" s="2">
+        <v>201</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F145" s="1"/>
+      <c r="G145" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H145" s="2">
+        <v>201</v>
+      </c>
+      <c r="I145" s="1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="146" customFormat="1" spans="1:9">
+      <c r="A146" s="1"/>
+      <c r="B146" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C146" s="2">
+        <v>201</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F146" s="1"/>
+      <c r="G146" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H146" s="2">
+        <v>201</v>
+      </c>
+      <c r="I146" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="148" customFormat="1" spans="1:9">
+      <c r="A148" s="1"/>
+      <c r="B148" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="C148" s="2">
+        <v>202</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F148" s="1"/>
+      <c r="G148" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H148" s="2">
+        <v>202</v>
+      </c>
+      <c r="I148" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="149" customFormat="1" spans="1:9">
+      <c r="A149" s="1"/>
+      <c r="B149" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C149" s="2">
+        <v>202</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F149" s="1"/>
+      <c r="G149" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H149" s="2">
+        <v>202</v>
+      </c>
+      <c r="I149" s="1" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="150" customFormat="1" spans="1:9">
+      <c r="A150" s="1"/>
+      <c r="B150" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C150" s="2">
+        <v>202</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F150" s="1"/>
+      <c r="G150" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H150" s="2">
+        <v>202</v>
+      </c>
+      <c r="I150" s="1" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="151" customFormat="1" spans="1:9">
+      <c r="A151" s="1"/>
+      <c r="B151" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C151" s="2">
+        <v>202</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F151" s="1"/>
+      <c r="G151" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H151" s="2">
+        <v>202</v>
+      </c>
+      <c r="I151" s="1" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="152" customFormat="1" spans="1:9">
+      <c r="A152" s="1"/>
+      <c r="B152" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C152" s="2">
+        <v>202</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F152" s="1"/>
+      <c r="G152" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H152" s="2">
+        <v>202</v>
+      </c>
+      <c r="I152" s="1" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="153" customFormat="1" spans="1:9">
+      <c r="A153" s="1"/>
+      <c r="B153" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C153" s="2">
+        <v>202</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F153" s="1"/>
+      <c r="G153" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H153" s="2">
+        <v>202</v>
+      </c>
+      <c r="I153" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="154" customFormat="1" spans="1:9">
+      <c r="A154" s="1"/>
+      <c r="B154" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C154" s="2">
+        <v>202</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F154" s="1"/>
+      <c r="G154" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H154" s="2">
+        <v>202</v>
+      </c>
+      <c r="I154" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="155" customFormat="1" spans="1:9">
+      <c r="A155" s="1"/>
+      <c r="B155" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C155" s="2">
+        <v>202</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F155" s="1"/>
+      <c r="G155" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H155" s="2">
+        <v>202</v>
+      </c>
+      <c r="I155" s="1" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="156" customFormat="1" spans="1:9">
+      <c r="A156" s="1"/>
+      <c r="B156" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C156" s="2">
+        <v>202</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F156" s="1"/>
+      <c r="G156" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H156" s="2">
+        <v>202</v>
+      </c>
+      <c r="I156" s="1" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="157" customFormat="1" spans="1:9">
+      <c r="A157" s="1"/>
+      <c r="B157" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C157" s="2">
+        <v>202</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F157" s="1"/>
+      <c r="G157" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H157" s="2">
+        <v>202</v>
+      </c>
+      <c r="I157" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="159" customFormat="1" spans="1:9">
+      <c r="A159" s="1"/>
+      <c r="B159" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C159" s="2">
+        <v>203</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F159" s="1"/>
+      <c r="G159" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H159" s="2">
+        <v>203</v>
+      </c>
+      <c r="I159" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="160" customFormat="1" spans="1:9">
+      <c r="A160" s="1"/>
+      <c r="B160" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C160" s="2">
+        <v>203</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F160" s="1"/>
+      <c r="G160" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H160" s="2">
+        <v>203</v>
+      </c>
+      <c r="I160" s="1" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="161" customFormat="1" spans="1:9">
+      <c r="A161" s="1"/>
+      <c r="B161" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C161" s="2">
+        <v>203</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F161" s="1"/>
+      <c r="G161" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H161" s="2">
+        <v>203</v>
+      </c>
+      <c r="I161" s="1" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="162" customFormat="1" spans="1:9">
+      <c r="A162" s="1"/>
+      <c r="B162" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C162" s="2">
+        <v>203</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F162" s="1"/>
+      <c r="G162" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H162" s="2">
+        <v>203</v>
+      </c>
+      <c r="I162" s="1" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="163" customFormat="1" spans="1:9">
+      <c r="A163" s="1"/>
+      <c r="B163" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C163" s="2">
+        <v>203</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F163" s="1"/>
+      <c r="G163" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H163" s="2">
+        <v>203</v>
+      </c>
+      <c r="I163" s="1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="164" customFormat="1" spans="1:9">
+      <c r="A164" s="1"/>
+      <c r="B164" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C164" s="2">
+        <v>203</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="E164" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F164" s="1"/>
+      <c r="G164" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H164" s="2">
+        <v>203</v>
+      </c>
+      <c r="I164" s="1" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="165" customFormat="1" spans="1:9">
+      <c r="A165" s="1"/>
+      <c r="B165" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C165" s="2">
+        <v>203</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F165" s="1"/>
+      <c r="G165" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H165" s="2">
+        <v>203</v>
+      </c>
+      <c r="I165" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="166" customFormat="1" spans="1:9">
+      <c r="A166" s="1"/>
+      <c r="B166" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C166" s="2">
+        <v>203</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F166" s="1"/>
+      <c r="G166" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H166" s="2">
+        <v>203</v>
+      </c>
+      <c r="I166" s="1" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="167" customFormat="1" spans="1:9">
+      <c r="A167" s="1"/>
+      <c r="B167" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C167" s="2">
+        <v>203</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F167" s="1"/>
+      <c r="G167" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H167" s="2">
+        <v>203</v>
+      </c>
+      <c r="I167" s="1" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="168" customFormat="1" spans="1:9">
+      <c r="A168" s="1"/>
+      <c r="B168" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C168" s="2">
+        <v>203</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F168" s="1"/>
+      <c r="G168" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H168" s="2">
+        <v>203</v>
+      </c>
+      <c r="I168" s="1" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="170" customFormat="1" spans="1:9">
+      <c r="A170" s="1"/>
+      <c r="B170" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C170" s="2">
+        <v>204</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F170" s="1"/>
+      <c r="G170" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H170" s="2">
+        <v>204</v>
+      </c>
+      <c r="I170" s="1" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="171" customFormat="1" spans="1:9">
+      <c r="A171" s="1"/>
+      <c r="B171" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="C171" s="2">
+        <v>204</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="E171" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F171" s="1"/>
+      <c r="G171" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H171" s="2">
+        <v>204</v>
+      </c>
+      <c r="I171" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="172" customFormat="1" spans="1:9">
+      <c r="A172" s="1"/>
+      <c r="B172" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="C172" s="2">
+        <v>204</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F172" s="1"/>
+      <c r="G172" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H172" s="2">
+        <v>204</v>
+      </c>
+      <c r="I172" s="1" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="173" customFormat="1" spans="1:9">
+      <c r="A173" s="1"/>
+      <c r="B173" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C173" s="2">
+        <v>204</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F173" s="1"/>
+      <c r="G173" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H173" s="2">
+        <v>204</v>
+      </c>
+      <c r="I173" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="174" customFormat="1" spans="1:9">
+      <c r="A174" s="1"/>
+      <c r="B174" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C174" s="2">
+        <v>204</v>
+      </c>
+      <c r="D174" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="E174" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F174" s="1"/>
+      <c r="G174" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H174" s="2">
+        <v>204</v>
+      </c>
+      <c r="I174" s="1" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="175" customFormat="1" spans="1:9">
+      <c r="A175" s="1"/>
+      <c r="B175" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C175" s="2">
+        <v>204</v>
+      </c>
+      <c r="D175" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="E175" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F175" s="1"/>
+      <c r="G175" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H175" s="2">
+        <v>204</v>
+      </c>
+      <c r="I175" s="1" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="176" customFormat="1" spans="1:9">
+      <c r="A176" s="1"/>
+      <c r="B176" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C176" s="2">
+        <v>204</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="E176" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F176" s="1"/>
+      <c r="G176" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H176" s="2">
+        <v>204</v>
+      </c>
+      <c r="I176" s="1" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="177" customFormat="1" spans="1:9">
+      <c r="A177" s="1"/>
+      <c r="B177" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C177" s="2">
+        <v>204</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="E177" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F177" s="1"/>
+      <c r="G177" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H177" s="2">
+        <v>204</v>
+      </c>
+      <c r="I177" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="178" customFormat="1" spans="1:9">
+      <c r="A178" s="1"/>
+      <c r="B178" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C178" s="2">
+        <v>204</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="E178" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F178" s="1"/>
+      <c r="G178" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H178" s="2">
+        <v>204</v>
+      </c>
+      <c r="I178" s="1" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="179" customFormat="1" spans="1:9">
+      <c r="A179" s="1"/>
+      <c r="B179" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="C179" s="2">
+        <v>204</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="E179" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F179" s="1"/>
+      <c r="G179" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H179" s="2">
+        <v>204</v>
+      </c>
+      <c r="I179" s="1" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="181" customFormat="1" spans="1:9">
+      <c r="A181" s="1"/>
+      <c r="B181" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C181" s="2">
+        <v>205</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F181" s="1"/>
+      <c r="G181" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H181" s="2">
+        <v>205</v>
+      </c>
+      <c r="I181" s="1" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="182" customFormat="1" spans="1:9">
+      <c r="A182" s="1"/>
+      <c r="B182" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C182" s="2">
+        <v>205</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F182" s="1"/>
+      <c r="G182" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H182" s="2">
+        <v>205</v>
+      </c>
+      <c r="I182" s="1" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="183" customFormat="1" spans="1:9">
+      <c r="A183" s="1"/>
+      <c r="B183" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="C183" s="2">
+        <v>205</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F183" s="1"/>
+      <c r="G183" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H183" s="2">
+        <v>205</v>
+      </c>
+      <c r="I183" s="1" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="184" customFormat="1" spans="1:9">
+      <c r="A184" s="1"/>
+      <c r="B184" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C184" s="2">
+        <v>205</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F184" s="1"/>
+      <c r="G184" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H184" s="2">
+        <v>205</v>
+      </c>
+      <c r="I184" s="1" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="185" customFormat="1" spans="1:9">
+      <c r="A185" s="1"/>
+      <c r="B185" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="C185" s="2">
+        <v>205</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F185" s="1"/>
+      <c r="G185" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H185" s="2">
+        <v>205</v>
+      </c>
+      <c r="I185" s="1" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="186" customFormat="1" spans="1:9">
+      <c r="A186" s="1"/>
+      <c r="B186" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="C186" s="2">
+        <v>205</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F186" s="1"/>
+      <c r="G186" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H186" s="2">
+        <v>205</v>
+      </c>
+      <c r="I186" s="1" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="187" customFormat="1" spans="1:9">
+      <c r="A187" s="1"/>
+      <c r="B187" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C187" s="2">
+        <v>205</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F187" s="1"/>
+      <c r="G187" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H187" s="2">
+        <v>205</v>
+      </c>
+      <c r="I187" s="1" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="188" customFormat="1" spans="1:9">
+      <c r="A188" s="1"/>
+      <c r="B188" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C188" s="2">
+        <v>205</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F188" s="1"/>
+      <c r="G188" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H188" s="2">
+        <v>205</v>
+      </c>
+      <c r="I188" s="1" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="189" customFormat="1" spans="1:9">
+      <c r="A189" s="1"/>
+      <c r="B189" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C189" s="2">
+        <v>205</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F189" s="1"/>
+      <c r="G189" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H189" s="2">
+        <v>205</v>
+      </c>
+      <c r="I189" s="1" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="190" customFormat="1" spans="1:9">
+      <c r="A190" s="1"/>
+      <c r="B190" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C190" s="2">
+        <v>205</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="E190" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F190" s="1"/>
+      <c r="G190" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H190" s="2">
+        <v>205</v>
+      </c>
+      <c r="I190" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="192" customFormat="1" spans="1:9">
+      <c r="A192" s="1"/>
+      <c r="B192" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="C192" s="2">
+        <v>206</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F192" s="1"/>
+      <c r="G192" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H192" s="2">
+        <v>206</v>
+      </c>
+      <c r="I192" s="1" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="193" customFormat="1" spans="1:9">
+      <c r="A193" s="1"/>
+      <c r="B193" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="C193" s="2">
+        <v>206</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F193" s="1"/>
+      <c r="G193" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H193" s="2">
+        <v>206</v>
+      </c>
+      <c r="I193" s="1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="194" customFormat="1" spans="1:9">
+      <c r="A194" s="1"/>
+      <c r="B194" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C194" s="2">
+        <v>206</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E194" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F194" s="1"/>
+      <c r="G194" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H194" s="2">
+        <v>206</v>
+      </c>
+      <c r="I194" s="1" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="195" customFormat="1" spans="1:9">
+      <c r="A195" s="1"/>
+      <c r="B195" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="C195" s="2">
+        <v>206</v>
+      </c>
+      <c r="D195" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F195" s="1"/>
+      <c r="G195" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H195" s="2">
+        <v>206</v>
+      </c>
+      <c r="I195" s="1" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="196" customFormat="1" spans="1:9">
+      <c r="A196" s="1"/>
+      <c r="B196" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="C196" s="2">
+        <v>206</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E196" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F196" s="1"/>
+      <c r="G196" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H196" s="2">
+        <v>206</v>
+      </c>
+      <c r="I196" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="197" customFormat="1" spans="1:9">
+      <c r="A197" s="1"/>
+      <c r="B197" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="C197" s="2">
+        <v>206</v>
+      </c>
+      <c r="D197" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E197" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F197" s="1"/>
+      <c r="G197" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H197" s="2">
+        <v>206</v>
+      </c>
+      <c r="I197" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="198" customFormat="1" spans="1:9">
+      <c r="A198" s="1"/>
+      <c r="B198" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C198" s="2">
+        <v>206</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F198" s="1"/>
+      <c r="G198" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H198" s="2">
+        <v>206</v>
+      </c>
+      <c r="I198" s="1" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="199" customFormat="1" spans="1:9">
+      <c r="A199" s="1"/>
+      <c r="B199" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C199" s="2">
+        <v>206</v>
+      </c>
+      <c r="D199" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E199" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F199" s="1"/>
+      <c r="G199" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H199" s="2">
+        <v>206</v>
+      </c>
+      <c r="I199" s="1" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="200" customFormat="1" spans="1:9">
+      <c r="A200" s="1"/>
+      <c r="B200" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C200" s="2">
+        <v>206</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F200" s="1"/>
+      <c r="G200" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H200" s="2">
+        <v>206</v>
+      </c>
+      <c r="I200" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="201" customFormat="1" spans="1:9">
+      <c r="A201" s="1"/>
+      <c r="B201" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C201" s="2">
+        <v>206</v>
+      </c>
+      <c r="D201" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F201" s="1"/>
+      <c r="G201" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H201" s="2">
+        <v>206</v>
+      </c>
+      <c r="I201" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="203" customFormat="1" spans="1:9">
+      <c r="A203" s="1"/>
+      <c r="B203" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C203" s="2">
+        <v>207</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="E203" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F203" s="1"/>
+      <c r="G203" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H203" s="2">
+        <v>207</v>
+      </c>
+      <c r="I203" s="1" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="204" customFormat="1" spans="1:9">
+      <c r="A204" s="1"/>
+      <c r="B204" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C204" s="2">
+        <v>207</v>
+      </c>
+      <c r="D204" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="E204" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F204" s="1"/>
+      <c r="G204" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H204" s="2">
+        <v>207</v>
+      </c>
+      <c r="I204" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="205" customFormat="1" spans="1:9">
+      <c r="A205" s="1"/>
+      <c r="B205" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C205" s="2">
+        <v>207</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F205" s="1"/>
+      <c r="G205" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H205" s="2">
+        <v>207</v>
+      </c>
+      <c r="I205" s="1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="206" customFormat="1" spans="1:9">
+      <c r="A206" s="1"/>
+      <c r="B206" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C206" s="2">
+        <v>207</v>
+      </c>
+      <c r="D206" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F206" s="1"/>
+      <c r="G206" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H206" s="2">
+        <v>207</v>
+      </c>
+      <c r="I206" s="1" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="207" customFormat="1" spans="1:9">
+      <c r="A207" s="1"/>
+      <c r="B207" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C207" s="2">
+        <v>207</v>
+      </c>
+      <c r="D207" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F207" s="1"/>
+      <c r="G207" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H207" s="2">
+        <v>207</v>
+      </c>
+      <c r="I207" s="1" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="208" customFormat="1" spans="1:9">
+      <c r="A208" s="1"/>
+      <c r="B208" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C208" s="2">
+        <v>207</v>
+      </c>
+      <c r="D208" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="E208" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F208" s="1"/>
+      <c r="G208" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H208" s="2">
+        <v>207</v>
+      </c>
+      <c r="I208" s="1" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="209" customFormat="1" spans="1:9">
+      <c r="A209" s="1"/>
+      <c r="B209" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C209" s="2">
+        <v>207</v>
+      </c>
+      <c r="D209" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="E209" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F209" s="1"/>
+      <c r="G209" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H209" s="2">
+        <v>207</v>
+      </c>
+      <c r="I209" s="1" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="210" customFormat="1" spans="1:9">
+      <c r="A210" s="1"/>
+      <c r="B210" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C210" s="2">
+        <v>207</v>
+      </c>
+      <c r="D210" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F210" s="1"/>
+      <c r="G210" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H210" s="2">
+        <v>207</v>
+      </c>
+      <c r="I210" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="211" customFormat="1" spans="1:9">
+      <c r="A211" s="1"/>
+      <c r="B211" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C211" s="2">
+        <v>207</v>
+      </c>
+      <c r="D211" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="E211" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F211" s="1"/>
+      <c r="G211" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H211" s="2">
+        <v>207</v>
+      </c>
+      <c r="I211" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="212" customFormat="1" spans="1:9">
+      <c r="A212" s="1"/>
+      <c r="B212" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C212" s="2">
+        <v>207</v>
+      </c>
+      <c r="D212" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="E212" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F212" s="1"/>
+      <c r="G212" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H212" s="2">
+        <v>207</v>
+      </c>
+      <c r="I212" s="1" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="214" customFormat="1" spans="1:9">
+      <c r="A214" s="1"/>
+      <c r="B214" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="C214" s="2">
+        <v>208</v>
+      </c>
+      <c r="D214" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="E214" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F214" s="1"/>
+      <c r="G214" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H214" s="2">
+        <v>208</v>
+      </c>
+      <c r="I214" s="1" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="215" customFormat="1" spans="1:9">
+      <c r="A215" s="1"/>
+      <c r="B215" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C215" s="2">
+        <v>208</v>
+      </c>
+      <c r="D215" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="E215" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F215" s="1"/>
+      <c r="G215" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H215" s="2">
+        <v>208</v>
+      </c>
+      <c r="I215" s="1" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="216" customFormat="1" spans="1:9">
+      <c r="A216" s="1"/>
+      <c r="B216" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="C216" s="2">
+        <v>208</v>
+      </c>
+      <c r="D216" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="E216" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F216" s="1"/>
+      <c r="G216" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H216" s="2">
+        <v>208</v>
+      </c>
+      <c r="I216" s="1" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="217" customFormat="1" spans="1:9">
+      <c r="A217" s="1"/>
+      <c r="B217" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C217" s="2">
+        <v>208</v>
+      </c>
+      <c r="D217" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="E217" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F217" s="1"/>
+      <c r="G217" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H217" s="2">
+        <v>208</v>
+      </c>
+      <c r="I217" s="1" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="218" customFormat="1" spans="1:9">
+      <c r="A218" s="1"/>
+      <c r="B218" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C218" s="2">
+        <v>208</v>
+      </c>
+      <c r="D218" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="E218" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F218" s="1"/>
+      <c r="G218" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H218" s="2">
+        <v>208</v>
+      </c>
+      <c r="I218" s="1" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="219" customFormat="1" spans="1:9">
+      <c r="A219" s="1"/>
+      <c r="B219" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C219" s="2">
+        <v>208</v>
+      </c>
+      <c r="D219" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="E219" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F219" s="1"/>
+      <c r="G219" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H219" s="2">
+        <v>208</v>
+      </c>
+      <c r="I219" s="1" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="220" customFormat="1" spans="1:9">
+      <c r="A220" s="1"/>
+      <c r="B220" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C220" s="2">
+        <v>208</v>
+      </c>
+      <c r="D220" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="E220" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F220" s="1"/>
+      <c r="G220" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H220" s="2">
+        <v>208</v>
+      </c>
+      <c r="I220" s="1" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="221" customFormat="1" spans="1:9">
+      <c r="A221" s="1"/>
+      <c r="B221" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="C221" s="2">
+        <v>208</v>
+      </c>
+      <c r="D221" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="E221" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F221" s="1"/>
+      <c r="G221" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H221" s="2">
+        <v>208</v>
+      </c>
+      <c r="I221" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="222" customFormat="1" spans="1:9">
+      <c r="A222" s="1"/>
+      <c r="B222" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="C222" s="2">
+        <v>208</v>
+      </c>
+      <c r="D222" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="E222" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F222" s="1"/>
+      <c r="G222" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H222" s="2">
+        <v>208</v>
+      </c>
+      <c r="I222" s="1" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="223" customFormat="1" spans="1:9">
+      <c r="A223" s="1"/>
+      <c r="B223" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="C223" s="2">
+        <v>208</v>
+      </c>
+      <c r="D223" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="E223" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F223" s="1"/>
+      <c r="G223" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H223" s="2">
+        <v>208</v>
+      </c>
+      <c r="I223" s="1" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="225" customFormat="1" spans="1:9">
+      <c r="A225" s="1"/>
+      <c r="B225" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="C225" s="2">
+        <v>301</v>
+      </c>
+      <c r="D225" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="E225" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F225" s="1"/>
+      <c r="G225" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H225" s="2">
+        <v>301</v>
+      </c>
+      <c r="I225" s="1" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="226" customFormat="1" spans="1:9">
+      <c r="A226" s="1"/>
+      <c r="B226" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C226" s="2">
+        <v>301</v>
+      </c>
+      <c r="D226" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="E226" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F226" s="1"/>
+      <c r="G226" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H226" s="2">
+        <v>301</v>
+      </c>
+      <c r="I226" s="1" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="227" customFormat="1" spans="1:9">
+      <c r="A227" s="1"/>
+      <c r="B227" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="C227" s="2">
+        <v>301</v>
+      </c>
+      <c r="D227" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="E227" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F227" s="1"/>
+      <c r="G227" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H227" s="2">
+        <v>301</v>
+      </c>
+      <c r="I227" s="1" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="228" customFormat="1" spans="1:9">
+      <c r="A228" s="1"/>
+      <c r="B228" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C228" s="2">
+        <v>301</v>
+      </c>
+      <c r="D228" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="E228" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F228" s="1"/>
+      <c r="G228" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H228" s="2">
+        <v>301</v>
+      </c>
+      <c r="I228" s="1" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="229" customFormat="1" spans="1:9">
+      <c r="A229" s="1"/>
+      <c r="B229" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="C229" s="2">
+        <v>301</v>
+      </c>
+      <c r="D229" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="E229" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F229" s="1"/>
+      <c r="G229" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H229" s="2">
+        <v>301</v>
+      </c>
+      <c r="I229" s="1" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="230" customFormat="1" spans="1:9">
+      <c r="A230" s="1"/>
+      <c r="B230" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="C230" s="2">
+        <v>301</v>
+      </c>
+      <c r="D230" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="E230" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F230" s="1"/>
+      <c r="G230" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H230" s="2">
+        <v>301</v>
+      </c>
+      <c r="I230" s="1" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="231" customFormat="1" spans="1:9">
+      <c r="A231" s="1"/>
+      <c r="B231" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="C231" s="2">
+        <v>301</v>
+      </c>
+      <c r="D231" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="E231" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F231" s="1"/>
+      <c r="G231" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H231" s="2">
+        <v>301</v>
+      </c>
+      <c r="I231" s="1" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="232" customFormat="1" spans="1:9">
+      <c r="A232" s="1"/>
+      <c r="B232" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="C232" s="2">
+        <v>301</v>
+      </c>
+      <c r="D232" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="E232" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F232" s="1"/>
+      <c r="G232" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H232" s="2">
+        <v>301</v>
+      </c>
+      <c r="I232" s="1" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="233" customFormat="1" spans="1:9">
+      <c r="A233" s="1"/>
+      <c r="B233" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="C233" s="2">
+        <v>301</v>
+      </c>
+      <c r="D233" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="E233" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F233" s="1"/>
+      <c r="G233" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H233" s="2">
+        <v>301</v>
+      </c>
+      <c r="I233" s="1" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="234" customFormat="1" spans="1:9">
+      <c r="A234" s="1"/>
+      <c r="B234" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="C234" s="2">
+        <v>301</v>
+      </c>
+      <c r="D234" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="E234" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F234" s="1"/>
+      <c r="G234" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H234" s="2">
+        <v>301</v>
+      </c>
+      <c r="I234" s="1" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="236" customFormat="1" spans="1:9">
+      <c r="A236" s="1"/>
+      <c r="B236" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C236" s="2">
+        <v>302</v>
+      </c>
+      <c r="D236" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="E236" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F236" s="1"/>
+      <c r="G236" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H236" s="2">
+        <v>302</v>
+      </c>
+      <c r="I236" s="1" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="237" customFormat="1" spans="1:9">
+      <c r="A237" s="1"/>
+      <c r="B237" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C237" s="2">
+        <v>302</v>
+      </c>
+      <c r="D237" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="E237" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F237" s="1"/>
+      <c r="G237" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H237" s="2">
+        <v>302</v>
+      </c>
+      <c r="I237" s="1" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="238" customFormat="1" spans="1:9">
+      <c r="A238" s="1"/>
+      <c r="B238" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C238" s="2">
+        <v>302</v>
+      </c>
+      <c r="D238" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="E238" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F238" s="1"/>
+      <c r="G238" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H238" s="2">
+        <v>302</v>
+      </c>
+      <c r="I238" s="1" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="239" customFormat="1" spans="1:9">
+      <c r="A239" s="1"/>
+      <c r="B239" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="C239" s="2">
+        <v>302</v>
+      </c>
+      <c r="D239" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="E239" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F239" s="1"/>
+      <c r="G239" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H239" s="2">
+        <v>302</v>
+      </c>
+      <c r="I239" s="1" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="240" customFormat="1" spans="1:9">
+      <c r="A240" s="1"/>
+      <c r="B240" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="C240" s="2">
+        <v>302</v>
+      </c>
+      <c r="D240" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="E240" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F240" s="1"/>
+      <c r="G240" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H240" s="2">
+        <v>302</v>
+      </c>
+      <c r="I240" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="241" customFormat="1" spans="1:9">
+      <c r="A241" s="1"/>
+      <c r="B241" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="C241" s="2">
+        <v>302</v>
+      </c>
+      <c r="D241" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="E241" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F241" s="1"/>
+      <c r="G241" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H241" s="2">
+        <v>302</v>
+      </c>
+      <c r="I241" s="1" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="242" customFormat="1" spans="1:9">
+      <c r="A242" s="1"/>
+      <c r="B242" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="C242" s="2">
+        <v>302</v>
+      </c>
+      <c r="D242" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="E242" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F242" s="1"/>
+      <c r="G242" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H242" s="2">
+        <v>302</v>
+      </c>
+      <c r="I242" s="1" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="243" customFormat="1" spans="1:9">
+      <c r="A243" s="1"/>
+      <c r="B243" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="C243" s="2">
+        <v>302</v>
+      </c>
+      <c r="D243" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="E243" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F243" s="1"/>
+      <c r="G243" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H243" s="2">
+        <v>302</v>
+      </c>
+      <c r="I243" s="1" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="244" customFormat="1" spans="1:9">
+      <c r="A244" s="1"/>
+      <c r="B244" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="C244" s="2">
+        <v>302</v>
+      </c>
+      <c r="D244" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="E244" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F244" s="1"/>
+      <c r="G244" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H244" s="2">
+        <v>302</v>
+      </c>
+      <c r="I244" s="1" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="245" customFormat="1" spans="1:9">
+      <c r="A245" s="1"/>
+      <c r="B245" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="C245" s="2">
+        <v>302</v>
+      </c>
+      <c r="D245" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="E245" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F245" s="1"/>
+      <c r="G245" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H245" s="2">
+        <v>302</v>
+      </c>
+      <c r="I245" s="1" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="247" customFormat="1" spans="1:9">
+      <c r="A247" s="1"/>
+      <c r="B247" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="C247" s="2">
+        <v>303</v>
+      </c>
+      <c r="D247" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="E247" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F247" s="1"/>
+      <c r="G247" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H247" s="2">
+        <v>303</v>
+      </c>
+      <c r="I247" s="1" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="248" customFormat="1" spans="1:9">
+      <c r="A248" s="1"/>
+      <c r="B248" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C248" s="2">
+        <v>303</v>
+      </c>
+      <c r="D248" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="E248" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F248" s="1"/>
+      <c r="G248" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H248" s="2">
+        <v>303</v>
+      </c>
+      <c r="I248" s="1" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="249" customFormat="1" spans="1:9">
+      <c r="A249" s="1"/>
+      <c r="B249" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C249" s="2">
+        <v>303</v>
+      </c>
+      <c r="D249" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="E249" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F249" s="1"/>
+      <c r="G249" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H249" s="2">
+        <v>303</v>
+      </c>
+      <c r="I249" s="1" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="250" customFormat="1" spans="1:9">
+      <c r="A250" s="1"/>
+      <c r="B250" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="C250" s="2">
+        <v>303</v>
+      </c>
+      <c r="D250" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="E250" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F250" s="1"/>
+      <c r="G250" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H250" s="2">
+        <v>303</v>
+      </c>
+      <c r="I250" s="1" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="251" customFormat="1" spans="1:9">
+      <c r="A251" s="1"/>
+      <c r="B251" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="C251" s="2">
+        <v>303</v>
+      </c>
+      <c r="D251" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="E251" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F251" s="1"/>
+      <c r="G251" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H251" s="2">
+        <v>303</v>
+      </c>
+      <c r="I251" s="1" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="252" customFormat="1" spans="1:9">
+      <c r="A252" s="1"/>
+      <c r="B252" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C252" s="2">
+        <v>303</v>
+      </c>
+      <c r="D252" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="E252" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F252" s="1"/>
+      <c r="G252" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H252" s="2">
+        <v>303</v>
+      </c>
+      <c r="I252" s="1" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="253" customFormat="1" spans="1:9">
+      <c r="A253" s="1"/>
+      <c r="B253" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="C253" s="2">
+        <v>303</v>
+      </c>
+      <c r="D253" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="E253" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F253" s="1"/>
+      <c r="G253" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H253" s="2">
+        <v>303</v>
+      </c>
+      <c r="I253" s="1" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="254" customFormat="1" spans="1:9">
+      <c r="A254" s="1"/>
+      <c r="B254" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="C254" s="2">
+        <v>303</v>
+      </c>
+      <c r="D254" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="E254" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F254" s="1"/>
+      <c r="G254" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H254" s="2">
+        <v>303</v>
+      </c>
+      <c r="I254" s="1" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="255" customFormat="1" spans="1:9">
+      <c r="A255" s="1"/>
+      <c r="B255" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="C255" s="2">
+        <v>303</v>
+      </c>
+      <c r="D255" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="E255" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F255" s="1"/>
+      <c r="G255" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H255" s="2">
+        <v>303</v>
+      </c>
+      <c r="I255" s="1" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="256" customFormat="1" spans="1:9">
+      <c r="A256" s="1"/>
+      <c r="B256" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="C256" s="2">
+        <v>303</v>
+      </c>
+      <c r="D256" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="E256" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F256" s="1"/>
+      <c r="G256" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H256" s="2">
+        <v>303</v>
+      </c>
+      <c r="I256" s="1" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="258" customFormat="1" spans="1:9">
+      <c r="A258" s="1"/>
+      <c r="B258" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="C258" s="2">
+        <v>304</v>
+      </c>
+      <c r="D258" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="E258" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F258" s="1"/>
+      <c r="G258" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H258" s="2">
+        <v>304</v>
+      </c>
+      <c r="I258" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="259" customFormat="1" spans="1:9">
+      <c r="A259" s="1"/>
+      <c r="B259" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="C259" s="2">
+        <v>304</v>
+      </c>
+      <c r="D259" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="E259" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F259" s="1"/>
+      <c r="G259" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H259" s="2">
+        <v>304</v>
+      </c>
+      <c r="I259" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="260" customFormat="1" spans="1:9">
+      <c r="A260" s="1"/>
+      <c r="B260" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="C260" s="2">
+        <v>304</v>
+      </c>
+      <c r="D260" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="E260" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F260" s="1"/>
+      <c r="G260" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H260" s="2">
+        <v>304</v>
+      </c>
+      <c r="I260" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="261" customFormat="1" spans="1:9">
+      <c r="A261" s="1"/>
+      <c r="B261" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="C261" s="2">
+        <v>304</v>
+      </c>
+      <c r="D261" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="E261" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F261" s="1"/>
+      <c r="G261" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H261" s="2">
+        <v>304</v>
+      </c>
+      <c r="I261" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="262" customFormat="1" spans="1:9">
+      <c r="A262" s="1"/>
+      <c r="B262" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C262" s="2">
+        <v>304</v>
+      </c>
+      <c r="D262" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="E262" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F262" s="1"/>
+      <c r="G262" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H262" s="2">
+        <v>304</v>
+      </c>
+      <c r="I262" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="263" customFormat="1" spans="1:9">
+      <c r="A263" s="1"/>
+      <c r="B263" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="C263" s="2">
+        <v>304</v>
+      </c>
+      <c r="D263" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="E263" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F263" s="1"/>
+      <c r="G263" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H263" s="2">
+        <v>304</v>
+      </c>
+      <c r="I263" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="264" customFormat="1" spans="1:9">
+      <c r="A264" s="1"/>
+      <c r="B264" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="C264" s="2">
+        <v>304</v>
+      </c>
+      <c r="D264" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="E264" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F264" s="1"/>
+      <c r="G264" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H264" s="2">
+        <v>304</v>
+      </c>
+      <c r="I264" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="265" customFormat="1" spans="1:9">
+      <c r="A265" s="1"/>
+      <c r="B265" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C265" s="2">
+        <v>304</v>
+      </c>
+      <c r="D265" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="E265" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F265" s="1"/>
+      <c r="G265" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H265" s="2">
+        <v>304</v>
+      </c>
+      <c r="I265" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="266" customFormat="1" spans="1:9">
+      <c r="A266" s="1"/>
+      <c r="B266" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="C266" s="2">
+        <v>304</v>
+      </c>
+      <c r="D266" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="E266" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F266" s="1"/>
+      <c r="G266" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H266" s="2">
+        <v>304</v>
+      </c>
+      <c r="I266" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="267" customFormat="1" spans="1:9">
+      <c r="A267" s="1"/>
+      <c r="B267" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="C267" s="2">
+        <v>304</v>
+      </c>
+      <c r="D267" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="E267" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F267" s="1"/>
+      <c r="G267" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H267" s="2">
+        <v>304</v>
+      </c>
+      <c r="I267" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9">
+      <c r="I268"/>
+    </row>
+    <row r="269" customFormat="1" spans="1:9">
+      <c r="A269" s="1"/>
+      <c r="B269" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C269" s="2">
+        <v>305</v>
+      </c>
+      <c r="D269" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="E269" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F269" s="1"/>
+      <c r="G269" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H269" s="2">
+        <v>305</v>
+      </c>
+      <c r="I269" s="1" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="270" customFormat="1" spans="1:9">
+      <c r="A270" s="1"/>
+      <c r="B270" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="C270" s="2">
+        <v>305</v>
+      </c>
+      <c r="D270" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="E270" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F270" s="1"/>
+      <c r="G270" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H270" s="2">
+        <v>305</v>
+      </c>
+      <c r="I270" s="1" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="271" customFormat="1" spans="1:9">
+      <c r="A271" s="1"/>
+      <c r="B271" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="C271" s="2">
+        <v>305</v>
+      </c>
+      <c r="D271" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="E271" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F271" s="1"/>
+      <c r="G271" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H271" s="2">
+        <v>305</v>
+      </c>
+      <c r="I271" s="1" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="272" customFormat="1" spans="1:9">
+      <c r="A272" s="1"/>
+      <c r="B272" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="C272" s="2">
+        <v>305</v>
+      </c>
+      <c r="D272" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="E272" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F272" s="1"/>
+      <c r="G272" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H272" s="2">
+        <v>305</v>
+      </c>
+      <c r="I272" s="1" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="273" customFormat="1" spans="1:9">
+      <c r="A273" s="1"/>
+      <c r="B273" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="C273" s="2">
+        <v>305</v>
+      </c>
+      <c r="D273" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="E273" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F273" s="1"/>
+      <c r="G273" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H273" s="2">
+        <v>305</v>
+      </c>
+      <c r="I273" s="1" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="274" customFormat="1" spans="1:9">
+      <c r="A274" s="1"/>
+      <c r="B274" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C274" s="2">
+        <v>305</v>
+      </c>
+      <c r="D274" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="E274" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F274" s="1"/>
+      <c r="G274" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H274" s="2">
+        <v>305</v>
+      </c>
+      <c r="I274" s="1" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="275" customFormat="1" spans="1:9">
+      <c r="A275" s="1"/>
+      <c r="B275" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="C275" s="2">
+        <v>305</v>
+      </c>
+      <c r="D275" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="E275" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F275" s="1"/>
+      <c r="G275" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H275" s="2">
+        <v>305</v>
+      </c>
+      <c r="I275" s="1" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="276" customFormat="1" spans="1:9">
+      <c r="A276" s="1"/>
+      <c r="B276" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="C276" s="2">
+        <v>305</v>
+      </c>
+      <c r="D276" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="E276" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F276" s="1"/>
+      <c r="G276" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H276" s="2">
+        <v>305</v>
+      </c>
+      <c r="I276" s="1" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="277" customFormat="1" spans="1:9">
+      <c r="A277" s="1"/>
+      <c r="B277" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="C277" s="2">
+        <v>305</v>
+      </c>
+      <c r="D277" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="E277" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F277" s="1"/>
+      <c r="G277" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H277" s="2">
+        <v>305</v>
+      </c>
+      <c r="I277" s="1" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="278" customFormat="1" spans="1:9">
+      <c r="A278" s="1"/>
+      <c r="B278" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="C278" s="2">
+        <v>305</v>
+      </c>
+      <c r="D278" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="E278" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F278" s="1"/>
+      <c r="G278" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H278" s="2">
+        <v>305</v>
+      </c>
+      <c r="I278" s="1" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="280" customFormat="1" spans="1:9">
+      <c r="A280" s="1"/>
+      <c r="B280" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="C280" s="2">
+        <v>306</v>
+      </c>
+      <c r="D280" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="E280" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F280" s="1"/>
+      <c r="G280" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H280" s="2">
+        <v>306</v>
+      </c>
+      <c r="I280" s="1" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="281" customFormat="1" spans="1:9">
+      <c r="A281" s="1"/>
+      <c r="B281" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="C281" s="2">
+        <v>306</v>
+      </c>
+      <c r="D281" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="E281" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F281" s="1"/>
+      <c r="G281" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H281" s="2">
+        <v>306</v>
+      </c>
+      <c r="I281" s="1" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="282" customFormat="1" spans="1:9">
+      <c r="A282" s="1"/>
+      <c r="B282" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="C282" s="2">
+        <v>306</v>
+      </c>
+      <c r="D282" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="E282" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F282" s="1"/>
+      <c r="G282" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H282" s="2">
+        <v>306</v>
+      </c>
+      <c r="I282" s="1" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="283" customFormat="1" spans="1:9">
+      <c r="A283" s="1"/>
+      <c r="B283" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="C283" s="2">
+        <v>306</v>
+      </c>
+      <c r="D283" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="E283" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F283" s="1"/>
+      <c r="G283" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H283" s="2">
+        <v>306</v>
+      </c>
+      <c r="I283" s="1" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="284" customFormat="1" spans="1:9">
+      <c r="A284" s="1"/>
+      <c r="B284" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="C284" s="2">
+        <v>306</v>
+      </c>
+      <c r="D284" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="E284" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F284" s="1"/>
+      <c r="G284" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H284" s="2">
+        <v>306</v>
+      </c>
+      <c r="I284" s="1" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="285" customFormat="1" spans="1:9">
+      <c r="A285" s="1"/>
+      <c r="B285" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="C285" s="2">
+        <v>306</v>
+      </c>
+      <c r="D285" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="E285" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F285" s="1"/>
+      <c r="G285" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H285" s="2">
+        <v>306</v>
+      </c>
+      <c r="I285" s="1" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="286" customFormat="1" spans="1:9">
+      <c r="A286" s="1"/>
+      <c r="B286" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="C286" s="2">
+        <v>306</v>
+      </c>
+      <c r="D286" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="E286" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F286" s="1"/>
+      <c r="G286" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H286" s="2">
+        <v>306</v>
+      </c>
+      <c r="I286" s="1" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="287" customFormat="1" spans="1:9">
+      <c r="A287" s="1"/>
+      <c r="B287" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="C287" s="2">
+        <v>306</v>
+      </c>
+      <c r="D287" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="E287" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F287" s="1"/>
+      <c r="G287" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H287" s="2">
+        <v>306</v>
+      </c>
+      <c r="I287" s="1" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="288" customFormat="1" spans="1:9">
+      <c r="A288" s="1"/>
+      <c r="B288" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="C288" s="2">
+        <v>306</v>
+      </c>
+      <c r="D288" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="E288" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F288" s="1"/>
+      <c r="G288" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H288" s="2">
+        <v>306</v>
+      </c>
+      <c r="I288" s="1" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="289" customFormat="1" spans="1:9">
+      <c r="A289" s="1"/>
+      <c r="B289" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="C289" s="2">
+        <v>306</v>
+      </c>
+      <c r="D289" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="E289" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F289" s="1"/>
+      <c r="G289" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H289" s="2">
+        <v>306</v>
+      </c>
+      <c r="I289" s="1" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="291" customFormat="1" spans="1:9">
+      <c r="A291" s="1"/>
+      <c r="B291" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="C291" s="2">
+        <v>307</v>
+      </c>
+      <c r="D291" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="E291" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F291" s="1"/>
+      <c r="G291" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H291" s="2">
+        <v>307</v>
+      </c>
+      <c r="I291" s="1" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="292" customFormat="1" spans="1:9">
+      <c r="A292" s="1"/>
+      <c r="B292" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="C292" s="2">
+        <v>307</v>
+      </c>
+      <c r="D292" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="E292" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F292" s="1"/>
+      <c r="G292" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H292" s="2">
+        <v>307</v>
+      </c>
+      <c r="I292" s="1" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="293" customFormat="1" spans="1:9">
+      <c r="A293" s="1"/>
+      <c r="B293" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="C293" s="2">
+        <v>307</v>
+      </c>
+      <c r="D293" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="E293" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F293" s="1"/>
+      <c r="G293" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H293" s="2">
+        <v>307</v>
+      </c>
+      <c r="I293" s="1" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="294" customFormat="1" spans="1:9">
+      <c r="A294" s="1"/>
+      <c r="B294" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="C294" s="2">
+        <v>307</v>
+      </c>
+      <c r="D294" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="E294" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F294" s="1"/>
+      <c r="G294" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H294" s="2">
+        <v>307</v>
+      </c>
+      <c r="I294" s="1" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="295" customFormat="1" spans="1:9">
+      <c r="A295" s="1"/>
+      <c r="B295" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="C295" s="2">
+        <v>307</v>
+      </c>
+      <c r="D295" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="E295" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F295" s="1"/>
+      <c r="G295" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H295" s="2">
+        <v>307</v>
+      </c>
+      <c r="I295" s="1" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="296" customFormat="1" spans="1:9">
+      <c r="A296" s="1"/>
+      <c r="B296" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="C296" s="2">
+        <v>307</v>
+      </c>
+      <c r="D296" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="E296" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F296" s="1"/>
+      <c r="G296" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H296" s="2">
+        <v>307</v>
+      </c>
+      <c r="I296" s="1" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="297" customFormat="1" spans="1:9">
+      <c r="A297" s="1"/>
+      <c r="B297" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="C297" s="2">
+        <v>307</v>
+      </c>
+      <c r="D297" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="E297" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F297" s="1"/>
+      <c r="G297" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H297" s="2">
+        <v>307</v>
+      </c>
+      <c r="I297" s="1" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="298" customFormat="1" spans="1:9">
+      <c r="A298" s="1"/>
+      <c r="B298" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="C298" s="2">
+        <v>307</v>
+      </c>
+      <c r="D298" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="E298" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F298" s="1"/>
+      <c r="G298" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H298" s="2">
+        <v>307</v>
+      </c>
+      <c r="I298" s="1" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="299" customFormat="1" spans="1:9">
+      <c r="A299" s="1"/>
+      <c r="B299" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="C299" s="2">
+        <v>307</v>
+      </c>
+      <c r="D299" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="E299" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F299" s="1"/>
+      <c r="G299" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H299" s="2">
+        <v>307</v>
+      </c>
+      <c r="I299" s="1" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="300" customFormat="1" spans="1:9">
+      <c r="A300" s="1"/>
+      <c r="B300" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="C300" s="2">
+        <v>307</v>
+      </c>
+      <c r="D300" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="E300" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F300" s="1"/>
+      <c r="G300" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H300" s="2">
+        <v>307</v>
+      </c>
+      <c r="I300" s="1" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="302" customFormat="1" spans="1:9">
+      <c r="A302" s="1"/>
+      <c r="B302" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="C302" s="2">
+        <v>308</v>
+      </c>
+      <c r="D302" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="E302" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F302" s="1"/>
+      <c r="G302" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H302" s="2">
+        <v>308</v>
+      </c>
+      <c r="I302" s="1" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="303" customFormat="1" spans="1:9">
+      <c r="A303" s="1"/>
+      <c r="B303" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="C303" s="2">
+        <v>308</v>
+      </c>
+      <c r="D303" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="E303" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F303" s="1"/>
+      <c r="G303" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H303" s="2">
+        <v>308</v>
+      </c>
+      <c r="I303" s="1" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="304" customFormat="1" spans="1:9">
+      <c r="A304" s="1"/>
+      <c r="B304" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="C304" s="2">
+        <v>308</v>
+      </c>
+      <c r="D304" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="E304" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F304" s="1"/>
+      <c r="G304" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H304" s="2">
+        <v>308</v>
+      </c>
+      <c r="I304" s="1" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="305" customFormat="1" spans="1:9">
+      <c r="A305" s="1"/>
+      <c r="B305" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="C305" s="2">
+        <v>308</v>
+      </c>
+      <c r="D305" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="E305" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F305" s="1"/>
+      <c r="G305" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H305" s="2">
+        <v>308</v>
+      </c>
+      <c r="I305" s="1" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="306" customFormat="1" spans="1:9">
+      <c r="A306" s="1"/>
+      <c r="B306" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="C306" s="2">
+        <v>308</v>
+      </c>
+      <c r="D306" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="E306" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F306" s="1"/>
+      <c r="G306" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H306" s="2">
+        <v>308</v>
+      </c>
+      <c r="I306" s="1" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="307" customFormat="1" spans="1:9">
+      <c r="A307" s="1"/>
+      <c r="B307" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="C307" s="2">
+        <v>308</v>
+      </c>
+      <c r="D307" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="E307" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F307" s="1"/>
+      <c r="G307" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H307" s="2">
+        <v>308</v>
+      </c>
+      <c r="I307" s="1" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="308" customFormat="1" spans="1:9">
+      <c r="A308" s="1"/>
+      <c r="B308" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="C308" s="2">
+        <v>308</v>
+      </c>
+      <c r="D308" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="E308" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F308" s="1"/>
+      <c r="G308" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H308" s="2">
+        <v>308</v>
+      </c>
+      <c r="I308" s="1" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="309" customFormat="1" spans="1:9">
+      <c r="A309" s="1"/>
+      <c r="B309" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="C309" s="2">
+        <v>308</v>
+      </c>
+      <c r="D309" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="E309" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F309" s="1"/>
+      <c r="G309" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H309" s="2">
+        <v>308</v>
+      </c>
+      <c r="I309" s="1" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="310" customFormat="1" spans="1:9">
+      <c r="A310" s="1"/>
+      <c r="B310" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="C310" s="2">
+        <v>308</v>
+      </c>
+      <c r="D310" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="E310" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F310" s="1"/>
+      <c r="G310" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H310" s="2">
+        <v>308</v>
+      </c>
+      <c r="I310" s="1" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="311" customFormat="1" spans="1:9">
+      <c r="A311" s="1"/>
+      <c r="B311" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="C311" s="2">
+        <v>308</v>
+      </c>
+      <c r="D311" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="E311" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F311" s="1"/>
+      <c r="G311" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H311" s="2">
+        <v>308</v>
+      </c>
+      <c r="I311" s="1" t="s">
+        <v>625</v>
       </c>
     </row>
   </sheetData>

--- a/Config/TalentConfig.xlsx
+++ b/Config/TalentConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="14010" windowHeight="10905"/>
+    <workbookView windowWidth="10875" windowHeight="9750"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>

--- a/Config/TalentConfig.xlsx
+++ b/Config/TalentConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="14175" windowHeight="10740"/>
+    <workbookView windowWidth="8205" windowHeight="10740"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1940" uniqueCount="695">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2120" uniqueCount="713">
   <si>
     <t>##var</t>
   </si>
@@ -727,6 +727,9 @@
     <t>结实</t>
   </si>
   <si>
+    <t>Sturdy</t>
+  </si>
+  <si>
     <t>英雄的生命值上限+4</t>
   </si>
   <si>
@@ -790,6 +793,9 @@
     <t>铜墙铁壁</t>
   </si>
   <si>
+    <t>IronWall</t>
+  </si>
+  <si>
     <t>受到的伤害降低1点</t>
   </si>
   <si>
@@ -853,6 +859,9 @@
     <t>强壮</t>
   </si>
   <si>
+    <t>Strong</t>
+  </si>
+  <si>
     <t>英雄的基础攻击力+1</t>
   </si>
   <si>
@@ -922,6 +931,9 @@
     <t>0.4</t>
   </si>
   <si>
+    <t>HeadMastery</t>
+  </si>
+  <si>
     <t>人头牌提供的攻击力+1</t>
   </si>
   <si>
@@ -985,6 +997,9 @@
     <t>强力打击</t>
   </si>
   <si>
+    <t>PowerStrike</t>
+  </si>
+  <si>
     <t>英雄暴击率+0.5%</t>
   </si>
   <si>
@@ -1048,6 +1063,9 @@
     <t>巨人杀手</t>
   </si>
   <si>
+    <t>GiantKiller</t>
+  </si>
+  <si>
     <t>对BOSS的伤害+0.5%</t>
   </si>
   <si>
@@ -1111,6 +1129,9 @@
     <t>好兆头</t>
   </si>
   <si>
+    <t>GoodOmen</t>
+  </si>
+  <si>
     <t>每关的首次亮牌,倍率+0.2</t>
   </si>
   <si>
@@ -1174,6 +1195,9 @@
     <t>侩子手</t>
   </si>
   <si>
+    <t>Executioner</t>
+  </si>
+  <si>
     <t>攻击血量低于10%的非BOSS敌人时,有0.5%概率斩杀</t>
   </si>
   <si>
@@ -1237,6 +1261,9 @@
     <t>逢凶化吉</t>
   </si>
   <si>
+    <t>AvoidMisfortune</t>
+  </si>
+  <si>
     <t>当血量低于20%以下时,击杀敌人会回复0.5%的血量</t>
   </si>
   <si>
@@ -1300,6 +1327,9 @@
     <t>人多势众</t>
   </si>
   <si>
+    <t>NumerousMight</t>
+  </si>
+  <si>
     <t>当敌人数量大于1时,造成的伤害+0.5%</t>
   </si>
   <si>
@@ -1363,6 +1393,9 @@
     <t>搓牌高手</t>
   </si>
   <si>
+    <t>CardShuffleMaster</t>
+  </si>
+  <si>
     <t>亮牌前,只要使用过搓牌,结算时就提供1点攻击力</t>
   </si>
   <si>
@@ -1495,6 +1528,9 @@
     <t>0.2</t>
   </si>
   <si>
+    <t>Reply</t>
+  </si>
+  <si>
     <t>每回结束后,回复0.5%的血量</t>
   </si>
   <si>
@@ -1558,6 +1594,9 @@
     <t>资本家</t>
   </si>
   <si>
+    <t>Capitalist</t>
+  </si>
+  <si>
     <t>每回合结算时,有1%概率获得1资金</t>
   </si>
   <si>
@@ -1684,6 +1723,9 @@
     <t>孤立无援</t>
   </si>
   <si>
+    <t>IsolatedHelpless</t>
+  </si>
+  <si>
     <t>只剩下1名敌人时,对其造成的伤害+0.5%</t>
   </si>
   <si>
@@ -1747,6 +1789,9 @@
     <t>触底反弹</t>
   </si>
   <si>
+    <t>BottomBounce</t>
+  </si>
+  <si>
     <t>当血量低于20%以下时,造成的伤害+0.5%</t>
   </si>
   <si>
@@ -1810,6 +1855,9 @@
     <t>点金手</t>
   </si>
   <si>
+    <t>GoldenTouch</t>
+  </si>
+  <si>
     <t>击杀敌人时,有1%概率获得1资金</t>
   </si>
   <si>
@@ -1873,6 +1921,9 @@
     <t>富裕</t>
   </si>
   <si>
+    <t>Wealthy</t>
+  </si>
+  <si>
     <t>初始拥有1资金</t>
   </si>
   <si>
@@ -1934,6 +1985,9 @@
   </si>
   <si>
     <t>追击</t>
+  </si>
+  <si>
+    <t>Pursuit</t>
   </si>
   <si>
     <t>攻击敌人时,有1%概率额外造成1次原伤害10%的攻击</t>
@@ -3114,7 +3168,7 @@
     <col min="4" max="4" width="8.03333333333333" style="3" customWidth="1"/>
     <col min="5" max="5" width="11.6166666666667" style="3" customWidth="1"/>
     <col min="6" max="6" width="5.43333333333333" style="3" customWidth="1"/>
-    <col min="7" max="7" width="6.3" style="3" customWidth="1"/>
+    <col min="7" max="7" width="7.825" style="3" customWidth="1"/>
     <col min="8" max="8" width="11.5083333333333" style="3" customWidth="1"/>
     <col min="9" max="9" width="12.4916666666667" style="3" customWidth="1"/>
     <col min="10" max="10" width="22.0666666666667" style="3" customWidth="1"/>
@@ -5766,7 +5820,9 @@
       <c r="F104" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G104" s="3"/>
+      <c r="G104" s="3" t="s">
+        <v>231</v>
+      </c>
       <c r="H104" s="3" t="s">
         <v>27</v>
       </c>
@@ -5774,13 +5830,13 @@
         <v>110</v>
       </c>
       <c r="J104" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="105" customFormat="1" spans="1:10">
       <c r="A105" s="3"/>
       <c r="B105" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C105" s="4">
         <v>110</v>
@@ -5794,7 +5850,9 @@
       <c r="F105" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G105" s="3"/>
+      <c r="G105" s="3" t="s">
+        <v>231</v>
+      </c>
       <c r="H105" s="3" t="s">
         <v>31</v>
       </c>
@@ -5802,13 +5860,13 @@
         <v>110</v>
       </c>
       <c r="J105" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="106" customFormat="1" spans="1:10">
       <c r="A106" s="3"/>
       <c r="B106" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C106" s="4">
         <v>110</v>
@@ -5822,7 +5880,9 @@
       <c r="F106" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G106" s="3"/>
+      <c r="G106" s="3" t="s">
+        <v>231</v>
+      </c>
       <c r="H106" s="3" t="s">
         <v>34</v>
       </c>
@@ -5830,13 +5890,13 @@
         <v>110</v>
       </c>
       <c r="J106" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="107" customFormat="1" spans="1:10">
       <c r="A107" s="3"/>
       <c r="B107" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C107" s="4">
         <v>110</v>
@@ -5850,7 +5910,9 @@
       <c r="F107" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G107" s="3"/>
+      <c r="G107" s="3" t="s">
+        <v>231</v>
+      </c>
       <c r="H107" s="3" t="s">
         <v>37</v>
       </c>
@@ -5858,13 +5920,13 @@
         <v>110</v>
       </c>
       <c r="J107" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="108" customFormat="1" spans="1:10">
       <c r="A108" s="3"/>
       <c r="B108" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C108" s="4">
         <v>110</v>
@@ -5878,7 +5940,9 @@
       <c r="F108" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G108" s="3"/>
+      <c r="G108" s="3" t="s">
+        <v>231</v>
+      </c>
       <c r="H108" s="3" t="s">
         <v>40</v>
       </c>
@@ -5886,13 +5950,13 @@
         <v>110</v>
       </c>
       <c r="J108" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="109" customFormat="1" spans="1:10">
       <c r="A109" s="3"/>
       <c r="B109" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C109" s="4">
         <v>110</v>
@@ -5906,7 +5970,9 @@
       <c r="F109" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G109" s="3"/>
+      <c r="G109" s="3" t="s">
+        <v>231</v>
+      </c>
       <c r="H109" s="3" t="s">
         <v>43</v>
       </c>
@@ -5914,13 +5980,13 @@
         <v>110</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="110" customFormat="1" spans="1:10">
       <c r="A110" s="3"/>
       <c r="B110" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C110" s="4">
         <v>110</v>
@@ -5934,7 +6000,9 @@
       <c r="F110" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G110" s="3"/>
+      <c r="G110" s="3" t="s">
+        <v>231</v>
+      </c>
       <c r="H110" s="3" t="s">
         <v>46</v>
       </c>
@@ -5942,13 +6010,13 @@
         <v>110</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="111" customFormat="1" spans="1:10">
       <c r="A111" s="3"/>
       <c r="B111" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C111" s="4">
         <v>110</v>
@@ -5962,7 +6030,9 @@
       <c r="F111" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G111" s="3"/>
+      <c r="G111" s="3" t="s">
+        <v>231</v>
+      </c>
       <c r="H111" s="3" t="s">
         <v>49</v>
       </c>
@@ -5970,13 +6040,13 @@
         <v>110</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="112" customFormat="1" spans="1:10">
       <c r="A112" s="3"/>
       <c r="B112" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C112" s="4">
         <v>110</v>
@@ -5990,7 +6060,9 @@
       <c r="F112" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G112" s="3"/>
+      <c r="G112" s="3" t="s">
+        <v>231</v>
+      </c>
       <c r="H112" s="3" t="s">
         <v>52</v>
       </c>
@@ -5998,13 +6070,13 @@
         <v>110</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="113" customFormat="1" spans="1:10">
       <c r="A113" s="3"/>
       <c r="B113" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C113" s="4">
         <v>110</v>
@@ -6018,7 +6090,9 @@
       <c r="F113" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G113" s="3"/>
+      <c r="G113" s="3" t="s">
+        <v>231</v>
+      </c>
       <c r="H113" s="3" t="s">
         <v>55</v>
       </c>
@@ -6026,19 +6100,19 @@
         <v>110</v>
       </c>
       <c r="J113" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="115" customFormat="1" spans="1:10">
       <c r="A115" s="3"/>
       <c r="B115" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C115" s="4">
         <v>111</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E115" s="3" t="s">
         <v>25</v>
@@ -6046,7 +6120,9 @@
       <c r="F115" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G115" s="3"/>
+      <c r="G115" s="3" t="s">
+        <v>253</v>
+      </c>
       <c r="H115" s="3" t="s">
         <v>27</v>
       </c>
@@ -6054,19 +6130,19 @@
         <v>111</v>
       </c>
       <c r="J115" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="116" customFormat="1" spans="1:10">
       <c r="A116" s="3"/>
       <c r="B116" s="3" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C116" s="4">
         <v>111</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E116" s="3" t="s">
         <v>25</v>
@@ -6074,7 +6150,9 @@
       <c r="F116" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G116" s="3"/>
+      <c r="G116" s="3" t="s">
+        <v>253</v>
+      </c>
       <c r="H116" s="3" t="s">
         <v>31</v>
       </c>
@@ -6082,19 +6160,19 @@
         <v>111</v>
       </c>
       <c r="J116" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="117" customFormat="1" spans="1:10">
       <c r="A117" s="3"/>
       <c r="B117" s="3" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C117" s="4">
         <v>111</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E117" s="3" t="s">
         <v>25</v>
@@ -6102,7 +6180,9 @@
       <c r="F117" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G117" s="3"/>
+      <c r="G117" s="3" t="s">
+        <v>253</v>
+      </c>
       <c r="H117" s="3" t="s">
         <v>34</v>
       </c>
@@ -6110,19 +6190,19 @@
         <v>111</v>
       </c>
       <c r="J117" s="3" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="118" customFormat="1" spans="1:10">
       <c r="A118" s="3"/>
       <c r="B118" s="3" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C118" s="4">
         <v>111</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E118" s="3" t="s">
         <v>25</v>
@@ -6130,7 +6210,9 @@
       <c r="F118" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G118" s="3"/>
+      <c r="G118" s="3" t="s">
+        <v>253</v>
+      </c>
       <c r="H118" s="3" t="s">
         <v>37</v>
       </c>
@@ -6138,19 +6220,19 @@
         <v>111</v>
       </c>
       <c r="J118" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="119" customFormat="1" spans="1:10">
       <c r="A119" s="3"/>
       <c r="B119" s="3" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C119" s="4">
         <v>111</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E119" s="3" t="s">
         <v>25</v>
@@ -6158,7 +6240,9 @@
       <c r="F119" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G119" s="3"/>
+      <c r="G119" s="3" t="s">
+        <v>253</v>
+      </c>
       <c r="H119" s="3" t="s">
         <v>40</v>
       </c>
@@ -6166,19 +6250,19 @@
         <v>111</v>
       </c>
       <c r="J119" s="3" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="120" customFormat="1" spans="1:10">
       <c r="A120" s="3"/>
       <c r="B120" s="3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C120" s="4">
         <v>111</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E120" s="3" t="s">
         <v>25</v>
@@ -6186,7 +6270,9 @@
       <c r="F120" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G120" s="3"/>
+      <c r="G120" s="3" t="s">
+        <v>253</v>
+      </c>
       <c r="H120" s="3" t="s">
         <v>43</v>
       </c>
@@ -6194,19 +6280,19 @@
         <v>111</v>
       </c>
       <c r="J120" s="3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="121" customFormat="1" spans="1:10">
       <c r="A121" s="3"/>
       <c r="B121" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C121" s="4">
         <v>111</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E121" s="3" t="s">
         <v>25</v>
@@ -6214,7 +6300,9 @@
       <c r="F121" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G121" s="3"/>
+      <c r="G121" s="3" t="s">
+        <v>253</v>
+      </c>
       <c r="H121" s="3" t="s">
         <v>46</v>
       </c>
@@ -6222,19 +6310,19 @@
         <v>111</v>
       </c>
       <c r="J121" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="122" customFormat="1" spans="1:10">
       <c r="A122" s="3"/>
       <c r="B122" s="3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C122" s="4">
         <v>111</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E122" s="3" t="s">
         <v>25</v>
@@ -6242,7 +6330,9 @@
       <c r="F122" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G122" s="3"/>
+      <c r="G122" s="3" t="s">
+        <v>253</v>
+      </c>
       <c r="H122" s="3" t="s">
         <v>49</v>
       </c>
@@ -6250,19 +6340,19 @@
         <v>111</v>
       </c>
       <c r="J122" s="3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="123" customFormat="1" spans="1:10">
       <c r="A123" s="3"/>
       <c r="B123" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C123" s="4">
         <v>111</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E123" s="3" t="s">
         <v>25</v>
@@ -6270,7 +6360,9 @@
       <c r="F123" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G123" s="3"/>
+      <c r="G123" s="3" t="s">
+        <v>253</v>
+      </c>
       <c r="H123" s="3" t="s">
         <v>52</v>
       </c>
@@ -6278,19 +6370,19 @@
         <v>111</v>
       </c>
       <c r="J123" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="124" customFormat="1" spans="1:10">
       <c r="A124" s="3"/>
       <c r="B124" s="3" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C124" s="4">
         <v>111</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E124" s="3" t="s">
         <v>25</v>
@@ -6298,7 +6390,9 @@
       <c r="F124" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G124" s="3"/>
+      <c r="G124" s="3" t="s">
+        <v>253</v>
+      </c>
       <c r="H124" s="3" t="s">
         <v>55</v>
       </c>
@@ -6306,19 +6400,19 @@
         <v>111</v>
       </c>
       <c r="J124" s="3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="126" customFormat="1" spans="1:10">
       <c r="A126" s="3"/>
       <c r="B126" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C126" s="4">
         <v>112</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E126" s="3" t="s">
         <v>25</v>
@@ -6326,7 +6420,9 @@
       <c r="F126" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G126" s="3"/>
+      <c r="G126" s="3" t="s">
+        <v>275</v>
+      </c>
       <c r="H126" s="3" t="s">
         <v>27</v>
       </c>
@@ -6334,19 +6430,19 @@
         <v>112</v>
       </c>
       <c r="J126" s="3" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="127" customFormat="1" spans="1:10">
       <c r="A127" s="3"/>
       <c r="B127" s="3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C127" s="4">
         <v>112</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E127" s="3" t="s">
         <v>25</v>
@@ -6354,7 +6450,9 @@
       <c r="F127" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G127" s="3"/>
+      <c r="G127" s="3" t="s">
+        <v>275</v>
+      </c>
       <c r="H127" s="3" t="s">
         <v>31</v>
       </c>
@@ -6362,19 +6460,19 @@
         <v>112</v>
       </c>
       <c r="J127" s="3" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="128" customFormat="1" spans="1:10">
       <c r="A128" s="3"/>
       <c r="B128" s="3" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C128" s="4">
         <v>112</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E128" s="3" t="s">
         <v>25</v>
@@ -6382,7 +6480,9 @@
       <c r="F128" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G128" s="3"/>
+      <c r="G128" s="3" t="s">
+        <v>275</v>
+      </c>
       <c r="H128" s="3" t="s">
         <v>34</v>
       </c>
@@ -6390,19 +6490,19 @@
         <v>112</v>
       </c>
       <c r="J128" s="3" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="129" customFormat="1" spans="1:10">
       <c r="A129" s="3"/>
       <c r="B129" s="3" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C129" s="4">
         <v>112</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E129" s="3" t="s">
         <v>25</v>
@@ -6410,7 +6510,9 @@
       <c r="F129" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G129" s="3"/>
+      <c r="G129" s="3" t="s">
+        <v>275</v>
+      </c>
       <c r="H129" s="3" t="s">
         <v>37</v>
       </c>
@@ -6418,19 +6520,19 @@
         <v>112</v>
       </c>
       <c r="J129" s="3" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="130" customFormat="1" spans="1:10">
       <c r="A130" s="3"/>
       <c r="B130" s="3" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C130" s="4">
         <v>112</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E130" s="3" t="s">
         <v>25</v>
@@ -6438,7 +6540,9 @@
       <c r="F130" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G130" s="3"/>
+      <c r="G130" s="3" t="s">
+        <v>275</v>
+      </c>
       <c r="H130" s="3" t="s">
         <v>40</v>
       </c>
@@ -6446,19 +6550,19 @@
         <v>112</v>
       </c>
       <c r="J130" s="3" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="131" customFormat="1" spans="1:10">
       <c r="A131" s="3"/>
       <c r="B131" s="3" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C131" s="4">
         <v>112</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E131" s="3" t="s">
         <v>25</v>
@@ -6466,7 +6570,9 @@
       <c r="F131" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G131" s="3"/>
+      <c r="G131" s="3" t="s">
+        <v>275</v>
+      </c>
       <c r="H131" s="3" t="s">
         <v>43</v>
       </c>
@@ -6474,19 +6580,19 @@
         <v>112</v>
       </c>
       <c r="J131" s="3" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="132" customFormat="1" spans="1:10">
       <c r="A132" s="3"/>
       <c r="B132" s="3" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C132" s="4">
         <v>112</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E132" s="3" t="s">
         <v>25</v>
@@ -6494,7 +6600,9 @@
       <c r="F132" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G132" s="3"/>
+      <c r="G132" s="3" t="s">
+        <v>275</v>
+      </c>
       <c r="H132" s="3" t="s">
         <v>46</v>
       </c>
@@ -6502,19 +6610,19 @@
         <v>112</v>
       </c>
       <c r="J132" s="3" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="133" customFormat="1" spans="1:10">
       <c r="A133" s="3"/>
       <c r="B133" s="3" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C133" s="4">
         <v>112</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E133" s="3" t="s">
         <v>25</v>
@@ -6522,7 +6630,9 @@
       <c r="F133" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G133" s="3"/>
+      <c r="G133" s="3" t="s">
+        <v>275</v>
+      </c>
       <c r="H133" s="3" t="s">
         <v>49</v>
       </c>
@@ -6530,19 +6640,19 @@
         <v>112</v>
       </c>
       <c r="J133" s="3" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="134" customFormat="1" spans="1:10">
       <c r="A134" s="3"/>
       <c r="B134" s="3" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C134" s="4">
         <v>112</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E134" s="3" t="s">
         <v>25</v>
@@ -6550,7 +6660,9 @@
       <c r="F134" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G134" s="3"/>
+      <c r="G134" s="3" t="s">
+        <v>275</v>
+      </c>
       <c r="H134" s="3" t="s">
         <v>52</v>
       </c>
@@ -6558,19 +6670,19 @@
         <v>112</v>
       </c>
       <c r="J134" s="3" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="135" customFormat="1" spans="1:10">
       <c r="A135" s="3"/>
       <c r="B135" s="3" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C135" s="4">
         <v>112</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E135" s="3" t="s">
         <v>25</v>
@@ -6578,7 +6690,9 @@
       <c r="F135" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G135" s="3"/>
+      <c r="G135" s="3" t="s">
+        <v>275</v>
+      </c>
       <c r="H135" s="3" t="s">
         <v>55</v>
       </c>
@@ -6586,27 +6700,29 @@
         <v>112</v>
       </c>
       <c r="J135" s="3" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="137" customFormat="1" spans="1:10">
       <c r="A137" s="3"/>
       <c r="B137" s="3" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C137" s="4">
         <v>201</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G137" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G137" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="H137" s="3" t="s">
         <v>27</v>
       </c>
@@ -6614,27 +6730,29 @@
         <v>201</v>
       </c>
       <c r="J137" s="3" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="138" customFormat="1" spans="1:10">
       <c r="A138" s="3"/>
       <c r="B138" s="3" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C138" s="4">
         <v>201</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G138" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G138" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="H138" s="3" t="s">
         <v>31</v>
       </c>
@@ -6642,27 +6760,29 @@
         <v>201</v>
       </c>
       <c r="J138" s="3" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="139" customFormat="1" spans="1:10">
       <c r="A139" s="3"/>
       <c r="B139" s="3" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="C139" s="4">
         <v>201</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G139" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G139" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="H139" s="3" t="s">
         <v>34</v>
       </c>
@@ -6670,27 +6790,29 @@
         <v>201</v>
       </c>
       <c r="J139" s="3" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="140" customFormat="1" spans="1:10">
       <c r="A140" s="3"/>
       <c r="B140" s="3" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C140" s="4">
         <v>201</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G140" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G140" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="H140" s="3" t="s">
         <v>37</v>
       </c>
@@ -6698,27 +6820,29 @@
         <v>201</v>
       </c>
       <c r="J140" s="3" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="141" customFormat="1" spans="1:10">
       <c r="A141" s="3"/>
       <c r="B141" s="3" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C141" s="4">
         <v>201</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G141" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G141" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="H141" s="3" t="s">
         <v>40</v>
       </c>
@@ -6726,27 +6850,29 @@
         <v>201</v>
       </c>
       <c r="J141" s="3" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="142" customFormat="1" spans="1:10">
       <c r="A142" s="3"/>
       <c r="B142" s="3" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C142" s="4">
         <v>201</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G142" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G142" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="H142" s="3" t="s">
         <v>43</v>
       </c>
@@ -6754,27 +6880,29 @@
         <v>201</v>
       </c>
       <c r="J142" s="3" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="143" customFormat="1" spans="1:10">
       <c r="A143" s="3"/>
       <c r="B143" s="3" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C143" s="4">
         <v>201</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G143" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G143" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="H143" s="3" t="s">
         <v>46</v>
       </c>
@@ -6782,27 +6910,29 @@
         <v>201</v>
       </c>
       <c r="J143" s="3" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="144" customFormat="1" spans="1:10">
       <c r="A144" s="3"/>
       <c r="B144" s="3" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C144" s="4">
         <v>201</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G144" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G144" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="H144" s="3" t="s">
         <v>49</v>
       </c>
@@ -6810,27 +6940,29 @@
         <v>201</v>
       </c>
       <c r="J144" s="3" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="145" customFormat="1" spans="1:10">
       <c r="A145" s="3"/>
       <c r="B145" s="3" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C145" s="4">
         <v>201</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G145" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G145" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="H145" s="3" t="s">
         <v>52</v>
       </c>
@@ -6838,27 +6970,29 @@
         <v>201</v>
       </c>
       <c r="J145" s="3" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="146" customFormat="1" spans="1:10">
       <c r="A146" s="3"/>
       <c r="B146" s="3" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C146" s="4">
         <v>201</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G146" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G146" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="H146" s="3" t="s">
         <v>55</v>
       </c>
@@ -6866,27 +7000,29 @@
         <v>201</v>
       </c>
       <c r="J146" s="3" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="148" customFormat="1" spans="1:10">
       <c r="A148" s="3"/>
       <c r="B148" s="3" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C148" s="4">
         <v>202</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G148" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G148" s="3" t="s">
+        <v>321</v>
+      </c>
       <c r="H148" s="3" t="s">
         <v>27</v>
       </c>
@@ -6894,27 +7030,29 @@
         <v>202</v>
       </c>
       <c r="J148" s="3" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="149" customFormat="1" spans="1:10">
       <c r="A149" s="3"/>
       <c r="B149" s="3" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="C149" s="4">
         <v>202</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F149" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G149" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G149" s="3" t="s">
+        <v>321</v>
+      </c>
       <c r="H149" s="3" t="s">
         <v>31</v>
       </c>
@@ -6922,27 +7060,29 @@
         <v>202</v>
       </c>
       <c r="J149" s="3" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="150" customFormat="1" spans="1:10">
       <c r="A150" s="3"/>
       <c r="B150" s="3" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C150" s="4">
         <v>202</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F150" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G150" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G150" s="3" t="s">
+        <v>321</v>
+      </c>
       <c r="H150" s="3" t="s">
         <v>34</v>
       </c>
@@ -6950,27 +7090,29 @@
         <v>202</v>
       </c>
       <c r="J150" s="3" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="151" customFormat="1" spans="1:10">
       <c r="A151" s="3"/>
       <c r="B151" s="3" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C151" s="4">
         <v>202</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F151" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G151" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G151" s="3" t="s">
+        <v>321</v>
+      </c>
       <c r="H151" s="3" t="s">
         <v>37</v>
       </c>
@@ -6978,27 +7120,29 @@
         <v>202</v>
       </c>
       <c r="J151" s="3" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="152" customFormat="1" spans="1:10">
       <c r="A152" s="3"/>
       <c r="B152" s="3" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C152" s="4">
         <v>202</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F152" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G152" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G152" s="3" t="s">
+        <v>321</v>
+      </c>
       <c r="H152" s="3" t="s">
         <v>40</v>
       </c>
@@ -7006,27 +7150,29 @@
         <v>202</v>
       </c>
       <c r="J152" s="3" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
     </row>
     <row r="153" customFormat="1" spans="1:10">
       <c r="A153" s="3"/>
       <c r="B153" s="3" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C153" s="4">
         <v>202</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F153" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G153" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G153" s="3" t="s">
+        <v>321</v>
+      </c>
       <c r="H153" s="3" t="s">
         <v>43</v>
       </c>
@@ -7034,27 +7180,29 @@
         <v>202</v>
       </c>
       <c r="J153" s="3" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
     </row>
     <row r="154" customFormat="1" spans="1:10">
       <c r="A154" s="3"/>
       <c r="B154" s="3" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="C154" s="4">
         <v>202</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F154" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G154" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G154" s="3" t="s">
+        <v>321</v>
+      </c>
       <c r="H154" s="3" t="s">
         <v>46</v>
       </c>
@@ -7062,27 +7210,29 @@
         <v>202</v>
       </c>
       <c r="J154" s="3" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
     <row r="155" customFormat="1" spans="1:10">
       <c r="A155" s="3"/>
       <c r="B155" s="3" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C155" s="4">
         <v>202</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F155" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G155" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G155" s="3" t="s">
+        <v>321</v>
+      </c>
       <c r="H155" s="3" t="s">
         <v>49</v>
       </c>
@@ -7090,27 +7240,29 @@
         <v>202</v>
       </c>
       <c r="J155" s="3" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
     </row>
     <row r="156" customFormat="1" spans="1:10">
       <c r="A156" s="3"/>
       <c r="B156" s="3" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="C156" s="4">
         <v>202</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F156" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G156" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G156" s="3" t="s">
+        <v>321</v>
+      </c>
       <c r="H156" s="3" t="s">
         <v>52</v>
       </c>
@@ -7118,27 +7270,29 @@
         <v>202</v>
       </c>
       <c r="J156" s="3" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="157" customFormat="1" spans="1:10">
       <c r="A157" s="3"/>
       <c r="B157" s="3" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C157" s="4">
         <v>202</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F157" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G157" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G157" s="3" t="s">
+        <v>321</v>
+      </c>
       <c r="H157" s="3" t="s">
         <v>55</v>
       </c>
@@ -7146,27 +7300,29 @@
         <v>202</v>
       </c>
       <c r="J157" s="3" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
     </row>
     <row r="159" customFormat="1" spans="1:10">
       <c r="A159" s="3"/>
       <c r="B159" s="3" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="C159" s="4">
         <v>203</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G159" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G159" s="3" t="s">
+        <v>343</v>
+      </c>
       <c r="H159" s="3" t="s">
         <v>27</v>
       </c>
@@ -7174,27 +7330,29 @@
         <v>203</v>
       </c>
       <c r="J159" s="3" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
     </row>
     <row r="160" customFormat="1" spans="1:10">
       <c r="A160" s="3"/>
       <c r="B160" s="3" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="C160" s="4">
         <v>203</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G160" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G160" s="3" t="s">
+        <v>343</v>
+      </c>
       <c r="H160" s="3" t="s">
         <v>31</v>
       </c>
@@ -7202,27 +7360,29 @@
         <v>203</v>
       </c>
       <c r="J160" s="3" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
     </row>
     <row r="161" customFormat="1" spans="1:10">
       <c r="A161" s="3"/>
       <c r="B161" s="3" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="C161" s="4">
         <v>203</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F161" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G161" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G161" s="3" t="s">
+        <v>343</v>
+      </c>
       <c r="H161" s="3" t="s">
         <v>34</v>
       </c>
@@ -7230,27 +7390,29 @@
         <v>203</v>
       </c>
       <c r="J161" s="3" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
     </row>
     <row r="162" customFormat="1" spans="1:10">
       <c r="A162" s="3"/>
       <c r="B162" s="3" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="C162" s="4">
         <v>203</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F162" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G162" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G162" s="3" t="s">
+        <v>343</v>
+      </c>
       <c r="H162" s="3" t="s">
         <v>37</v>
       </c>
@@ -7258,27 +7420,29 @@
         <v>203</v>
       </c>
       <c r="J162" s="3" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
     </row>
     <row r="163" customFormat="1" spans="1:10">
       <c r="A163" s="3"/>
       <c r="B163" s="3" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="C163" s="4">
         <v>203</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F163" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G163" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G163" s="3" t="s">
+        <v>343</v>
+      </c>
       <c r="H163" s="3" t="s">
         <v>40</v>
       </c>
@@ -7286,27 +7450,29 @@
         <v>203</v>
       </c>
       <c r="J163" s="3" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
     </row>
     <row r="164" customFormat="1" spans="1:10">
       <c r="A164" s="3"/>
       <c r="B164" s="3" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="C164" s="4">
         <v>203</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F164" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G164" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G164" s="3" t="s">
+        <v>343</v>
+      </c>
       <c r="H164" s="3" t="s">
         <v>43</v>
       </c>
@@ -7314,27 +7480,29 @@
         <v>203</v>
       </c>
       <c r="J164" s="3" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
     </row>
     <row r="165" customFormat="1" spans="1:10">
       <c r="A165" s="3"/>
       <c r="B165" s="3" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="C165" s="4">
         <v>203</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F165" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G165" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G165" s="3" t="s">
+        <v>343</v>
+      </c>
       <c r="H165" s="3" t="s">
         <v>46</v>
       </c>
@@ -7342,27 +7510,29 @@
         <v>203</v>
       </c>
       <c r="J165" s="3" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
     </row>
     <row r="166" customFormat="1" spans="1:10">
       <c r="A166" s="3"/>
       <c r="B166" s="3" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="C166" s="4">
         <v>203</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F166" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G166" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G166" s="3" t="s">
+        <v>343</v>
+      </c>
       <c r="H166" s="3" t="s">
         <v>49</v>
       </c>
@@ -7370,27 +7540,29 @@
         <v>203</v>
       </c>
       <c r="J166" s="3" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
     </row>
     <row r="167" customFormat="1" spans="1:10">
       <c r="A167" s="3"/>
       <c r="B167" s="3" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="C167" s="4">
         <v>203</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F167" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G167" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G167" s="3" t="s">
+        <v>343</v>
+      </c>
       <c r="H167" s="3" t="s">
         <v>52</v>
       </c>
@@ -7398,27 +7570,29 @@
         <v>203</v>
       </c>
       <c r="J167" s="3" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
     </row>
     <row r="168" customFormat="1" spans="1:10">
       <c r="A168" s="3"/>
       <c r="B168" s="3" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="C168" s="4">
         <v>203</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F168" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G168" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G168" s="3" t="s">
+        <v>343</v>
+      </c>
       <c r="H168" s="3" t="s">
         <v>55</v>
       </c>
@@ -7426,27 +7600,29 @@
         <v>203</v>
       </c>
       <c r="J168" s="3" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
     </row>
     <row r="170" customFormat="1" spans="1:10">
       <c r="A170" s="3"/>
       <c r="B170" s="3" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="C170" s="4">
         <v>204</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F170" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G170" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G170" s="3" t="s">
+        <v>365</v>
+      </c>
       <c r="H170" s="3" t="s">
         <v>27</v>
       </c>
@@ -7454,27 +7630,29 @@
         <v>204</v>
       </c>
       <c r="J170" s="3" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
     </row>
     <row r="171" customFormat="1" spans="1:10">
       <c r="A171" s="3"/>
       <c r="B171" s="3" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="C171" s="4">
         <v>204</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F171" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G171" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G171" s="3" t="s">
+        <v>365</v>
+      </c>
       <c r="H171" s="3" t="s">
         <v>31</v>
       </c>
@@ -7482,27 +7660,29 @@
         <v>204</v>
       </c>
       <c r="J171" s="3" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
     </row>
     <row r="172" customFormat="1" spans="1:10">
       <c r="A172" s="3"/>
       <c r="B172" s="3" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="C172" s="4">
         <v>204</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F172" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G172" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G172" s="3" t="s">
+        <v>365</v>
+      </c>
       <c r="H172" s="3" t="s">
         <v>34</v>
       </c>
@@ -7510,27 +7690,29 @@
         <v>204</v>
       </c>
       <c r="J172" s="3" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
     </row>
     <row r="173" customFormat="1" spans="1:10">
       <c r="A173" s="3"/>
       <c r="B173" s="3" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="C173" s="4">
         <v>204</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F173" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G173" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G173" s="3" t="s">
+        <v>365</v>
+      </c>
       <c r="H173" s="3" t="s">
         <v>37</v>
       </c>
@@ -7538,27 +7720,29 @@
         <v>204</v>
       </c>
       <c r="J173" s="3" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
     </row>
     <row r="174" customFormat="1" spans="1:10">
       <c r="A174" s="3"/>
       <c r="B174" s="3" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="C174" s="4">
         <v>204</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F174" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G174" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G174" s="3" t="s">
+        <v>365</v>
+      </c>
       <c r="H174" s="3" t="s">
         <v>40</v>
       </c>
@@ -7566,27 +7750,29 @@
         <v>204</v>
       </c>
       <c r="J174" s="3" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
     </row>
     <row r="175" customFormat="1" spans="1:10">
       <c r="A175" s="3"/>
       <c r="B175" s="3" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="C175" s="4">
         <v>204</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F175" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G175" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G175" s="3" t="s">
+        <v>365</v>
+      </c>
       <c r="H175" s="3" t="s">
         <v>43</v>
       </c>
@@ -7594,27 +7780,29 @@
         <v>204</v>
       </c>
       <c r="J175" s="3" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
     </row>
     <row r="176" customFormat="1" spans="1:10">
       <c r="A176" s="3"/>
       <c r="B176" s="3" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="C176" s="4">
         <v>204</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F176" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G176" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G176" s="3" t="s">
+        <v>365</v>
+      </c>
       <c r="H176" s="3" t="s">
         <v>46</v>
       </c>
@@ -7622,27 +7810,29 @@
         <v>204</v>
       </c>
       <c r="J176" s="3" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
     </row>
     <row r="177" customFormat="1" spans="1:10">
       <c r="A177" s="3"/>
       <c r="B177" s="3" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="C177" s="4">
         <v>204</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F177" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G177" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G177" s="3" t="s">
+        <v>365</v>
+      </c>
       <c r="H177" s="3" t="s">
         <v>49</v>
       </c>
@@ -7650,27 +7840,29 @@
         <v>204</v>
       </c>
       <c r="J177" s="3" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
     </row>
     <row r="178" customFormat="1" spans="1:10">
       <c r="A178" s="3"/>
       <c r="B178" s="3" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="C178" s="4">
         <v>204</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F178" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G178" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G178" s="3" t="s">
+        <v>365</v>
+      </c>
       <c r="H178" s="3" t="s">
         <v>52</v>
       </c>
@@ -7678,27 +7870,29 @@
         <v>204</v>
       </c>
       <c r="J178" s="3" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
     </row>
     <row r="179" customFormat="1" spans="1:10">
       <c r="A179" s="3"/>
       <c r="B179" s="3" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="C179" s="4">
         <v>204</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F179" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G179" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G179" s="3" t="s">
+        <v>365</v>
+      </c>
       <c r="H179" s="3" t="s">
         <v>55</v>
       </c>
@@ -7706,27 +7900,29 @@
         <v>204</v>
       </c>
       <c r="J179" s="3" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
     </row>
     <row r="181" customFormat="1" spans="1:10">
       <c r="A181" s="3"/>
       <c r="B181" s="3" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="C181" s="4">
         <v>205</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F181" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G181" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G181" t="s">
+        <v>387</v>
+      </c>
       <c r="H181" s="3" t="s">
         <v>27</v>
       </c>
@@ -7734,27 +7930,29 @@
         <v>205</v>
       </c>
       <c r="J181" s="3" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
     </row>
     <row r="182" customFormat="1" spans="1:10">
       <c r="A182" s="3"/>
       <c r="B182" s="3" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="C182" s="4">
         <v>205</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F182" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G182" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G182" t="s">
+        <v>387</v>
+      </c>
       <c r="H182" s="3" t="s">
         <v>31</v>
       </c>
@@ -7762,27 +7960,29 @@
         <v>205</v>
       </c>
       <c r="J182" s="3" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
     </row>
     <row r="183" customFormat="1" spans="1:10">
       <c r="A183" s="3"/>
       <c r="B183" s="3" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="C183" s="4">
         <v>205</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F183" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G183" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G183" t="s">
+        <v>387</v>
+      </c>
       <c r="H183" s="3" t="s">
         <v>34</v>
       </c>
@@ -7790,27 +7990,29 @@
         <v>205</v>
       </c>
       <c r="J183" s="3" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
     </row>
     <row r="184" customFormat="1" spans="1:10">
       <c r="A184" s="3"/>
       <c r="B184" s="3" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C184" s="4">
         <v>205</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F184" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G184" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G184" t="s">
+        <v>387</v>
+      </c>
       <c r="H184" s="3" t="s">
         <v>37</v>
       </c>
@@ -7818,27 +8020,29 @@
         <v>205</v>
       </c>
       <c r="J184" s="3" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
     </row>
     <row r="185" customFormat="1" spans="1:10">
       <c r="A185" s="3"/>
       <c r="B185" s="3" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="C185" s="4">
         <v>205</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F185" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G185" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G185" t="s">
+        <v>387</v>
+      </c>
       <c r="H185" s="3" t="s">
         <v>40</v>
       </c>
@@ -7846,27 +8050,29 @@
         <v>205</v>
       </c>
       <c r="J185" s="3" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
     </row>
     <row r="186" customFormat="1" spans="1:10">
       <c r="A186" s="3"/>
       <c r="B186" s="3" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="C186" s="4">
         <v>205</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F186" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G186" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G186" t="s">
+        <v>387</v>
+      </c>
       <c r="H186" s="3" t="s">
         <v>43</v>
       </c>
@@ -7874,27 +8080,29 @@
         <v>205</v>
       </c>
       <c r="J186" s="3" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
     </row>
     <row r="187" customFormat="1" spans="1:10">
       <c r="A187" s="3"/>
       <c r="B187" s="3" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="C187" s="4">
         <v>205</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F187" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G187" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G187" t="s">
+        <v>387</v>
+      </c>
       <c r="H187" s="3" t="s">
         <v>46</v>
       </c>
@@ -7902,27 +8110,29 @@
         <v>205</v>
       </c>
       <c r="J187" s="3" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
     </row>
     <row r="188" customFormat="1" spans="1:10">
       <c r="A188" s="3"/>
       <c r="B188" s="3" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="C188" s="4">
         <v>205</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F188" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G188" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G188" t="s">
+        <v>387</v>
+      </c>
       <c r="H188" s="3" t="s">
         <v>49</v>
       </c>
@@ -7930,27 +8140,29 @@
         <v>205</v>
       </c>
       <c r="J188" s="3" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
     </row>
     <row r="189" customFormat="1" spans="1:10">
       <c r="A189" s="3"/>
       <c r="B189" s="3" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="C189" s="4">
         <v>205</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F189" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G189" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G189" t="s">
+        <v>387</v>
+      </c>
       <c r="H189" s="3" t="s">
         <v>52</v>
       </c>
@@ -7958,27 +8170,29 @@
         <v>205</v>
       </c>
       <c r="J189" s="3" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
     </row>
     <row r="190" customFormat="1" spans="1:10">
       <c r="A190" s="3"/>
       <c r="B190" s="3" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="C190" s="4">
         <v>205</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F190" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G190" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G190" t="s">
+        <v>387</v>
+      </c>
       <c r="H190" s="3" t="s">
         <v>55</v>
       </c>
@@ -7986,27 +8200,29 @@
         <v>205</v>
       </c>
       <c r="J190" s="3" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
     </row>
     <row r="192" customFormat="1" spans="1:10">
       <c r="A192" s="3"/>
       <c r="B192" s="3" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="C192" s="4">
         <v>206</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F192" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G192" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G192" t="s">
+        <v>409</v>
+      </c>
       <c r="H192" s="3" t="s">
         <v>27</v>
       </c>
@@ -8014,27 +8230,29 @@
         <v>206</v>
       </c>
       <c r="J192" s="3" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
     </row>
     <row r="193" customFormat="1" spans="1:10">
       <c r="A193" s="3"/>
       <c r="B193" s="3" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="C193" s="4">
         <v>206</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F193" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G193" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G193" t="s">
+        <v>409</v>
+      </c>
       <c r="H193" s="3" t="s">
         <v>31</v>
       </c>
@@ -8042,27 +8260,29 @@
         <v>206</v>
       </c>
       <c r="J193" s="3" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
     </row>
     <row r="194" customFormat="1" spans="1:10">
       <c r="A194" s="3"/>
       <c r="B194" s="3" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="C194" s="4">
         <v>206</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F194" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G194" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G194" t="s">
+        <v>409</v>
+      </c>
       <c r="H194" s="3" t="s">
         <v>34</v>
       </c>
@@ -8070,27 +8290,29 @@
         <v>206</v>
       </c>
       <c r="J194" s="3" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
     </row>
     <row r="195" customFormat="1" spans="1:10">
       <c r="A195" s="3"/>
       <c r="B195" s="3" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="C195" s="4">
         <v>206</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F195" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G195" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G195" t="s">
+        <v>409</v>
+      </c>
       <c r="H195" s="3" t="s">
         <v>37</v>
       </c>
@@ -8098,27 +8320,29 @@
         <v>206</v>
       </c>
       <c r="J195" s="3" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
     </row>
     <row r="196" customFormat="1" spans="1:10">
       <c r="A196" s="3"/>
       <c r="B196" s="3" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="C196" s="4">
         <v>206</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F196" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G196" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G196" t="s">
+        <v>409</v>
+      </c>
       <c r="H196" s="3" t="s">
         <v>40</v>
       </c>
@@ -8126,27 +8350,29 @@
         <v>206</v>
       </c>
       <c r="J196" s="3" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
     </row>
     <row r="197" customFormat="1" spans="1:10">
       <c r="A197" s="3"/>
       <c r="B197" s="3" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="C197" s="4">
         <v>206</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F197" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G197" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G197" t="s">
+        <v>409</v>
+      </c>
       <c r="H197" s="3" t="s">
         <v>43</v>
       </c>
@@ -8154,27 +8380,29 @@
         <v>206</v>
       </c>
       <c r="J197" s="3" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
     </row>
     <row r="198" customFormat="1" spans="1:10">
       <c r="A198" s="3"/>
       <c r="B198" s="3" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="C198" s="4">
         <v>206</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F198" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G198" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G198" t="s">
+        <v>409</v>
+      </c>
       <c r="H198" s="3" t="s">
         <v>46</v>
       </c>
@@ -8182,27 +8410,29 @@
         <v>206</v>
       </c>
       <c r="J198" s="3" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
     </row>
     <row r="199" customFormat="1" spans="1:10">
       <c r="A199" s="3"/>
       <c r="B199" s="3" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="C199" s="4">
         <v>206</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F199" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G199" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G199" t="s">
+        <v>409</v>
+      </c>
       <c r="H199" s="3" t="s">
         <v>49</v>
       </c>
@@ -8210,27 +8440,29 @@
         <v>206</v>
       </c>
       <c r="J199" s="3" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
     </row>
     <row r="200" customFormat="1" spans="1:10">
       <c r="A200" s="3"/>
       <c r="B200" s="3" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="C200" s="4">
         <v>206</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F200" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G200" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G200" t="s">
+        <v>409</v>
+      </c>
       <c r="H200" s="3" t="s">
         <v>52</v>
       </c>
@@ -8238,27 +8470,29 @@
         <v>206</v>
       </c>
       <c r="J200" s="3" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
     </row>
     <row r="201" customFormat="1" spans="1:10">
       <c r="A201" s="3"/>
       <c r="B201" s="3" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="C201" s="4">
         <v>206</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F201" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G201" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G201" t="s">
+        <v>409</v>
+      </c>
       <c r="H201" s="3" t="s">
         <v>55</v>
       </c>
@@ -8266,27 +8500,29 @@
         <v>206</v>
       </c>
       <c r="J201" s="3" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
     </row>
     <row r="203" customFormat="1" spans="1:10">
       <c r="A203" s="3"/>
       <c r="B203" s="3" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="C203" s="4">
         <v>207</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F203" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G203" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G203" s="3" t="s">
+        <v>431</v>
+      </c>
       <c r="H203" s="3" t="s">
         <v>27</v>
       </c>
@@ -8294,27 +8530,29 @@
         <v>207</v>
       </c>
       <c r="J203" s="3" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
     </row>
     <row r="204" customFormat="1" spans="1:10">
       <c r="A204" s="3"/>
       <c r="B204" s="3" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="C204" s="4">
         <v>207</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F204" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G204" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G204" s="3" t="s">
+        <v>431</v>
+      </c>
       <c r="H204" s="3" t="s">
         <v>31</v>
       </c>
@@ -8322,27 +8560,29 @@
         <v>207</v>
       </c>
       <c r="J204" s="3" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
     </row>
     <row r="205" customFormat="1" spans="1:10">
       <c r="A205" s="3"/>
       <c r="B205" s="3" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="C205" s="4">
         <v>207</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F205" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G205" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G205" s="3" t="s">
+        <v>431</v>
+      </c>
       <c r="H205" s="3" t="s">
         <v>34</v>
       </c>
@@ -8350,27 +8590,29 @@
         <v>207</v>
       </c>
       <c r="J205" s="3" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
     </row>
     <row r="206" customFormat="1" spans="1:10">
       <c r="A206" s="3"/>
       <c r="B206" s="3" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="C206" s="4">
         <v>207</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="E206" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F206" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G206" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G206" s="3" t="s">
+        <v>431</v>
+      </c>
       <c r="H206" s="3" t="s">
         <v>37</v>
       </c>
@@ -8378,27 +8620,29 @@
         <v>207</v>
       </c>
       <c r="J206" s="3" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
     </row>
     <row r="207" customFormat="1" spans="1:10">
       <c r="A207" s="3"/>
       <c r="B207" s="3" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="C207" s="4">
         <v>207</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F207" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G207" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G207" s="3" t="s">
+        <v>431</v>
+      </c>
       <c r="H207" s="3" t="s">
         <v>40</v>
       </c>
@@ -8406,27 +8650,29 @@
         <v>207</v>
       </c>
       <c r="J207" s="3" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
     </row>
     <row r="208" customFormat="1" spans="1:10">
       <c r="A208" s="3"/>
       <c r="B208" s="3" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="C208" s="4">
         <v>207</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F208" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G208" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G208" s="3" t="s">
+        <v>431</v>
+      </c>
       <c r="H208" s="3" t="s">
         <v>43</v>
       </c>
@@ -8434,27 +8680,29 @@
         <v>207</v>
       </c>
       <c r="J208" s="3" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
     </row>
     <row r="209" customFormat="1" spans="1:10">
       <c r="A209" s="3"/>
       <c r="B209" s="3" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="C209" s="4">
         <v>207</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F209" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G209" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G209" s="3" t="s">
+        <v>431</v>
+      </c>
       <c r="H209" s="3" t="s">
         <v>46</v>
       </c>
@@ -8462,27 +8710,29 @@
         <v>207</v>
       </c>
       <c r="J209" s="3" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
     </row>
     <row r="210" customFormat="1" spans="1:10">
       <c r="A210" s="3"/>
       <c r="B210" s="3" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="C210" s="4">
         <v>207</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F210" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G210" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G210" s="3" t="s">
+        <v>431</v>
+      </c>
       <c r="H210" s="3" t="s">
         <v>49</v>
       </c>
@@ -8490,27 +8740,29 @@
         <v>207</v>
       </c>
       <c r="J210" s="3" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
     </row>
     <row r="211" customFormat="1" spans="1:10">
       <c r="A211" s="3"/>
       <c r="B211" s="3" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="C211" s="4">
         <v>207</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F211" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G211" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G211" s="3" t="s">
+        <v>431</v>
+      </c>
       <c r="H211" s="3" t="s">
         <v>52</v>
       </c>
@@ -8518,27 +8770,29 @@
         <v>207</v>
       </c>
       <c r="J211" s="3" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
     </row>
     <row r="212" customFormat="1" spans="1:10">
       <c r="A212" s="3"/>
       <c r="B212" s="3" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="C212" s="4">
         <v>207</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F212" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G212" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G212" s="3" t="s">
+        <v>431</v>
+      </c>
       <c r="H212" s="3" t="s">
         <v>55</v>
       </c>
@@ -8546,27 +8800,29 @@
         <v>207</v>
       </c>
       <c r="J212" s="3" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
     </row>
     <row r="214" customFormat="1" spans="1:10">
       <c r="A214" s="3"/>
       <c r="B214" s="3" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="C214" s="4">
         <v>208</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F214" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G214" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G214" s="3" t="s">
+        <v>453</v>
+      </c>
       <c r="H214" s="3" t="s">
         <v>27</v>
       </c>
@@ -8574,27 +8830,29 @@
         <v>208</v>
       </c>
       <c r="J214" s="3" t="s">
-        <v>443</v>
+        <v>454</v>
       </c>
     </row>
     <row r="215" customFormat="1" spans="1:10">
       <c r="A215" s="3"/>
       <c r="B215" s="3" t="s">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="C215" s="4">
         <v>208</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="E215" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F215" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G215" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G215" s="3" t="s">
+        <v>453</v>
+      </c>
       <c r="H215" s="3" t="s">
         <v>31</v>
       </c>
@@ -8602,27 +8860,29 @@
         <v>208</v>
       </c>
       <c r="J215" s="3" t="s">
-        <v>445</v>
+        <v>456</v>
       </c>
     </row>
     <row r="216" customFormat="1" spans="1:10">
       <c r="A216" s="3"/>
       <c r="B216" s="3" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="C216" s="4">
         <v>208</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="E216" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F216" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G216" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G216" s="3" t="s">
+        <v>453</v>
+      </c>
       <c r="H216" s="3" t="s">
         <v>34</v>
       </c>
@@ -8630,27 +8890,29 @@
         <v>208</v>
       </c>
       <c r="J216" s="3" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
     </row>
     <row r="217" customFormat="1" spans="1:10">
       <c r="A217" s="3"/>
       <c r="B217" s="3" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="C217" s="4">
         <v>208</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="E217" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F217" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G217" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G217" s="3" t="s">
+        <v>453</v>
+      </c>
       <c r="H217" s="3" t="s">
         <v>37</v>
       </c>
@@ -8658,27 +8920,29 @@
         <v>208</v>
       </c>
       <c r="J217" s="3" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
     </row>
     <row r="218" customFormat="1" spans="1:10">
       <c r="A218" s="3"/>
       <c r="B218" s="3" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="C218" s="4">
         <v>208</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F218" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G218" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G218" s="3" t="s">
+        <v>453</v>
+      </c>
       <c r="H218" s="3" t="s">
         <v>40</v>
       </c>
@@ -8686,27 +8950,29 @@
         <v>208</v>
       </c>
       <c r="J218" s="3" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
     </row>
     <row r="219" customFormat="1" spans="1:10">
       <c r="A219" s="3"/>
       <c r="B219" s="3" t="s">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="C219" s="4">
         <v>208</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F219" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G219" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G219" s="3" t="s">
+        <v>453</v>
+      </c>
       <c r="H219" s="3" t="s">
         <v>43</v>
       </c>
@@ -8714,27 +8980,29 @@
         <v>208</v>
       </c>
       <c r="J219" s="3" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
     </row>
     <row r="220" customFormat="1" spans="1:10">
       <c r="A220" s="3"/>
       <c r="B220" s="3" t="s">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="C220" s="4">
         <v>208</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F220" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G220" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G220" s="3" t="s">
+        <v>453</v>
+      </c>
       <c r="H220" s="3" t="s">
         <v>46</v>
       </c>
@@ -8742,27 +9010,29 @@
         <v>208</v>
       </c>
       <c r="J220" s="3" t="s">
-        <v>455</v>
+        <v>466</v>
       </c>
     </row>
     <row r="221" customFormat="1" spans="1:10">
       <c r="A221" s="3"/>
       <c r="B221" s="3" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="C221" s="4">
         <v>208</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F221" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G221" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G221" s="3" t="s">
+        <v>453</v>
+      </c>
       <c r="H221" s="3" t="s">
         <v>49</v>
       </c>
@@ -8770,27 +9040,29 @@
         <v>208</v>
       </c>
       <c r="J221" s="3" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
     </row>
     <row r="222" customFormat="1" spans="1:10">
       <c r="A222" s="3"/>
       <c r="B222" s="3" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="C222" s="4">
         <v>208</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F222" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G222" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G222" s="3" t="s">
+        <v>453</v>
+      </c>
       <c r="H222" s="3" t="s">
         <v>52</v>
       </c>
@@ -8798,27 +9070,29 @@
         <v>208</v>
       </c>
       <c r="J222" s="3" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
     </row>
     <row r="223" customFormat="1" spans="1:10">
       <c r="A223" s="3"/>
       <c r="B223" s="3" t="s">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="C223" s="4">
         <v>208</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F223" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G223" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="G223" s="3" t="s">
+        <v>453</v>
+      </c>
       <c r="H223" s="3" t="s">
         <v>55</v>
       </c>
@@ -8826,7 +9100,7 @@
         <v>208</v>
       </c>
       <c r="J223" s="3" t="s">
-        <v>461</v>
+        <v>472</v>
       </c>
     </row>
     <row r="224" customFormat="1" spans="1:10">
@@ -8844,19 +9118,19 @@
     <row r="225" s="1" customFormat="1" spans="1:10">
       <c r="A225" s="2"/>
       <c r="B225" s="2" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="C225" s="5">
         <v>209</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="G225" s="2"/>
       <c r="H225" s="2" t="s">
@@ -8866,25 +9140,25 @@
         <v>209</v>
       </c>
       <c r="J225" s="1" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
     </row>
     <row r="226" s="1" customFormat="1" spans="1:10">
       <c r="A226" s="2"/>
       <c r="B226" s="2" t="s">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="C226" s="5">
         <v>209</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="G226" s="2"/>
       <c r="H226" s="2" t="s">
@@ -8894,25 +9168,25 @@
         <v>209</v>
       </c>
       <c r="J226" s="1" t="s">
-        <v>466</v>
+        <v>477</v>
       </c>
     </row>
     <row r="227" s="1" customFormat="1" spans="1:10">
       <c r="A227" s="2"/>
       <c r="B227" s="2" t="s">
-        <v>467</v>
+        <v>478</v>
       </c>
       <c r="C227" s="5">
         <v>209</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="G227" s="2"/>
       <c r="H227" s="2" t="s">
@@ -8922,25 +9196,25 @@
         <v>209</v>
       </c>
       <c r="J227" s="1" t="s">
-        <v>468</v>
+        <v>479</v>
       </c>
     </row>
     <row r="228" s="1" customFormat="1" spans="1:10">
       <c r="A228" s="2"/>
       <c r="B228" s="2" t="s">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="C228" s="5">
         <v>209</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="G228" s="2"/>
       <c r="H228" s="2" t="s">
@@ -8950,25 +9224,25 @@
         <v>209</v>
       </c>
       <c r="J228" s="1" t="s">
-        <v>470</v>
+        <v>481</v>
       </c>
     </row>
     <row r="229" s="1" customFormat="1" spans="1:10">
       <c r="A229" s="2"/>
       <c r="B229" s="2" t="s">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="C229" s="5">
         <v>209</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="G229" s="2"/>
       <c r="H229" s="2" t="s">
@@ -8978,25 +9252,25 @@
         <v>209</v>
       </c>
       <c r="J229" s="1" t="s">
-        <v>472</v>
+        <v>483</v>
       </c>
     </row>
     <row r="230" s="1" customFormat="1" spans="1:10">
       <c r="A230" s="2"/>
       <c r="B230" s="2" t="s">
-        <v>473</v>
+        <v>484</v>
       </c>
       <c r="C230" s="5">
         <v>209</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="G230" s="2"/>
       <c r="H230" s="2" t="s">
@@ -9006,25 +9280,25 @@
         <v>209</v>
       </c>
       <c r="J230" s="1" t="s">
-        <v>474</v>
+        <v>485</v>
       </c>
     </row>
     <row r="231" s="1" customFormat="1" spans="1:10">
       <c r="A231" s="2"/>
       <c r="B231" s="2" t="s">
-        <v>475</v>
+        <v>486</v>
       </c>
       <c r="C231" s="5">
         <v>209</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="G231" s="2"/>
       <c r="H231" s="2" t="s">
@@ -9034,25 +9308,25 @@
         <v>209</v>
       </c>
       <c r="J231" s="1" t="s">
-        <v>476</v>
+        <v>487</v>
       </c>
     </row>
     <row r="232" s="1" customFormat="1" spans="1:10">
       <c r="A232" s="2"/>
       <c r="B232" s="2" t="s">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="C232" s="5">
         <v>209</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="G232" s="2"/>
       <c r="H232" s="2" t="s">
@@ -9062,25 +9336,25 @@
         <v>209</v>
       </c>
       <c r="J232" s="1" t="s">
-        <v>478</v>
+        <v>489</v>
       </c>
     </row>
     <row r="233" s="1" customFormat="1" spans="1:10">
       <c r="A233" s="2"/>
       <c r="B233" s="2" t="s">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="C233" s="5">
         <v>209</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="E233" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="G233" s="2"/>
       <c r="H233" s="2" t="s">
@@ -9090,25 +9364,25 @@
         <v>209</v>
       </c>
       <c r="J233" s="1" t="s">
-        <v>480</v>
+        <v>491</v>
       </c>
     </row>
     <row r="234" s="1" customFormat="1" spans="1:10">
       <c r="A234" s="2"/>
       <c r="B234" s="2" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="C234" s="5">
         <v>209</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="G234" s="2"/>
       <c r="H234" s="2" t="s">
@@ -9118,7 +9392,7 @@
         <v>209</v>
       </c>
       <c r="J234" s="1" t="s">
-        <v>482</v>
+        <v>493</v>
       </c>
     </row>
     <row r="235" customFormat="1" spans="1:10">
@@ -9136,21 +9410,23 @@
     <row r="236" customFormat="1" spans="1:10">
       <c r="A236" s="3"/>
       <c r="B236" s="3" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="C236" s="4">
         <v>301</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="E236" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F236" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G236" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G236" s="3" t="s">
+        <v>498</v>
+      </c>
       <c r="H236" s="3" t="s">
         <v>27</v>
       </c>
@@ -9158,27 +9434,29 @@
         <v>301</v>
       </c>
       <c r="J236" s="3" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
     </row>
     <row r="237" customFormat="1" spans="1:10">
       <c r="A237" s="3"/>
       <c r="B237" s="3" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="C237" s="4">
         <v>301</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="E237" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F237" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G237" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G237" s="3" t="s">
+        <v>498</v>
+      </c>
       <c r="H237" s="3" t="s">
         <v>31</v>
       </c>
@@ -9186,27 +9464,29 @@
         <v>301</v>
       </c>
       <c r="J237" s="3" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
     </row>
     <row r="238" customFormat="1" spans="1:10">
       <c r="A238" s="3"/>
       <c r="B238" s="3" t="s">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="C238" s="4">
         <v>301</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="E238" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F238" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G238" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G238" s="3" t="s">
+        <v>498</v>
+      </c>
       <c r="H238" s="3" t="s">
         <v>34</v>
       </c>
@@ -9214,27 +9494,29 @@
         <v>301</v>
       </c>
       <c r="J238" s="3" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" customFormat="1" spans="1:10">
       <c r="A239" s="3"/>
       <c r="B239" s="3" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="C239" s="4">
         <v>301</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="E239" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F239" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G239" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G239" s="3" t="s">
+        <v>498</v>
+      </c>
       <c r="H239" s="3" t="s">
         <v>37</v>
       </c>
@@ -9242,27 +9524,29 @@
         <v>301</v>
       </c>
       <c r="J239" s="3" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" customFormat="1" spans="1:10">
       <c r="A240" s="3"/>
       <c r="B240" s="3" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="C240" s="4">
         <v>301</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="E240" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F240" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G240" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G240" s="3" t="s">
+        <v>498</v>
+      </c>
       <c r="H240" s="3" t="s">
         <v>40</v>
       </c>
@@ -9270,27 +9554,29 @@
         <v>301</v>
       </c>
       <c r="J240" s="3" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
     </row>
     <row r="241" customFormat="1" spans="1:10">
       <c r="A241" s="3"/>
       <c r="B241" s="3" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="C241" s="4">
         <v>301</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="E241" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F241" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G241" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G241" s="3" t="s">
+        <v>498</v>
+      </c>
       <c r="H241" s="3" t="s">
         <v>43</v>
       </c>
@@ -9298,27 +9584,29 @@
         <v>301</v>
       </c>
       <c r="J241" s="3" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
     </row>
     <row r="242" customFormat="1" spans="1:10">
       <c r="A242" s="3"/>
       <c r="B242" s="3" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="C242" s="4">
         <v>301</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="E242" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F242" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G242" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G242" s="3" t="s">
+        <v>498</v>
+      </c>
       <c r="H242" s="3" t="s">
         <v>46</v>
       </c>
@@ -9326,27 +9614,29 @@
         <v>301</v>
       </c>
       <c r="J242" s="3" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
     </row>
     <row r="243" customFormat="1" spans="1:10">
       <c r="A243" s="3"/>
       <c r="B243" s="3" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="C243" s="4">
         <v>301</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="E243" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F243" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G243" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G243" s="3" t="s">
+        <v>498</v>
+      </c>
       <c r="H243" s="3" t="s">
         <v>49</v>
       </c>
@@ -9354,27 +9644,29 @@
         <v>301</v>
       </c>
       <c r="J243" s="3" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
     </row>
     <row r="244" customFormat="1" spans="1:10">
       <c r="A244" s="3"/>
       <c r="B244" s="3" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="C244" s="4">
         <v>301</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F244" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G244" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G244" s="3" t="s">
+        <v>498</v>
+      </c>
       <c r="H244" s="3" t="s">
         <v>52</v>
       </c>
@@ -9382,27 +9674,29 @@
         <v>301</v>
       </c>
       <c r="J244" s="3" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
     </row>
     <row r="245" customFormat="1" spans="1:10">
       <c r="A245" s="3"/>
       <c r="B245" s="3" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="C245" s="4">
         <v>301</v>
       </c>
       <c r="D245" s="3" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="E245" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F245" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G245" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G245" s="3" t="s">
+        <v>498</v>
+      </c>
       <c r="H245" s="3" t="s">
         <v>55</v>
       </c>
@@ -9410,27 +9704,29 @@
         <v>301</v>
       </c>
       <c r="J245" s="3" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
     </row>
     <row r="247" customFormat="1" spans="1:10">
       <c r="A247" s="3"/>
       <c r="B247" s="3" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="C247" s="4">
         <v>302</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="E247" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F247" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G247" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G247" s="3" t="s">
+        <v>520</v>
+      </c>
       <c r="H247" s="3" t="s">
         <v>27</v>
       </c>
@@ -9438,27 +9734,29 @@
         <v>302</v>
       </c>
       <c r="J247" s="3" t="s">
-        <v>508</v>
+        <v>521</v>
       </c>
     </row>
     <row r="248" customFormat="1" spans="1:10">
       <c r="A248" s="3"/>
       <c r="B248" s="3" t="s">
-        <v>509</v>
+        <v>522</v>
       </c>
       <c r="C248" s="4">
         <v>302</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="E248" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F248" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G248" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G248" s="3" t="s">
+        <v>520</v>
+      </c>
       <c r="H248" s="3" t="s">
         <v>31</v>
       </c>
@@ -9466,27 +9764,29 @@
         <v>302</v>
       </c>
       <c r="J248" s="3" t="s">
-        <v>510</v>
+        <v>523</v>
       </c>
     </row>
     <row r="249" customFormat="1" spans="1:10">
       <c r="A249" s="3"/>
       <c r="B249" s="3" t="s">
-        <v>511</v>
+        <v>524</v>
       </c>
       <c r="C249" s="4">
         <v>302</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="E249" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F249" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G249" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G249" s="3" t="s">
+        <v>520</v>
+      </c>
       <c r="H249" s="3" t="s">
         <v>34</v>
       </c>
@@ -9494,27 +9794,29 @@
         <v>302</v>
       </c>
       <c r="J249" s="3" t="s">
-        <v>512</v>
+        <v>525</v>
       </c>
     </row>
     <row r="250" customFormat="1" spans="1:10">
       <c r="A250" s="3"/>
       <c r="B250" s="3" t="s">
-        <v>513</v>
+        <v>526</v>
       </c>
       <c r="C250" s="4">
         <v>302</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="E250" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F250" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G250" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G250" s="3" t="s">
+        <v>520</v>
+      </c>
       <c r="H250" s="3" t="s">
         <v>37</v>
       </c>
@@ -9522,27 +9824,29 @@
         <v>302</v>
       </c>
       <c r="J250" s="3" t="s">
-        <v>514</v>
+        <v>527</v>
       </c>
     </row>
     <row r="251" customFormat="1" spans="1:10">
       <c r="A251" s="3"/>
       <c r="B251" s="3" t="s">
-        <v>515</v>
+        <v>528</v>
       </c>
       <c r="C251" s="4">
         <v>302</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="E251" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F251" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G251" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G251" s="3" t="s">
+        <v>520</v>
+      </c>
       <c r="H251" s="3" t="s">
         <v>40</v>
       </c>
@@ -9550,27 +9854,29 @@
         <v>302</v>
       </c>
       <c r="J251" s="3" t="s">
-        <v>516</v>
+        <v>529</v>
       </c>
     </row>
     <row r="252" customFormat="1" spans="1:10">
       <c r="A252" s="3"/>
       <c r="B252" s="3" t="s">
-        <v>517</v>
+        <v>530</v>
       </c>
       <c r="C252" s="4">
         <v>302</v>
       </c>
       <c r="D252" s="3" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="E252" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F252" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G252" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G252" s="3" t="s">
+        <v>520</v>
+      </c>
       <c r="H252" s="3" t="s">
         <v>43</v>
       </c>
@@ -9578,27 +9884,29 @@
         <v>302</v>
       </c>
       <c r="J252" s="3" t="s">
-        <v>518</v>
+        <v>531</v>
       </c>
     </row>
     <row r="253" customFormat="1" spans="1:10">
       <c r="A253" s="3"/>
       <c r="B253" s="3" t="s">
-        <v>519</v>
+        <v>532</v>
       </c>
       <c r="C253" s="4">
         <v>302</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="E253" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F253" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G253" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G253" s="3" t="s">
+        <v>520</v>
+      </c>
       <c r="H253" s="3" t="s">
         <v>46</v>
       </c>
@@ -9606,27 +9914,29 @@
         <v>302</v>
       </c>
       <c r="J253" s="3" t="s">
-        <v>520</v>
+        <v>533</v>
       </c>
     </row>
     <row r="254" customFormat="1" spans="1:10">
       <c r="A254" s="3"/>
       <c r="B254" s="3" t="s">
-        <v>521</v>
+        <v>534</v>
       </c>
       <c r="C254" s="4">
         <v>302</v>
       </c>
       <c r="D254" s="3" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="E254" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F254" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G254" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G254" s="3" t="s">
+        <v>520</v>
+      </c>
       <c r="H254" s="3" t="s">
         <v>49</v>
       </c>
@@ -9634,27 +9944,29 @@
         <v>302</v>
       </c>
       <c r="J254" s="3" t="s">
-        <v>522</v>
+        <v>535</v>
       </c>
     </row>
     <row r="255" customFormat="1" spans="1:10">
       <c r="A255" s="3"/>
       <c r="B255" s="3" t="s">
-        <v>523</v>
+        <v>536</v>
       </c>
       <c r="C255" s="4">
         <v>302</v>
       </c>
       <c r="D255" s="3" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="E255" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F255" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G255" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G255" s="3" t="s">
+        <v>520</v>
+      </c>
       <c r="H255" s="3" t="s">
         <v>52</v>
       </c>
@@ -9662,27 +9974,29 @@
         <v>302</v>
       </c>
       <c r="J255" s="3" t="s">
-        <v>524</v>
+        <v>537</v>
       </c>
     </row>
     <row r="256" customFormat="1" spans="1:10">
       <c r="A256" s="3"/>
       <c r="B256" s="3" t="s">
-        <v>525</v>
+        <v>538</v>
       </c>
       <c r="C256" s="4">
         <v>302</v>
       </c>
       <c r="D256" s="3" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="E256" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F256" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G256" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G256" s="3" t="s">
+        <v>520</v>
+      </c>
       <c r="H256" s="3" t="s">
         <v>55</v>
       </c>
@@ -9690,25 +10004,25 @@
         <v>302</v>
       </c>
       <c r="J256" s="3" t="s">
-        <v>526</v>
+        <v>539</v>
       </c>
     </row>
     <row r="258" customFormat="1" spans="1:10">
       <c r="A258" s="3"/>
       <c r="B258" s="3" t="s">
-        <v>527</v>
+        <v>540</v>
       </c>
       <c r="C258" s="4">
         <v>303</v>
       </c>
       <c r="D258" s="3" t="s">
-        <v>528</v>
+        <v>541</v>
       </c>
       <c r="E258" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F258" s="3" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="G258" s="3"/>
       <c r="H258" s="3" t="s">
@@ -9718,25 +10032,25 @@
         <v>303</v>
       </c>
       <c r="J258" s="3" t="s">
-        <v>529</v>
+        <v>542</v>
       </c>
     </row>
     <row r="259" customFormat="1" spans="1:10">
       <c r="A259" s="3"/>
       <c r="B259" s="3" t="s">
-        <v>530</v>
+        <v>543</v>
       </c>
       <c r="C259" s="4">
         <v>303</v>
       </c>
       <c r="D259" s="3" t="s">
-        <v>528</v>
+        <v>541</v>
       </c>
       <c r="E259" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F259" s="3" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="G259" s="3"/>
       <c r="H259" s="3" t="s">
@@ -9746,25 +10060,25 @@
         <v>303</v>
       </c>
       <c r="J259" s="3" t="s">
-        <v>531</v>
+        <v>544</v>
       </c>
     </row>
     <row r="260" customFormat="1" spans="1:10">
       <c r="A260" s="3"/>
       <c r="B260" s="3" t="s">
-        <v>532</v>
+        <v>545</v>
       </c>
       <c r="C260" s="4">
         <v>303</v>
       </c>
       <c r="D260" s="3" t="s">
-        <v>528</v>
+        <v>541</v>
       </c>
       <c r="E260" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F260" s="3" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="G260" s="3"/>
       <c r="H260" s="3" t="s">
@@ -9774,25 +10088,25 @@
         <v>303</v>
       </c>
       <c r="J260" s="3" t="s">
-        <v>533</v>
+        <v>546</v>
       </c>
     </row>
     <row r="261" customFormat="1" spans="1:10">
       <c r="A261" s="3"/>
       <c r="B261" s="3" t="s">
-        <v>534</v>
+        <v>547</v>
       </c>
       <c r="C261" s="4">
         <v>303</v>
       </c>
       <c r="D261" s="3" t="s">
-        <v>528</v>
+        <v>541</v>
       </c>
       <c r="E261" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F261" s="3" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="G261" s="3"/>
       <c r="H261" s="3" t="s">
@@ -9802,25 +10116,25 @@
         <v>303</v>
       </c>
       <c r="J261" s="3" t="s">
-        <v>535</v>
+        <v>548</v>
       </c>
     </row>
     <row r="262" customFormat="1" spans="1:10">
       <c r="A262" s="3"/>
       <c r="B262" s="3" t="s">
-        <v>536</v>
+        <v>549</v>
       </c>
       <c r="C262" s="4">
         <v>303</v>
       </c>
       <c r="D262" s="3" t="s">
-        <v>528</v>
+        <v>541</v>
       </c>
       <c r="E262" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F262" s="3" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="G262" s="3"/>
       <c r="H262" s="3" t="s">
@@ -9830,25 +10144,25 @@
         <v>303</v>
       </c>
       <c r="J262" s="3" t="s">
-        <v>537</v>
+        <v>550</v>
       </c>
     </row>
     <row r="263" customFormat="1" spans="1:10">
       <c r="A263" s="3"/>
       <c r="B263" s="3" t="s">
-        <v>538</v>
+        <v>551</v>
       </c>
       <c r="C263" s="4">
         <v>303</v>
       </c>
       <c r="D263" s="3" t="s">
-        <v>528</v>
+        <v>541</v>
       </c>
       <c r="E263" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F263" s="3" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="G263" s="3"/>
       <c r="H263" s="3" t="s">
@@ -9858,25 +10172,25 @@
         <v>303</v>
       </c>
       <c r="J263" s="3" t="s">
-        <v>539</v>
+        <v>552</v>
       </c>
     </row>
     <row r="264" customFormat="1" spans="1:10">
       <c r="A264" s="3"/>
       <c r="B264" s="3" t="s">
-        <v>540</v>
+        <v>553</v>
       </c>
       <c r="C264" s="4">
         <v>303</v>
       </c>
       <c r="D264" s="3" t="s">
-        <v>528</v>
+        <v>541</v>
       </c>
       <c r="E264" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F264" s="3" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="G264" s="3"/>
       <c r="H264" s="3" t="s">
@@ -9886,25 +10200,25 @@
         <v>303</v>
       </c>
       <c r="J264" s="3" t="s">
-        <v>541</v>
+        <v>554</v>
       </c>
     </row>
     <row r="265" customFormat="1" spans="1:10">
       <c r="A265" s="3"/>
       <c r="B265" s="3" t="s">
-        <v>542</v>
+        <v>555</v>
       </c>
       <c r="C265" s="4">
         <v>303</v>
       </c>
       <c r="D265" s="3" t="s">
-        <v>528</v>
+        <v>541</v>
       </c>
       <c r="E265" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F265" s="3" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="G265" s="3"/>
       <c r="H265" s="3" t="s">
@@ -9914,25 +10228,25 @@
         <v>303</v>
       </c>
       <c r="J265" s="3" t="s">
-        <v>543</v>
+        <v>556</v>
       </c>
     </row>
     <row r="266" customFormat="1" spans="1:10">
       <c r="A266" s="3"/>
       <c r="B266" s="3" t="s">
-        <v>544</v>
+        <v>557</v>
       </c>
       <c r="C266" s="4">
         <v>303</v>
       </c>
       <c r="D266" s="3" t="s">
-        <v>528</v>
+        <v>541</v>
       </c>
       <c r="E266" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F266" s="3" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="G266" s="3"/>
       <c r="H266" s="3" t="s">
@@ -9942,25 +10256,25 @@
         <v>303</v>
       </c>
       <c r="J266" s="3" t="s">
-        <v>545</v>
+        <v>558</v>
       </c>
     </row>
     <row r="267" customFormat="1" spans="1:10">
       <c r="A267" s="3"/>
       <c r="B267" s="3" t="s">
-        <v>546</v>
+        <v>559</v>
       </c>
       <c r="C267" s="4">
         <v>303</v>
       </c>
       <c r="D267" s="3" t="s">
-        <v>528</v>
+        <v>541</v>
       </c>
       <c r="E267" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F267" s="3" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="G267" s="3"/>
       <c r="H267" s="3" t="s">
@@ -9970,27 +10284,29 @@
         <v>303</v>
       </c>
       <c r="J267" s="3" t="s">
-        <v>547</v>
+        <v>560</v>
       </c>
     </row>
     <row r="269" customFormat="1" spans="1:10">
       <c r="A269" s="3"/>
       <c r="B269" s="3" t="s">
-        <v>548</v>
+        <v>561</v>
       </c>
       <c r="C269" s="4">
         <v>304</v>
       </c>
       <c r="D269" s="3" t="s">
-        <v>549</v>
+        <v>562</v>
       </c>
       <c r="E269" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F269" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G269" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G269" s="3" t="s">
+        <v>563</v>
+      </c>
       <c r="H269" s="3" t="s">
         <v>27</v>
       </c>
@@ -9998,27 +10314,29 @@
         <v>304</v>
       </c>
       <c r="J269" t="s">
-        <v>550</v>
+        <v>564</v>
       </c>
     </row>
     <row r="270" customFormat="1" spans="1:10">
       <c r="A270" s="3"/>
       <c r="B270" s="3" t="s">
-        <v>551</v>
+        <v>565</v>
       </c>
       <c r="C270" s="4">
         <v>304</v>
       </c>
       <c r="D270" s="3" t="s">
-        <v>549</v>
+        <v>562</v>
       </c>
       <c r="E270" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F270" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G270" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G270" s="3" t="s">
+        <v>563</v>
+      </c>
       <c r="H270" s="3" t="s">
         <v>31</v>
       </c>
@@ -10026,27 +10344,29 @@
         <v>304</v>
       </c>
       <c r="J270" t="s">
-        <v>552</v>
+        <v>566</v>
       </c>
     </row>
     <row r="271" customFormat="1" spans="1:10">
       <c r="A271" s="3"/>
       <c r="B271" s="3" t="s">
-        <v>553</v>
+        <v>567</v>
       </c>
       <c r="C271" s="4">
         <v>304</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>549</v>
+        <v>562</v>
       </c>
       <c r="E271" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F271" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G271" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G271" s="3" t="s">
+        <v>563</v>
+      </c>
       <c r="H271" s="3" t="s">
         <v>34</v>
       </c>
@@ -10054,27 +10374,29 @@
         <v>304</v>
       </c>
       <c r="J271" t="s">
-        <v>554</v>
+        <v>568</v>
       </c>
     </row>
     <row r="272" customFormat="1" spans="1:10">
       <c r="A272" s="3"/>
       <c r="B272" s="3" t="s">
-        <v>555</v>
+        <v>569</v>
       </c>
       <c r="C272" s="4">
         <v>304</v>
       </c>
       <c r="D272" s="3" t="s">
-        <v>549</v>
+        <v>562</v>
       </c>
       <c r="E272" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F272" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G272" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G272" s="3" t="s">
+        <v>563</v>
+      </c>
       <c r="H272" s="3" t="s">
         <v>37</v>
       </c>
@@ -10082,27 +10404,29 @@
         <v>304</v>
       </c>
       <c r="J272" t="s">
-        <v>556</v>
+        <v>570</v>
       </c>
     </row>
     <row r="273" customFormat="1" spans="1:10">
       <c r="A273" s="3"/>
       <c r="B273" s="3" t="s">
-        <v>557</v>
+        <v>571</v>
       </c>
       <c r="C273" s="4">
         <v>304</v>
       </c>
       <c r="D273" s="3" t="s">
-        <v>549</v>
+        <v>562</v>
       </c>
       <c r="E273" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F273" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G273" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G273" s="3" t="s">
+        <v>563</v>
+      </c>
       <c r="H273" s="3" t="s">
         <v>40</v>
       </c>
@@ -10110,27 +10434,29 @@
         <v>304</v>
       </c>
       <c r="J273" t="s">
-        <v>558</v>
+        <v>572</v>
       </c>
     </row>
     <row r="274" customFormat="1" spans="1:10">
       <c r="A274" s="3"/>
       <c r="B274" s="3" t="s">
-        <v>559</v>
+        <v>573</v>
       </c>
       <c r="C274" s="4">
         <v>304</v>
       </c>
       <c r="D274" s="3" t="s">
-        <v>549</v>
+        <v>562</v>
       </c>
       <c r="E274" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F274" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G274" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G274" s="3" t="s">
+        <v>563</v>
+      </c>
       <c r="H274" s="3" t="s">
         <v>43</v>
       </c>
@@ -10138,27 +10464,29 @@
         <v>304</v>
       </c>
       <c r="J274" t="s">
-        <v>560</v>
+        <v>574</v>
       </c>
     </row>
     <row r="275" customFormat="1" spans="1:10">
       <c r="A275" s="3"/>
       <c r="B275" s="3" t="s">
-        <v>561</v>
+        <v>575</v>
       </c>
       <c r="C275" s="4">
         <v>304</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>549</v>
+        <v>562</v>
       </c>
       <c r="E275" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F275" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G275" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G275" s="3" t="s">
+        <v>563</v>
+      </c>
       <c r="H275" s="3" t="s">
         <v>46</v>
       </c>
@@ -10166,27 +10494,29 @@
         <v>304</v>
       </c>
       <c r="J275" t="s">
-        <v>562</v>
+        <v>576</v>
       </c>
     </row>
     <row r="276" customFormat="1" spans="1:10">
       <c r="A276" s="3"/>
       <c r="B276" s="3" t="s">
-        <v>563</v>
+        <v>577</v>
       </c>
       <c r="C276" s="4">
         <v>304</v>
       </c>
       <c r="D276" s="3" t="s">
-        <v>549</v>
+        <v>562</v>
       </c>
       <c r="E276" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F276" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G276" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G276" s="3" t="s">
+        <v>563</v>
+      </c>
       <c r="H276" s="3" t="s">
         <v>49</v>
       </c>
@@ -10194,27 +10524,29 @@
         <v>304</v>
       </c>
       <c r="J276" t="s">
-        <v>564</v>
+        <v>578</v>
       </c>
     </row>
     <row r="277" customFormat="1" spans="1:10">
       <c r="A277" s="3"/>
       <c r="B277" s="3" t="s">
-        <v>565</v>
+        <v>579</v>
       </c>
       <c r="C277" s="4">
         <v>304</v>
       </c>
       <c r="D277" s="3" t="s">
-        <v>549</v>
+        <v>562</v>
       </c>
       <c r="E277" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F277" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G277" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G277" s="3" t="s">
+        <v>563</v>
+      </c>
       <c r="H277" s="3" t="s">
         <v>52</v>
       </c>
@@ -10222,27 +10554,29 @@
         <v>304</v>
       </c>
       <c r="J277" t="s">
-        <v>566</v>
+        <v>580</v>
       </c>
     </row>
     <row r="278" customFormat="1" spans="1:10">
       <c r="A278" s="3"/>
       <c r="B278" s="3" t="s">
-        <v>567</v>
+        <v>581</v>
       </c>
       <c r="C278" s="4">
         <v>304</v>
       </c>
       <c r="D278" s="3" t="s">
-        <v>549</v>
+        <v>562</v>
       </c>
       <c r="E278" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F278" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G278" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G278" s="3" t="s">
+        <v>563</v>
+      </c>
       <c r="H278" s="3" t="s">
         <v>55</v>
       </c>
@@ -10250,7 +10584,7 @@
         <v>304</v>
       </c>
       <c r="J278" t="s">
-        <v>568</v>
+        <v>582</v>
       </c>
     </row>
     <row r="279" spans="1:10">
@@ -10259,21 +10593,23 @@
     <row r="280" customFormat="1" spans="1:10">
       <c r="A280" s="3"/>
       <c r="B280" s="3" t="s">
-        <v>569</v>
+        <v>583</v>
       </c>
       <c r="C280" s="4">
         <v>305</v>
       </c>
       <c r="D280" s="3" t="s">
-        <v>570</v>
+        <v>584</v>
       </c>
       <c r="E280" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F280" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G280" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G280" s="3" t="s">
+        <v>585</v>
+      </c>
       <c r="H280" s="3" t="s">
         <v>27</v>
       </c>
@@ -10281,27 +10617,29 @@
         <v>305</v>
       </c>
       <c r="J280" s="3" t="s">
-        <v>571</v>
+        <v>586</v>
       </c>
     </row>
     <row r="281" customFormat="1" spans="1:10">
       <c r="A281" s="3"/>
       <c r="B281" s="3" t="s">
-        <v>572</v>
+        <v>587</v>
       </c>
       <c r="C281" s="4">
         <v>305</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>570</v>
+        <v>584</v>
       </c>
       <c r="E281" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F281" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G281" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G281" s="3" t="s">
+        <v>585</v>
+      </c>
       <c r="H281" s="3" t="s">
         <v>31</v>
       </c>
@@ -10309,27 +10647,29 @@
         <v>305</v>
       </c>
       <c r="J281" s="3" t="s">
-        <v>573</v>
+        <v>588</v>
       </c>
     </row>
     <row r="282" customFormat="1" spans="1:10">
       <c r="A282" s="3"/>
       <c r="B282" s="3" t="s">
-        <v>574</v>
+        <v>589</v>
       </c>
       <c r="C282" s="4">
         <v>305</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>570</v>
+        <v>584</v>
       </c>
       <c r="E282" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F282" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G282" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G282" s="3" t="s">
+        <v>585</v>
+      </c>
       <c r="H282" s="3" t="s">
         <v>34</v>
       </c>
@@ -10337,27 +10677,29 @@
         <v>305</v>
       </c>
       <c r="J282" s="3" t="s">
-        <v>575</v>
+        <v>590</v>
       </c>
     </row>
     <row r="283" customFormat="1" spans="1:10">
       <c r="A283" s="3"/>
       <c r="B283" s="3" t="s">
-        <v>576</v>
+        <v>591</v>
       </c>
       <c r="C283" s="4">
         <v>305</v>
       </c>
       <c r="D283" s="3" t="s">
-        <v>570</v>
+        <v>584</v>
       </c>
       <c r="E283" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F283" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G283" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G283" s="3" t="s">
+        <v>585</v>
+      </c>
       <c r="H283" s="3" t="s">
         <v>37</v>
       </c>
@@ -10365,27 +10707,29 @@
         <v>305</v>
       </c>
       <c r="J283" s="3" t="s">
-        <v>577</v>
+        <v>592</v>
       </c>
     </row>
     <row r="284" customFormat="1" spans="1:10">
       <c r="A284" s="3"/>
       <c r="B284" s="3" t="s">
-        <v>578</v>
+        <v>593</v>
       </c>
       <c r="C284" s="4">
         <v>305</v>
       </c>
       <c r="D284" s="3" t="s">
-        <v>570</v>
+        <v>584</v>
       </c>
       <c r="E284" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F284" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G284" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G284" s="3" t="s">
+        <v>585</v>
+      </c>
       <c r="H284" s="3" t="s">
         <v>40</v>
       </c>
@@ -10393,27 +10737,29 @@
         <v>305</v>
       </c>
       <c r="J284" s="3" t="s">
-        <v>579</v>
+        <v>594</v>
       </c>
     </row>
     <row r="285" customFormat="1" spans="1:10">
       <c r="A285" s="3"/>
       <c r="B285" s="3" t="s">
-        <v>580</v>
+        <v>595</v>
       </c>
       <c r="C285" s="4">
         <v>305</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>570</v>
+        <v>584</v>
       </c>
       <c r="E285" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F285" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G285" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G285" s="3" t="s">
+        <v>585</v>
+      </c>
       <c r="H285" s="3" t="s">
         <v>43</v>
       </c>
@@ -10421,27 +10767,29 @@
         <v>305</v>
       </c>
       <c r="J285" s="3" t="s">
-        <v>581</v>
+        <v>596</v>
       </c>
     </row>
     <row r="286" customFormat="1" spans="1:10">
       <c r="A286" s="3"/>
       <c r="B286" s="3" t="s">
-        <v>582</v>
+        <v>597</v>
       </c>
       <c r="C286" s="4">
         <v>305</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>570</v>
+        <v>584</v>
       </c>
       <c r="E286" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F286" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G286" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G286" s="3" t="s">
+        <v>585</v>
+      </c>
       <c r="H286" s="3" t="s">
         <v>46</v>
       </c>
@@ -10449,27 +10797,29 @@
         <v>305</v>
       </c>
       <c r="J286" s="3" t="s">
-        <v>583</v>
+        <v>598</v>
       </c>
     </row>
     <row r="287" customFormat="1" spans="1:10">
       <c r="A287" s="3"/>
       <c r="B287" s="3" t="s">
-        <v>584</v>
+        <v>599</v>
       </c>
       <c r="C287" s="4">
         <v>305</v>
       </c>
       <c r="D287" s="3" t="s">
-        <v>570</v>
+        <v>584</v>
       </c>
       <c r="E287" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F287" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G287" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G287" s="3" t="s">
+        <v>585</v>
+      </c>
       <c r="H287" s="3" t="s">
         <v>49</v>
       </c>
@@ -10477,27 +10827,29 @@
         <v>305</v>
       </c>
       <c r="J287" s="3" t="s">
-        <v>585</v>
+        <v>600</v>
       </c>
     </row>
     <row r="288" customFormat="1" spans="1:10">
       <c r="A288" s="3"/>
       <c r="B288" s="3" t="s">
-        <v>586</v>
+        <v>601</v>
       </c>
       <c r="C288" s="4">
         <v>305</v>
       </c>
       <c r="D288" s="3" t="s">
-        <v>570</v>
+        <v>584</v>
       </c>
       <c r="E288" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F288" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G288" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G288" s="3" t="s">
+        <v>585</v>
+      </c>
       <c r="H288" s="3" t="s">
         <v>52</v>
       </c>
@@ -10505,27 +10857,29 @@
         <v>305</v>
       </c>
       <c r="J288" s="3" t="s">
-        <v>587</v>
+        <v>602</v>
       </c>
     </row>
     <row r="289" customFormat="1" spans="1:10">
       <c r="A289" s="3"/>
       <c r="B289" s="3" t="s">
-        <v>588</v>
+        <v>603</v>
       </c>
       <c r="C289" s="4">
         <v>305</v>
       </c>
       <c r="D289" s="3" t="s">
-        <v>570</v>
+        <v>584</v>
       </c>
       <c r="E289" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F289" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G289" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G289" s="3" t="s">
+        <v>585</v>
+      </c>
       <c r="H289" s="3" t="s">
         <v>55</v>
       </c>
@@ -10533,27 +10887,29 @@
         <v>305</v>
       </c>
       <c r="J289" s="3" t="s">
-        <v>589</v>
+        <v>604</v>
       </c>
     </row>
     <row r="291" customFormat="1" spans="1:10">
       <c r="A291" s="3"/>
       <c r="B291" s="3" t="s">
-        <v>590</v>
+        <v>605</v>
       </c>
       <c r="C291" s="4">
         <v>306</v>
       </c>
       <c r="D291" s="3" t="s">
-        <v>591</v>
+        <v>606</v>
       </c>
       <c r="E291" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F291" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G291" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G291" s="3" t="s">
+        <v>607</v>
+      </c>
       <c r="H291" s="3" t="s">
         <v>27</v>
       </c>
@@ -10561,27 +10917,29 @@
         <v>306</v>
       </c>
       <c r="J291" s="3" t="s">
-        <v>592</v>
+        <v>608</v>
       </c>
     </row>
     <row r="292" customFormat="1" spans="1:10">
       <c r="A292" s="3"/>
       <c r="B292" s="3" t="s">
-        <v>593</v>
+        <v>609</v>
       </c>
       <c r="C292" s="4">
         <v>306</v>
       </c>
       <c r="D292" s="3" t="s">
-        <v>591</v>
+        <v>606</v>
       </c>
       <c r="E292" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F292" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G292" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G292" s="3" t="s">
+        <v>607</v>
+      </c>
       <c r="H292" s="3" t="s">
         <v>31</v>
       </c>
@@ -10589,27 +10947,29 @@
         <v>306</v>
       </c>
       <c r="J292" s="3" t="s">
-        <v>594</v>
+        <v>610</v>
       </c>
     </row>
     <row r="293" customFormat="1" spans="1:10">
       <c r="A293" s="3"/>
       <c r="B293" s="3" t="s">
-        <v>595</v>
+        <v>611</v>
       </c>
       <c r="C293" s="4">
         <v>306</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>591</v>
+        <v>606</v>
       </c>
       <c r="E293" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F293" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G293" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G293" s="3" t="s">
+        <v>607</v>
+      </c>
       <c r="H293" s="3" t="s">
         <v>34</v>
       </c>
@@ -10617,27 +10977,29 @@
         <v>306</v>
       </c>
       <c r="J293" s="3" t="s">
-        <v>596</v>
+        <v>612</v>
       </c>
     </row>
     <row r="294" customFormat="1" spans="1:10">
       <c r="A294" s="3"/>
       <c r="B294" s="3" t="s">
-        <v>597</v>
+        <v>613</v>
       </c>
       <c r="C294" s="4">
         <v>306</v>
       </c>
       <c r="D294" s="3" t="s">
-        <v>591</v>
+        <v>606</v>
       </c>
       <c r="E294" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F294" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G294" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G294" s="3" t="s">
+        <v>607</v>
+      </c>
       <c r="H294" s="3" t="s">
         <v>37</v>
       </c>
@@ -10645,27 +11007,29 @@
         <v>306</v>
       </c>
       <c r="J294" s="3" t="s">
-        <v>598</v>
+        <v>614</v>
       </c>
     </row>
     <row r="295" customFormat="1" spans="1:10">
       <c r="A295" s="3"/>
       <c r="B295" s="3" t="s">
-        <v>599</v>
+        <v>615</v>
       </c>
       <c r="C295" s="4">
         <v>306</v>
       </c>
       <c r="D295" s="3" t="s">
-        <v>591</v>
+        <v>606</v>
       </c>
       <c r="E295" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F295" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G295" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G295" s="3" t="s">
+        <v>607</v>
+      </c>
       <c r="H295" s="3" t="s">
         <v>40</v>
       </c>
@@ -10673,27 +11037,29 @@
         <v>306</v>
       </c>
       <c r="J295" s="3" t="s">
-        <v>600</v>
+        <v>616</v>
       </c>
     </row>
     <row r="296" customFormat="1" spans="1:10">
       <c r="A296" s="3"/>
       <c r="B296" s="3" t="s">
-        <v>601</v>
+        <v>617</v>
       </c>
       <c r="C296" s="4">
         <v>306</v>
       </c>
       <c r="D296" s="3" t="s">
-        <v>591</v>
+        <v>606</v>
       </c>
       <c r="E296" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F296" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G296" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G296" s="3" t="s">
+        <v>607</v>
+      </c>
       <c r="H296" s="3" t="s">
         <v>43</v>
       </c>
@@ -10701,27 +11067,29 @@
         <v>306</v>
       </c>
       <c r="J296" s="3" t="s">
-        <v>602</v>
+        <v>618</v>
       </c>
     </row>
     <row r="297" customFormat="1" spans="1:10">
       <c r="A297" s="3"/>
       <c r="B297" s="3" t="s">
-        <v>603</v>
+        <v>619</v>
       </c>
       <c r="C297" s="4">
         <v>306</v>
       </c>
       <c r="D297" s="3" t="s">
-        <v>591</v>
+        <v>606</v>
       </c>
       <c r="E297" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F297" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G297" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G297" s="3" t="s">
+        <v>607</v>
+      </c>
       <c r="H297" s="3" t="s">
         <v>46</v>
       </c>
@@ -10729,27 +11097,29 @@
         <v>306</v>
       </c>
       <c r="J297" s="3" t="s">
-        <v>604</v>
+        <v>620</v>
       </c>
     </row>
     <row r="298" customFormat="1" spans="1:10">
       <c r="A298" s="3"/>
       <c r="B298" s="3" t="s">
-        <v>605</v>
+        <v>621</v>
       </c>
       <c r="C298" s="4">
         <v>306</v>
       </c>
       <c r="D298" s="3" t="s">
-        <v>591</v>
+        <v>606</v>
       </c>
       <c r="E298" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F298" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G298" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G298" s="3" t="s">
+        <v>607</v>
+      </c>
       <c r="H298" s="3" t="s">
         <v>49</v>
       </c>
@@ -10757,27 +11127,29 @@
         <v>306</v>
       </c>
       <c r="J298" s="3" t="s">
-        <v>606</v>
+        <v>622</v>
       </c>
     </row>
     <row r="299" customFormat="1" spans="1:10">
       <c r="A299" s="3"/>
       <c r="B299" s="3" t="s">
-        <v>607</v>
+        <v>623</v>
       </c>
       <c r="C299" s="4">
         <v>306</v>
       </c>
       <c r="D299" s="3" t="s">
-        <v>591</v>
+        <v>606</v>
       </c>
       <c r="E299" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F299" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G299" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G299" s="3" t="s">
+        <v>607</v>
+      </c>
       <c r="H299" s="3" t="s">
         <v>52</v>
       </c>
@@ -10785,27 +11157,29 @@
         <v>306</v>
       </c>
       <c r="J299" s="3" t="s">
-        <v>608</v>
+        <v>624</v>
       </c>
     </row>
     <row r="300" customFormat="1" spans="1:10">
       <c r="A300" s="3"/>
       <c r="B300" s="3" t="s">
-        <v>609</v>
+        <v>625</v>
       </c>
       <c r="C300" s="4">
         <v>306</v>
       </c>
       <c r="D300" s="3" t="s">
-        <v>591</v>
+        <v>606</v>
       </c>
       <c r="E300" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F300" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G300" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G300" s="3" t="s">
+        <v>607</v>
+      </c>
       <c r="H300" s="3" t="s">
         <v>55</v>
       </c>
@@ -10813,27 +11187,29 @@
         <v>306</v>
       </c>
       <c r="J300" s="3" t="s">
-        <v>610</v>
+        <v>626</v>
       </c>
     </row>
     <row r="302" customFormat="1" spans="1:10">
       <c r="A302" s="3"/>
       <c r="B302" s="3" t="s">
-        <v>611</v>
+        <v>627</v>
       </c>
       <c r="C302" s="4">
         <v>307</v>
       </c>
       <c r="D302" s="3" t="s">
-        <v>612</v>
+        <v>628</v>
       </c>
       <c r="E302" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F302" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G302" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G302" s="3" t="s">
+        <v>629</v>
+      </c>
       <c r="H302" s="3" t="s">
         <v>27</v>
       </c>
@@ -10841,27 +11217,29 @@
         <v>307</v>
       </c>
       <c r="J302" s="3" t="s">
-        <v>613</v>
+        <v>630</v>
       </c>
     </row>
     <row r="303" customFormat="1" spans="1:10">
       <c r="A303" s="3"/>
       <c r="B303" s="3" t="s">
-        <v>614</v>
+        <v>631</v>
       </c>
       <c r="C303" s="4">
         <v>307</v>
       </c>
       <c r="D303" s="3" t="s">
-        <v>612</v>
+        <v>628</v>
       </c>
       <c r="E303" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F303" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G303" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G303" s="3" t="s">
+        <v>629</v>
+      </c>
       <c r="H303" s="3" t="s">
         <v>31</v>
       </c>
@@ -10869,27 +11247,29 @@
         <v>307</v>
       </c>
       <c r="J303" s="3" t="s">
-        <v>615</v>
+        <v>632</v>
       </c>
     </row>
     <row r="304" customFormat="1" spans="1:10">
       <c r="A304" s="3"/>
       <c r="B304" s="3" t="s">
-        <v>616</v>
+        <v>633</v>
       </c>
       <c r="C304" s="4">
         <v>307</v>
       </c>
       <c r="D304" s="3" t="s">
-        <v>612</v>
+        <v>628</v>
       </c>
       <c r="E304" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F304" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G304" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G304" s="3" t="s">
+        <v>629</v>
+      </c>
       <c r="H304" s="3" t="s">
         <v>34</v>
       </c>
@@ -10897,27 +11277,29 @@
         <v>307</v>
       </c>
       <c r="J304" s="3" t="s">
-        <v>617</v>
+        <v>634</v>
       </c>
     </row>
     <row r="305" customFormat="1" spans="1:10">
       <c r="A305" s="3"/>
       <c r="B305" s="3" t="s">
-        <v>618</v>
+        <v>635</v>
       </c>
       <c r="C305" s="4">
         <v>307</v>
       </c>
       <c r="D305" s="3" t="s">
-        <v>612</v>
+        <v>628</v>
       </c>
       <c r="E305" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F305" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G305" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G305" s="3" t="s">
+        <v>629</v>
+      </c>
       <c r="H305" s="3" t="s">
         <v>37</v>
       </c>
@@ -10925,27 +11307,29 @@
         <v>307</v>
       </c>
       <c r="J305" s="3" t="s">
-        <v>619</v>
+        <v>636</v>
       </c>
     </row>
     <row r="306" customFormat="1" spans="1:10">
       <c r="A306" s="3"/>
       <c r="B306" s="3" t="s">
-        <v>620</v>
+        <v>637</v>
       </c>
       <c r="C306" s="4">
         <v>307</v>
       </c>
       <c r="D306" s="3" t="s">
-        <v>612</v>
+        <v>628</v>
       </c>
       <c r="E306" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F306" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G306" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G306" s="3" t="s">
+        <v>629</v>
+      </c>
       <c r="H306" s="3" t="s">
         <v>40</v>
       </c>
@@ -10953,27 +11337,29 @@
         <v>307</v>
       </c>
       <c r="J306" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
     </row>
     <row r="307" customFormat="1" spans="1:10">
       <c r="A307" s="3"/>
       <c r="B307" s="3" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="C307" s="4">
         <v>307</v>
       </c>
       <c r="D307" s="3" t="s">
-        <v>612</v>
+        <v>628</v>
       </c>
       <c r="E307" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F307" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G307" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G307" s="3" t="s">
+        <v>629</v>
+      </c>
       <c r="H307" s="3" t="s">
         <v>43</v>
       </c>
@@ -10981,27 +11367,29 @@
         <v>307</v>
       </c>
       <c r="J307" s="3" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="308" customFormat="1" spans="1:10">
       <c r="A308" s="3"/>
       <c r="B308" s="3" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="C308" s="4">
         <v>307</v>
       </c>
       <c r="D308" s="3" t="s">
-        <v>612</v>
+        <v>628</v>
       </c>
       <c r="E308" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F308" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G308" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G308" s="3" t="s">
+        <v>629</v>
+      </c>
       <c r="H308" s="3" t="s">
         <v>46</v>
       </c>
@@ -11009,27 +11397,29 @@
         <v>307</v>
       </c>
       <c r="J308" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
     </row>
     <row r="309" customFormat="1" spans="1:10">
       <c r="A309" s="3"/>
       <c r="B309" s="3" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
       <c r="C309" s="4">
         <v>307</v>
       </c>
       <c r="D309" s="3" t="s">
-        <v>612</v>
+        <v>628</v>
       </c>
       <c r="E309" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F309" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G309" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G309" s="3" t="s">
+        <v>629</v>
+      </c>
       <c r="H309" s="3" t="s">
         <v>49</v>
       </c>
@@ -11037,27 +11427,29 @@
         <v>307</v>
       </c>
       <c r="J309" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="310" customFormat="1" spans="1:10">
       <c r="A310" s="3"/>
       <c r="B310" s="3" t="s">
-        <v>628</v>
+        <v>645</v>
       </c>
       <c r="C310" s="4">
         <v>307</v>
       </c>
       <c r="D310" s="3" t="s">
-        <v>612</v>
+        <v>628</v>
       </c>
       <c r="E310" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F310" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G310" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G310" s="3" t="s">
+        <v>629</v>
+      </c>
       <c r="H310" s="3" t="s">
         <v>52</v>
       </c>
@@ -11065,27 +11457,29 @@
         <v>307</v>
       </c>
       <c r="J310" s="3" t="s">
-        <v>629</v>
+        <v>646</v>
       </c>
     </row>
     <row r="311" customFormat="1" spans="1:10">
       <c r="A311" s="3"/>
       <c r="B311" s="3" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="C311" s="4">
         <v>307</v>
       </c>
       <c r="D311" s="3" t="s">
-        <v>612</v>
+        <v>628</v>
       </c>
       <c r="E311" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F311" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G311" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G311" s="3" t="s">
+        <v>629</v>
+      </c>
       <c r="H311" s="3" t="s">
         <v>55</v>
       </c>
@@ -11093,27 +11487,29 @@
         <v>307</v>
       </c>
       <c r="J311" s="3" t="s">
-        <v>631</v>
+        <v>648</v>
       </c>
     </row>
     <row r="313" customFormat="1" spans="1:10">
       <c r="A313" s="3"/>
       <c r="B313" s="3" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
       <c r="C313" s="4">
         <v>308</v>
       </c>
       <c r="D313" s="3" t="s">
-        <v>633</v>
+        <v>650</v>
       </c>
       <c r="E313" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F313" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G313" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G313" s="3" t="s">
+        <v>651</v>
+      </c>
       <c r="H313" s="3" t="s">
         <v>27</v>
       </c>
@@ -11121,27 +11517,29 @@
         <v>308</v>
       </c>
       <c r="J313" s="3" t="s">
-        <v>634</v>
+        <v>652</v>
       </c>
     </row>
     <row r="314" customFormat="1" spans="1:10">
       <c r="A314" s="3"/>
       <c r="B314" s="3" t="s">
-        <v>635</v>
+        <v>653</v>
       </c>
       <c r="C314" s="4">
         <v>308</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>633</v>
+        <v>650</v>
       </c>
       <c r="E314" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F314" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G314" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G314" s="3" t="s">
+        <v>651</v>
+      </c>
       <c r="H314" s="3" t="s">
         <v>31</v>
       </c>
@@ -11149,27 +11547,29 @@
         <v>308</v>
       </c>
       <c r="J314" s="3" t="s">
-        <v>636</v>
+        <v>654</v>
       </c>
     </row>
     <row r="315" customFormat="1" spans="1:10">
       <c r="A315" s="3"/>
       <c r="B315" s="3" t="s">
-        <v>637</v>
+        <v>655</v>
       </c>
       <c r="C315" s="4">
         <v>308</v>
       </c>
       <c r="D315" s="3" t="s">
-        <v>633</v>
+        <v>650</v>
       </c>
       <c r="E315" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F315" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G315" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G315" s="3" t="s">
+        <v>651</v>
+      </c>
       <c r="H315" s="3" t="s">
         <v>34</v>
       </c>
@@ -11177,27 +11577,29 @@
         <v>308</v>
       </c>
       <c r="J315" s="3" t="s">
-        <v>638</v>
+        <v>656</v>
       </c>
     </row>
     <row r="316" customFormat="1" spans="1:10">
       <c r="A316" s="3"/>
       <c r="B316" s="3" t="s">
-        <v>639</v>
+        <v>657</v>
       </c>
       <c r="C316" s="4">
         <v>308</v>
       </c>
       <c r="D316" s="3" t="s">
-        <v>633</v>
+        <v>650</v>
       </c>
       <c r="E316" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F316" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G316" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G316" s="3" t="s">
+        <v>651</v>
+      </c>
       <c r="H316" s="3" t="s">
         <v>37</v>
       </c>
@@ -11205,27 +11607,29 @@
         <v>308</v>
       </c>
       <c r="J316" s="3" t="s">
-        <v>640</v>
+        <v>658</v>
       </c>
     </row>
     <row r="317" customFormat="1" spans="1:10">
       <c r="A317" s="3"/>
       <c r="B317" s="3" t="s">
-        <v>641</v>
+        <v>659</v>
       </c>
       <c r="C317" s="4">
         <v>308</v>
       </c>
       <c r="D317" s="3" t="s">
-        <v>633</v>
+        <v>650</v>
       </c>
       <c r="E317" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F317" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G317" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G317" s="3" t="s">
+        <v>651</v>
+      </c>
       <c r="H317" s="3" t="s">
         <v>40</v>
       </c>
@@ -11233,27 +11637,29 @@
         <v>308</v>
       </c>
       <c r="J317" s="3" t="s">
-        <v>642</v>
+        <v>660</v>
       </c>
     </row>
     <row r="318" customFormat="1" spans="1:10">
       <c r="A318" s="3"/>
       <c r="B318" s="3" t="s">
-        <v>643</v>
+        <v>661</v>
       </c>
       <c r="C318" s="4">
         <v>308</v>
       </c>
       <c r="D318" s="3" t="s">
-        <v>633</v>
+        <v>650</v>
       </c>
       <c r="E318" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F318" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G318" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G318" s="3" t="s">
+        <v>651</v>
+      </c>
       <c r="H318" s="3" t="s">
         <v>43</v>
       </c>
@@ -11261,27 +11667,29 @@
         <v>308</v>
       </c>
       <c r="J318" s="3" t="s">
-        <v>644</v>
+        <v>662</v>
       </c>
     </row>
     <row r="319" customFormat="1" spans="1:10">
       <c r="A319" s="3"/>
       <c r="B319" s="3" t="s">
-        <v>645</v>
+        <v>663</v>
       </c>
       <c r="C319" s="4">
         <v>308</v>
       </c>
       <c r="D319" s="3" t="s">
-        <v>633</v>
+        <v>650</v>
       </c>
       <c r="E319" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F319" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G319" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G319" s="3" t="s">
+        <v>651</v>
+      </c>
       <c r="H319" s="3" t="s">
         <v>46</v>
       </c>
@@ -11289,27 +11697,29 @@
         <v>308</v>
       </c>
       <c r="J319" s="3" t="s">
-        <v>646</v>
+        <v>664</v>
       </c>
     </row>
     <row r="320" customFormat="1" spans="1:10">
       <c r="A320" s="3"/>
       <c r="B320" s="3" t="s">
-        <v>647</v>
+        <v>665</v>
       </c>
       <c r="C320" s="4">
         <v>308</v>
       </c>
       <c r="D320" s="3" t="s">
-        <v>633</v>
+        <v>650</v>
       </c>
       <c r="E320" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F320" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G320" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G320" s="3" t="s">
+        <v>651</v>
+      </c>
       <c r="H320" s="3" t="s">
         <v>49</v>
       </c>
@@ -11317,27 +11727,29 @@
         <v>308</v>
       </c>
       <c r="J320" s="3" t="s">
-        <v>648</v>
+        <v>666</v>
       </c>
     </row>
     <row r="321" customFormat="1" spans="1:11">
       <c r="A321" s="3"/>
       <c r="B321" s="3" t="s">
-        <v>649</v>
+        <v>667</v>
       </c>
       <c r="C321" s="4">
         <v>308</v>
       </c>
       <c r="D321" s="3" t="s">
-        <v>633</v>
+        <v>650</v>
       </c>
       <c r="E321" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F321" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G321" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G321" s="3" t="s">
+        <v>651</v>
+      </c>
       <c r="H321" s="3" t="s">
         <v>52</v>
       </c>
@@ -11345,27 +11757,29 @@
         <v>308</v>
       </c>
       <c r="J321" s="3" t="s">
-        <v>650</v>
+        <v>668</v>
       </c>
     </row>
     <row r="322" customFormat="1" spans="1:11">
       <c r="A322" s="3"/>
       <c r="B322" s="3" t="s">
-        <v>651</v>
+        <v>669</v>
       </c>
       <c r="C322" s="4">
         <v>308</v>
       </c>
       <c r="D322" s="3" t="s">
-        <v>633</v>
+        <v>650</v>
       </c>
       <c r="E322" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F322" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="G322" s="3"/>
+        <v>497</v>
+      </c>
+      <c r="G322" s="3" t="s">
+        <v>651</v>
+      </c>
       <c r="H322" s="3" t="s">
         <v>55</v>
       </c>
@@ -11373,25 +11787,25 @@
         <v>308</v>
       </c>
       <c r="J322" s="3" t="s">
-        <v>652</v>
+        <v>670</v>
       </c>
     </row>
     <row r="324" s="1" customFormat="1" spans="1:11">
       <c r="A324" s="2"/>
       <c r="B324" s="2" t="s">
-        <v>653</v>
+        <v>671</v>
       </c>
       <c r="C324" s="5">
         <v>309</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>654</v>
+        <v>672</v>
       </c>
       <c r="E324" s="2" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F324" s="2" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="G324" s="2"/>
       <c r="H324" s="2" t="s">
@@ -11401,25 +11815,25 @@
         <v>309</v>
       </c>
       <c r="J324" s="1" t="s">
-        <v>655</v>
+        <v>673</v>
       </c>
     </row>
     <row r="325" s="1" customFormat="1" spans="1:11">
       <c r="A325" s="2"/>
       <c r="B325" s="2" t="s">
-        <v>656</v>
+        <v>674</v>
       </c>
       <c r="C325" s="5">
         <v>309</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>654</v>
+        <v>672</v>
       </c>
       <c r="E325" s="2" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F325" s="2" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="G325" s="2"/>
       <c r="H325" s="2" t="s">
@@ -11429,25 +11843,25 @@
         <v>309</v>
       </c>
       <c r="J325" s="1" t="s">
-        <v>657</v>
+        <v>675</v>
       </c>
     </row>
     <row r="326" s="1" customFormat="1" spans="1:11">
       <c r="A326" s="2"/>
       <c r="B326" s="2" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="C326" s="5">
         <v>309</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>654</v>
+        <v>672</v>
       </c>
       <c r="E326" s="2" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F326" s="2" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="G326" s="2"/>
       <c r="H326" s="2" t="s">
@@ -11457,25 +11871,25 @@
         <v>309</v>
       </c>
       <c r="J326" s="1" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="327" s="1" customFormat="1" spans="1:11">
       <c r="A327" s="2"/>
       <c r="B327" s="2" t="s">
-        <v>660</v>
+        <v>678</v>
       </c>
       <c r="C327" s="5">
         <v>309</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>654</v>
+        <v>672</v>
       </c>
       <c r="E327" s="2" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F327" s="2" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="G327" s="2"/>
       <c r="H327" s="2" t="s">
@@ -11485,25 +11899,25 @@
         <v>309</v>
       </c>
       <c r="J327" s="1" t="s">
-        <v>661</v>
+        <v>679</v>
       </c>
     </row>
     <row r="328" s="1" customFormat="1" spans="1:11">
       <c r="A328" s="2"/>
       <c r="B328" s="2" t="s">
-        <v>662</v>
+        <v>680</v>
       </c>
       <c r="C328" s="5">
         <v>309</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>654</v>
+        <v>672</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F328" s="2" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="G328" s="2"/>
       <c r="H328" s="2" t="s">
@@ -11513,25 +11927,25 @@
         <v>309</v>
       </c>
       <c r="J328" s="1" t="s">
-        <v>663</v>
+        <v>681</v>
       </c>
     </row>
     <row r="329" s="1" customFormat="1" spans="1:11">
       <c r="A329" s="2"/>
       <c r="B329" s="2" t="s">
-        <v>664</v>
+        <v>682</v>
       </c>
       <c r="C329" s="5">
         <v>309</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>654</v>
+        <v>672</v>
       </c>
       <c r="E329" s="2" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F329" s="2" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="G329" s="2"/>
       <c r="H329" s="2" t="s">
@@ -11541,25 +11955,25 @@
         <v>309</v>
       </c>
       <c r="J329" s="1" t="s">
-        <v>665</v>
+        <v>683</v>
       </c>
     </row>
     <row r="330" s="1" customFormat="1" spans="1:11">
       <c r="A330" s="2"/>
       <c r="B330" s="2" t="s">
-        <v>666</v>
+        <v>684</v>
       </c>
       <c r="C330" s="5">
         <v>309</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>654</v>
+        <v>672</v>
       </c>
       <c r="E330" s="2" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F330" s="2" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="G330" s="2"/>
       <c r="H330" s="2" t="s">
@@ -11569,25 +11983,25 @@
         <v>309</v>
       </c>
       <c r="J330" s="1" t="s">
-        <v>667</v>
+        <v>685</v>
       </c>
     </row>
     <row r="331" s="1" customFormat="1" spans="1:11">
       <c r="A331" s="2"/>
       <c r="B331" s="2" t="s">
-        <v>668</v>
+        <v>686</v>
       </c>
       <c r="C331" s="5">
         <v>309</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>654</v>
+        <v>672</v>
       </c>
       <c r="E331" s="2" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F331" s="2" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="G331" s="2"/>
       <c r="H331" s="2" t="s">
@@ -11597,25 +12011,25 @@
         <v>309</v>
       </c>
       <c r="J331" s="1" t="s">
-        <v>669</v>
+        <v>687</v>
       </c>
     </row>
     <row r="332" s="1" customFormat="1" spans="1:11">
       <c r="A332" s="2"/>
       <c r="B332" s="2" t="s">
-        <v>670</v>
+        <v>688</v>
       </c>
       <c r="C332" s="5">
         <v>309</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>654</v>
+        <v>672</v>
       </c>
       <c r="E332" s="2" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F332" s="2" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="G332" s="2"/>
       <c r="H332" s="2" t="s">
@@ -11625,25 +12039,25 @@
         <v>309</v>
       </c>
       <c r="J332" s="1" t="s">
-        <v>671</v>
+        <v>689</v>
       </c>
     </row>
     <row r="333" s="1" customFormat="1" spans="1:11">
       <c r="A333" s="2"/>
       <c r="B333" s="2" t="s">
-        <v>672</v>
+        <v>690</v>
       </c>
       <c r="C333" s="5">
         <v>309</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>654</v>
+        <v>672</v>
       </c>
       <c r="E333" s="2" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F333" s="2" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="G333" s="2"/>
       <c r="H333" s="2" t="s">
@@ -11653,7 +12067,7 @@
         <v>309</v>
       </c>
       <c r="J333" s="1" t="s">
-        <v>673</v>
+        <v>691</v>
       </c>
     </row>
     <row r="334" s="2" customFormat="1" spans="1:11">
@@ -11670,19 +12084,19 @@
     <row r="335" s="1" customFormat="1" spans="1:11">
       <c r="A335" s="2"/>
       <c r="B335" s="2" t="s">
-        <v>674</v>
+        <v>692</v>
       </c>
       <c r="C335" s="5">
         <v>310</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>675</v>
+        <v>693</v>
       </c>
       <c r="E335" s="2" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F335" s="2" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="G335" s="2"/>
       <c r="H335" s="2" t="s">
@@ -11692,25 +12106,25 @@
         <v>310</v>
       </c>
       <c r="J335" s="1" t="s">
-        <v>676</v>
+        <v>694</v>
       </c>
     </row>
     <row r="336" s="1" customFormat="1" spans="1:11">
       <c r="A336" s="2"/>
       <c r="B336" s="2" t="s">
-        <v>677</v>
+        <v>695</v>
       </c>
       <c r="C336" s="5">
         <v>310</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>675</v>
+        <v>693</v>
       </c>
       <c r="E336" s="2" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F336" s="2" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="G336" s="2"/>
       <c r="H336" s="2" t="s">
@@ -11720,25 +12134,25 @@
         <v>310</v>
       </c>
       <c r="J336" s="1" t="s">
-        <v>678</v>
+        <v>696</v>
       </c>
     </row>
     <row r="337" s="1" customFormat="1" spans="1:10">
       <c r="A337" s="2"/>
       <c r="B337" s="2" t="s">
-        <v>679</v>
+        <v>697</v>
       </c>
       <c r="C337" s="5">
         <v>310</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>675</v>
+        <v>693</v>
       </c>
       <c r="E337" s="2" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F337" s="2" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="G337" s="2"/>
       <c r="H337" s="2" t="s">
@@ -11748,25 +12162,25 @@
         <v>310</v>
       </c>
       <c r="J337" s="1" t="s">
-        <v>680</v>
+        <v>698</v>
       </c>
     </row>
     <row r="338" s="1" customFormat="1" spans="1:10">
       <c r="A338" s="2"/>
       <c r="B338" s="2" t="s">
-        <v>681</v>
+        <v>699</v>
       </c>
       <c r="C338" s="5">
         <v>310</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>675</v>
+        <v>693</v>
       </c>
       <c r="E338" s="2" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F338" s="2" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="G338" s="2"/>
       <c r="H338" s="2" t="s">
@@ -11776,25 +12190,25 @@
         <v>310</v>
       </c>
       <c r="J338" s="1" t="s">
-        <v>682</v>
+        <v>700</v>
       </c>
     </row>
     <row r="339" s="1" customFormat="1" spans="1:10">
       <c r="A339" s="2"/>
       <c r="B339" s="2" t="s">
-        <v>683</v>
+        <v>701</v>
       </c>
       <c r="C339" s="5">
         <v>310</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>675</v>
+        <v>693</v>
       </c>
       <c r="E339" s="2" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F339" s="2" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="G339" s="2"/>
       <c r="H339" s="2" t="s">
@@ -11804,25 +12218,25 @@
         <v>310</v>
       </c>
       <c r="J339" s="1" t="s">
-        <v>684</v>
+        <v>702</v>
       </c>
     </row>
     <row r="340" s="1" customFormat="1" spans="1:10">
       <c r="A340" s="2"/>
       <c r="B340" s="2" t="s">
-        <v>685</v>
+        <v>703</v>
       </c>
       <c r="C340" s="5">
         <v>310</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>675</v>
+        <v>693</v>
       </c>
       <c r="E340" s="2" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F340" s="2" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="G340" s="2"/>
       <c r="H340" s="2" t="s">
@@ -11832,25 +12246,25 @@
         <v>310</v>
       </c>
       <c r="J340" s="1" t="s">
-        <v>686</v>
+        <v>704</v>
       </c>
     </row>
     <row r="341" s="1" customFormat="1" spans="1:10">
       <c r="A341" s="2"/>
       <c r="B341" s="2" t="s">
-        <v>687</v>
+        <v>705</v>
       </c>
       <c r="C341" s="5">
         <v>310</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>675</v>
+        <v>693</v>
       </c>
       <c r="E341" s="2" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F341" s="2" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="G341" s="2"/>
       <c r="H341" s="2" t="s">
@@ -11860,25 +12274,25 @@
         <v>310</v>
       </c>
       <c r="J341" s="1" t="s">
-        <v>688</v>
+        <v>706</v>
       </c>
     </row>
     <row r="342" s="1" customFormat="1" spans="1:10">
       <c r="A342" s="2"/>
       <c r="B342" s="2" t="s">
-        <v>689</v>
+        <v>707</v>
       </c>
       <c r="C342" s="5">
         <v>310</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>675</v>
+        <v>693</v>
       </c>
       <c r="E342" s="2" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F342" s="2" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="G342" s="2"/>
       <c r="H342" s="2" t="s">
@@ -11888,25 +12302,25 @@
         <v>310</v>
       </c>
       <c r="J342" s="1" t="s">
-        <v>690</v>
+        <v>708</v>
       </c>
     </row>
     <row r="343" s="1" customFormat="1" spans="1:10">
       <c r="A343" s="2"/>
       <c r="B343" s="2" t="s">
-        <v>691</v>
+        <v>709</v>
       </c>
       <c r="C343" s="5">
         <v>310</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>675</v>
+        <v>693</v>
       </c>
       <c r="E343" s="2" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F343" s="2" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="G343" s="2"/>
       <c r="H343" s="2" t="s">
@@ -11916,25 +12330,25 @@
         <v>310</v>
       </c>
       <c r="J343" s="1" t="s">
-        <v>692</v>
+        <v>710</v>
       </c>
     </row>
     <row r="344" s="1" customFormat="1" spans="1:10">
       <c r="A344" s="2"/>
       <c r="B344" s="2" t="s">
-        <v>693</v>
+        <v>711</v>
       </c>
       <c r="C344" s="5">
         <v>310</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>675</v>
+        <v>693</v>
       </c>
       <c r="E344" s="2" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F344" s="2" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="G344" s="2"/>
       <c r="H344" s="2" t="s">
@@ -11944,7 +12358,7 @@
         <v>310</v>
       </c>
       <c r="J344" s="1" t="s">
-        <v>694</v>
+        <v>712</v>
       </c>
     </row>
   </sheetData>

--- a/Config/TalentConfig.xlsx
+++ b/Config/TalentConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="8205" windowHeight="10740"/>
+    <workbookView windowWidth="16380" windowHeight="7635"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>

--- a/Config/TalentConfig.xlsx
+++ b/Config/TalentConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="16590" windowHeight="10440"/>
+    <workbookView windowWidth="17355" windowHeight="11655"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2220" uniqueCount="723">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2250" uniqueCount="726">
   <si>
     <t>##var</t>
   </si>
@@ -1486,6 +1486,9 @@
     <t>史诗圣物</t>
   </si>
   <si>
+    <t>EpicSacredRelic</t>
+  </si>
+  <si>
     <t>商店中出现史诗品质圣物的概率+0.2%</t>
   </si>
   <si>
@@ -2083,6 +2086,9 @@
     <t>传说圣物</t>
   </si>
   <si>
+    <t>LegendSacredRelic</t>
+  </si>
+  <si>
     <t>商店中出现传说品质圣物的概率+0.2%</t>
   </si>
   <si>
@@ -2144,6 +2150,9 @@
   </si>
   <si>
     <t>圣物容量</t>
+  </si>
+  <si>
+    <t>SacredRelicCapacity</t>
   </si>
   <si>
     <t>允许携带的圣物容量+1</t>
@@ -9342,7 +9351,9 @@
       <c r="F225" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="G225" s="2"/>
+      <c r="G225" s="2" t="s">
+        <v>484</v>
+      </c>
       <c r="H225" s="2" t="s">
         <v>28</v>
       </c>
@@ -9350,13 +9361,13 @@
         <v>209</v>
       </c>
       <c r="J225" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="226" s="1" customFormat="1" spans="1:10">
       <c r="A226" s="2"/>
       <c r="B226" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C226" s="5">
         <v>209</v>
@@ -9370,7 +9381,9 @@
       <c r="F226" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="G226" s="2"/>
+      <c r="G226" s="2" t="s">
+        <v>484</v>
+      </c>
       <c r="H226" s="2" t="s">
         <v>32</v>
       </c>
@@ -9378,13 +9391,13 @@
         <v>209</v>
       </c>
       <c r="J226" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="227" s="1" customFormat="1" spans="1:10">
       <c r="A227" s="2"/>
       <c r="B227" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C227" s="5">
         <v>209</v>
@@ -9398,7 +9411,9 @@
       <c r="F227" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="G227" s="2"/>
+      <c r="G227" s="2" t="s">
+        <v>484</v>
+      </c>
       <c r="H227" s="2" t="s">
         <v>35</v>
       </c>
@@ -9406,13 +9421,13 @@
         <v>209</v>
       </c>
       <c r="J227" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="228" s="1" customFormat="1" spans="1:10">
       <c r="A228" s="2"/>
       <c r="B228" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C228" s="5">
         <v>209</v>
@@ -9426,7 +9441,9 @@
       <c r="F228" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="G228" s="2"/>
+      <c r="G228" s="2" t="s">
+        <v>484</v>
+      </c>
       <c r="H228" s="2" t="s">
         <v>38</v>
       </c>
@@ -9434,13 +9451,13 @@
         <v>209</v>
       </c>
       <c r="J228" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="229" s="1" customFormat="1" spans="1:10">
       <c r="A229" s="2"/>
       <c r="B229" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C229" s="5">
         <v>209</v>
@@ -9454,7 +9471,9 @@
       <c r="F229" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="G229" s="2"/>
+      <c r="G229" s="2" t="s">
+        <v>484</v>
+      </c>
       <c r="H229" s="2" t="s">
         <v>41</v>
       </c>
@@ -9462,13 +9481,13 @@
         <v>209</v>
       </c>
       <c r="J229" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="230" s="1" customFormat="1" spans="1:10">
       <c r="A230" s="2"/>
       <c r="B230" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C230" s="5">
         <v>209</v>
@@ -9482,7 +9501,9 @@
       <c r="F230" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="G230" s="2"/>
+      <c r="G230" s="2" t="s">
+        <v>484</v>
+      </c>
       <c r="H230" s="2" t="s">
         <v>44</v>
       </c>
@@ -9490,13 +9511,13 @@
         <v>209</v>
       </c>
       <c r="J230" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" s="1" customFormat="1" spans="1:10">
       <c r="A231" s="2"/>
       <c r="B231" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C231" s="5">
         <v>209</v>
@@ -9510,7 +9531,9 @@
       <c r="F231" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="G231" s="2"/>
+      <c r="G231" s="2" t="s">
+        <v>484</v>
+      </c>
       <c r="H231" s="2" t="s">
         <v>47</v>
       </c>
@@ -9518,13 +9541,13 @@
         <v>209</v>
       </c>
       <c r="J231" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" s="1" customFormat="1" spans="1:10">
       <c r="A232" s="2"/>
       <c r="B232" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C232" s="5">
         <v>209</v>
@@ -9538,7 +9561,9 @@
       <c r="F232" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="G232" s="2"/>
+      <c r="G232" s="2" t="s">
+        <v>484</v>
+      </c>
       <c r="H232" s="2" t="s">
         <v>50</v>
       </c>
@@ -9546,13 +9571,13 @@
         <v>209</v>
       </c>
       <c r="J232" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="233" s="1" customFormat="1" spans="1:10">
       <c r="A233" s="2"/>
       <c r="B233" s="2" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C233" s="5">
         <v>209</v>
@@ -9566,7 +9591,9 @@
       <c r="F233" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="G233" s="2"/>
+      <c r="G233" s="2" t="s">
+        <v>484</v>
+      </c>
       <c r="H233" s="2" t="s">
         <v>53</v>
       </c>
@@ -9574,13 +9601,13 @@
         <v>209</v>
       </c>
       <c r="J233" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="234" s="1" customFormat="1" spans="1:10">
       <c r="A234" s="2"/>
       <c r="B234" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C234" s="5">
         <v>209</v>
@@ -9594,7 +9621,9 @@
       <c r="F234" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="G234" s="2"/>
+      <c r="G234" s="2" t="s">
+        <v>484</v>
+      </c>
       <c r="H234" s="2" t="s">
         <v>56</v>
       </c>
@@ -9602,7 +9631,7 @@
         <v>209</v>
       </c>
       <c r="J234" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="235" customFormat="1" spans="1:10">
@@ -9620,22 +9649,22 @@
     <row r="236" customFormat="1" spans="1:10">
       <c r="A236" s="3"/>
       <c r="B236" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C236" s="4">
         <v>301</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E236" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F236" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G236" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H236" s="3" t="s">
         <v>28</v>
@@ -9644,28 +9673,28 @@
         <v>301</v>
       </c>
       <c r="J236" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="237" customFormat="1" spans="1:10">
       <c r="A237" s="3"/>
       <c r="B237" s="3" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C237" s="4">
         <v>301</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E237" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F237" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G237" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H237" s="3" t="s">
         <v>32</v>
@@ -9674,28 +9703,28 @@
         <v>301</v>
       </c>
       <c r="J237" s="3" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="238" customFormat="1" spans="1:10">
       <c r="A238" s="3"/>
       <c r="B238" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C238" s="4">
         <v>301</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E238" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F238" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G238" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H238" s="3" t="s">
         <v>35</v>
@@ -9704,28 +9733,28 @@
         <v>301</v>
       </c>
       <c r="J238" s="3" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="239" customFormat="1" spans="1:10">
       <c r="A239" s="3"/>
       <c r="B239" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C239" s="4">
         <v>301</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E239" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F239" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G239" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H239" s="3" t="s">
         <v>38</v>
@@ -9734,28 +9763,28 @@
         <v>301</v>
       </c>
       <c r="J239" s="3" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="240" customFormat="1" spans="1:10">
       <c r="A240" s="3"/>
       <c r="B240" s="3" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C240" s="4">
         <v>301</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E240" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F240" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G240" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H240" s="3" t="s">
         <v>41</v>
@@ -9764,28 +9793,28 @@
         <v>301</v>
       </c>
       <c r="J240" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="241" customFormat="1" spans="1:10">
       <c r="A241" s="3"/>
       <c r="B241" s="3" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C241" s="4">
         <v>301</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E241" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F241" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G241" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H241" s="3" t="s">
         <v>44</v>
@@ -9794,28 +9823,28 @@
         <v>301</v>
       </c>
       <c r="J241" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="242" customFormat="1" spans="1:10">
       <c r="A242" s="3"/>
       <c r="B242" s="3" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C242" s="4">
         <v>301</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E242" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F242" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G242" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H242" s="3" t="s">
         <v>47</v>
@@ -9824,28 +9853,28 @@
         <v>301</v>
       </c>
       <c r="J242" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="243" customFormat="1" spans="1:10">
       <c r="A243" s="3"/>
       <c r="B243" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C243" s="4">
         <v>301</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E243" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F243" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G243" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H243" s="3" t="s">
         <v>50</v>
@@ -9854,28 +9883,28 @@
         <v>301</v>
       </c>
       <c r="J243" s="3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="244" customFormat="1" spans="1:10">
       <c r="A244" s="3"/>
       <c r="B244" s="3" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C244" s="4">
         <v>301</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F244" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G244" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H244" s="3" t="s">
         <v>53</v>
@@ -9884,28 +9913,28 @@
         <v>301</v>
       </c>
       <c r="J244" s="3" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="245" customFormat="1" spans="1:10">
       <c r="A245" s="3"/>
       <c r="B245" s="3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C245" s="4">
         <v>301</v>
       </c>
       <c r="D245" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E245" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F245" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G245" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H245" s="3" t="s">
         <v>56</v>
@@ -9914,28 +9943,28 @@
         <v>301</v>
       </c>
       <c r="J245" s="3" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="247" customFormat="1" spans="1:10">
       <c r="A247" s="3"/>
       <c r="B247" s="3" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C247" s="4">
         <v>302</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E247" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F247" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G247" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H247" s="3" t="s">
         <v>28</v>
@@ -9944,28 +9973,28 @@
         <v>302</v>
       </c>
       <c r="J247" s="3" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="248" customFormat="1" spans="1:10">
       <c r="A248" s="3"/>
       <c r="B248" s="3" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C248" s="4">
         <v>302</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E248" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F248" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G248" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H248" s="3" t="s">
         <v>32</v>
@@ -9974,28 +10003,28 @@
         <v>302</v>
       </c>
       <c r="J248" s="3" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="249" customFormat="1" spans="1:10">
       <c r="A249" s="3"/>
       <c r="B249" s="3" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C249" s="4">
         <v>302</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E249" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F249" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G249" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H249" s="3" t="s">
         <v>35</v>
@@ -10004,28 +10033,28 @@
         <v>302</v>
       </c>
       <c r="J249" s="3" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="250" customFormat="1" spans="1:10">
       <c r="A250" s="3"/>
       <c r="B250" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C250" s="4">
         <v>302</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E250" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F250" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G250" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H250" s="3" t="s">
         <v>38</v>
@@ -10034,28 +10063,28 @@
         <v>302</v>
       </c>
       <c r="J250" s="3" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="251" customFormat="1" spans="1:10">
       <c r="A251" s="3"/>
       <c r="B251" s="3" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C251" s="4">
         <v>302</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E251" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F251" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G251" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H251" s="3" t="s">
         <v>41</v>
@@ -10064,28 +10093,28 @@
         <v>302</v>
       </c>
       <c r="J251" s="3" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="252" customFormat="1" spans="1:10">
       <c r="A252" s="3"/>
       <c r="B252" s="3" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C252" s="4">
         <v>302</v>
       </c>
       <c r="D252" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E252" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F252" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G252" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H252" s="3" t="s">
         <v>44</v>
@@ -10094,28 +10123,28 @@
         <v>302</v>
       </c>
       <c r="J252" s="3" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="253" customFormat="1" spans="1:10">
       <c r="A253" s="3"/>
       <c r="B253" s="3" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C253" s="4">
         <v>302</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E253" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F253" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H253" s="3" t="s">
         <v>47</v>
@@ -10124,28 +10153,28 @@
         <v>302</v>
       </c>
       <c r="J253" s="3" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="254" customFormat="1" spans="1:10">
       <c r="A254" s="3"/>
       <c r="B254" s="3" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C254" s="4">
         <v>302</v>
       </c>
       <c r="D254" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E254" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F254" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G254" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H254" s="3" t="s">
         <v>50</v>
@@ -10154,28 +10183,28 @@
         <v>302</v>
       </c>
       <c r="J254" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="255" customFormat="1" spans="1:10">
       <c r="A255" s="3"/>
       <c r="B255" s="3" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C255" s="4">
         <v>302</v>
       </c>
       <c r="D255" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E255" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F255" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G255" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H255" s="3" t="s">
         <v>53</v>
@@ -10184,28 +10213,28 @@
         <v>302</v>
       </c>
       <c r="J255" s="3" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="256" customFormat="1" spans="1:10">
       <c r="A256" s="3"/>
       <c r="B256" s="3" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C256" s="4">
         <v>302</v>
       </c>
       <c r="D256" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E256" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F256" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G256" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H256" s="3" t="s">
         <v>56</v>
@@ -10214,28 +10243,28 @@
         <v>302</v>
       </c>
       <c r="J256" s="3" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="258" customFormat="1" spans="1:10">
       <c r="A258" s="3"/>
       <c r="B258" s="3" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C258" s="4">
         <v>303</v>
       </c>
       <c r="D258" s="3" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E258" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F258" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G258" s="3" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H258" s="3" t="s">
         <v>28</v>
@@ -10244,28 +10273,28 @@
         <v>303</v>
       </c>
       <c r="J258" s="3" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="259" customFormat="1" spans="1:10">
       <c r="A259" s="3"/>
       <c r="B259" s="3" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C259" s="4">
         <v>303</v>
       </c>
       <c r="D259" s="3" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E259" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F259" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G259" s="3" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H259" s="3" t="s">
         <v>32</v>
@@ -10274,28 +10303,28 @@
         <v>303</v>
       </c>
       <c r="J259" s="3" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="260" customFormat="1" spans="1:10">
       <c r="A260" s="3"/>
       <c r="B260" s="3" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C260" s="4">
         <v>303</v>
       </c>
       <c r="D260" s="3" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E260" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F260" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G260" s="3" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H260" s="3" t="s">
         <v>35</v>
@@ -10304,28 +10333,28 @@
         <v>303</v>
       </c>
       <c r="J260" s="3" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="261" customFormat="1" spans="1:10">
       <c r="A261" s="3"/>
       <c r="B261" s="3" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C261" s="4">
         <v>303</v>
       </c>
       <c r="D261" s="3" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E261" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F261" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G261" s="3" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H261" s="3" t="s">
         <v>38</v>
@@ -10334,28 +10363,28 @@
         <v>303</v>
       </c>
       <c r="J261" s="3" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="262" customFormat="1" spans="1:10">
       <c r="A262" s="3"/>
       <c r="B262" s="3" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C262" s="4">
         <v>303</v>
       </c>
       <c r="D262" s="3" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E262" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F262" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G262" s="3" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H262" s="3" t="s">
         <v>41</v>
@@ -10364,28 +10393,28 @@
         <v>303</v>
       </c>
       <c r="J262" s="3" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="263" customFormat="1" spans="1:10">
       <c r="A263" s="3"/>
       <c r="B263" s="3" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C263" s="4">
         <v>303</v>
       </c>
       <c r="D263" s="3" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E263" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F263" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G263" s="3" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H263" s="3" t="s">
         <v>44</v>
@@ -10394,28 +10423,28 @@
         <v>303</v>
       </c>
       <c r="J263" s="3" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="264" customFormat="1" spans="1:10">
       <c r="A264" s="3"/>
       <c r="B264" s="3" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C264" s="4">
         <v>303</v>
       </c>
       <c r="D264" s="3" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E264" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F264" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G264" s="3" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H264" s="3" t="s">
         <v>47</v>
@@ -10424,28 +10453,28 @@
         <v>303</v>
       </c>
       <c r="J264" s="3" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="265" customFormat="1" spans="1:10">
       <c r="A265" s="3"/>
       <c r="B265" s="3" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C265" s="4">
         <v>303</v>
       </c>
       <c r="D265" s="3" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E265" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F265" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G265" s="3" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H265" s="3" t="s">
         <v>50</v>
@@ -10454,28 +10483,28 @@
         <v>303</v>
       </c>
       <c r="J265" s="3" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="266" customFormat="1" spans="1:10">
       <c r="A266" s="3"/>
       <c r="B266" s="3" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C266" s="4">
         <v>303</v>
       </c>
       <c r="D266" s="3" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E266" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F266" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G266" s="3" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H266" s="3" t="s">
         <v>53</v>
@@ -10484,28 +10513,28 @@
         <v>303</v>
       </c>
       <c r="J266" s="3" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="267" customFormat="1" spans="1:10">
       <c r="A267" s="3"/>
       <c r="B267" s="3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C267" s="4">
         <v>303</v>
       </c>
       <c r="D267" s="3" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E267" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F267" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G267" s="3" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H267" s="3" t="s">
         <v>56</v>
@@ -10514,28 +10543,28 @@
         <v>303</v>
       </c>
       <c r="J267" s="3" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="269" customFormat="1" spans="1:10">
       <c r="A269" s="3"/>
       <c r="B269" s="3" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C269" s="4">
         <v>304</v>
       </c>
       <c r="D269" s="3" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E269" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F269" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G269" s="3" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H269" s="3" t="s">
         <v>28</v>
@@ -10544,28 +10573,28 @@
         <v>304</v>
       </c>
       <c r="J269" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="270" customFormat="1" spans="1:10">
       <c r="A270" s="3"/>
       <c r="B270" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C270" s="4">
         <v>304</v>
       </c>
       <c r="D270" s="3" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E270" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F270" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G270" s="3" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H270" s="3" t="s">
         <v>32</v>
@@ -10574,28 +10603,28 @@
         <v>304</v>
       </c>
       <c r="J270" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="271" customFormat="1" spans="1:10">
       <c r="A271" s="3"/>
       <c r="B271" s="3" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C271" s="4">
         <v>304</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E271" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F271" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G271" s="3" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H271" s="3" t="s">
         <v>35</v>
@@ -10604,28 +10633,28 @@
         <v>304</v>
       </c>
       <c r="J271" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="272" customFormat="1" spans="1:10">
       <c r="A272" s="3"/>
       <c r="B272" s="3" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C272" s="4">
         <v>304</v>
       </c>
       <c r="D272" s="3" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E272" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F272" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G272" s="3" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H272" s="3" t="s">
         <v>38</v>
@@ -10634,28 +10663,28 @@
         <v>304</v>
       </c>
       <c r="J272" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="273" customFormat="1" spans="1:10">
       <c r="A273" s="3"/>
       <c r="B273" s="3" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C273" s="4">
         <v>304</v>
       </c>
       <c r="D273" s="3" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E273" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F273" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G273" s="3" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H273" s="3" t="s">
         <v>41</v>
@@ -10664,28 +10693,28 @@
         <v>304</v>
       </c>
       <c r="J273" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="274" customFormat="1" spans="1:10">
       <c r="A274" s="3"/>
       <c r="B274" s="3" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C274" s="4">
         <v>304</v>
       </c>
       <c r="D274" s="3" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E274" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F274" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G274" s="3" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H274" s="3" t="s">
         <v>44</v>
@@ -10694,28 +10723,28 @@
         <v>304</v>
       </c>
       <c r="J274" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="275" customFormat="1" spans="1:10">
       <c r="A275" s="3"/>
       <c r="B275" s="3" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C275" s="4">
         <v>304</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E275" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F275" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G275" s="3" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H275" s="3" t="s">
         <v>47</v>
@@ -10724,28 +10753,28 @@
         <v>304</v>
       </c>
       <c r="J275" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="276" customFormat="1" spans="1:10">
       <c r="A276" s="3"/>
       <c r="B276" s="3" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C276" s="4">
         <v>304</v>
       </c>
       <c r="D276" s="3" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E276" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F276" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G276" s="3" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H276" s="3" t="s">
         <v>50</v>
@@ -10754,28 +10783,28 @@
         <v>304</v>
       </c>
       <c r="J276" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="277" customFormat="1" spans="1:10">
       <c r="A277" s="3"/>
       <c r="B277" s="3" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C277" s="4">
         <v>304</v>
       </c>
       <c r="D277" s="3" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E277" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F277" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G277" s="3" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H277" s="3" t="s">
         <v>53</v>
@@ -10784,28 +10813,28 @@
         <v>304</v>
       </c>
       <c r="J277" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="278" customFormat="1" spans="1:10">
       <c r="A278" s="3"/>
       <c r="B278" s="3" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C278" s="4">
         <v>304</v>
       </c>
       <c r="D278" s="3" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E278" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F278" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G278" s="3" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H278" s="3" t="s">
         <v>56</v>
@@ -10814,7 +10843,7 @@
         <v>304</v>
       </c>
       <c r="J278" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="279" spans="1:10">
@@ -10823,22 +10852,22 @@
     <row r="280" customFormat="1" spans="1:10">
       <c r="A280" s="3"/>
       <c r="B280" s="3" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C280" s="4">
         <v>305</v>
       </c>
       <c r="D280" s="3" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E280" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F280" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G280" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H280" s="3" t="s">
         <v>28</v>
@@ -10847,28 +10876,28 @@
         <v>305</v>
       </c>
       <c r="J280" s="3" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="281" customFormat="1" spans="1:10">
       <c r="A281" s="3"/>
       <c r="B281" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C281" s="4">
         <v>305</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E281" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F281" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G281" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H281" s="3" t="s">
         <v>32</v>
@@ -10877,28 +10906,28 @@
         <v>305</v>
       </c>
       <c r="J281" s="3" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="282" customFormat="1" spans="1:10">
       <c r="A282" s="3"/>
       <c r="B282" s="3" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C282" s="4">
         <v>305</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E282" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F282" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G282" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H282" s="3" t="s">
         <v>35</v>
@@ -10907,28 +10936,28 @@
         <v>305</v>
       </c>
       <c r="J282" s="3" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="283" customFormat="1" spans="1:10">
       <c r="A283" s="3"/>
       <c r="B283" s="3" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C283" s="4">
         <v>305</v>
       </c>
       <c r="D283" s="3" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E283" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F283" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G283" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H283" s="3" t="s">
         <v>38</v>
@@ -10937,28 +10966,28 @@
         <v>305</v>
       </c>
       <c r="J283" s="3" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="284" customFormat="1" spans="1:10">
       <c r="A284" s="3"/>
       <c r="B284" s="3" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C284" s="4">
         <v>305</v>
       </c>
       <c r="D284" s="3" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E284" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F284" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G284" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H284" s="3" t="s">
         <v>41</v>
@@ -10967,28 +10996,28 @@
         <v>305</v>
       </c>
       <c r="J284" s="3" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="285" customFormat="1" spans="1:10">
       <c r="A285" s="3"/>
       <c r="B285" s="3" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C285" s="4">
         <v>305</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E285" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F285" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G285" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H285" s="3" t="s">
         <v>44</v>
@@ -10997,28 +11026,28 @@
         <v>305</v>
       </c>
       <c r="J285" s="3" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="286" customFormat="1" spans="1:10">
       <c r="A286" s="3"/>
       <c r="B286" s="3" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C286" s="4">
         <v>305</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E286" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F286" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G286" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H286" s="3" t="s">
         <v>47</v>
@@ -11027,28 +11056,28 @@
         <v>305</v>
       </c>
       <c r="J286" s="3" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="287" customFormat="1" spans="1:10">
       <c r="A287" s="3"/>
       <c r="B287" s="3" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C287" s="4">
         <v>305</v>
       </c>
       <c r="D287" s="3" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E287" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F287" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G287" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H287" s="3" t="s">
         <v>50</v>
@@ -11057,28 +11086,28 @@
         <v>305</v>
       </c>
       <c r="J287" s="3" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="288" customFormat="1" spans="1:10">
       <c r="A288" s="3"/>
       <c r="B288" s="3" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C288" s="4">
         <v>305</v>
       </c>
       <c r="D288" s="3" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E288" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F288" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G288" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H288" s="3" t="s">
         <v>53</v>
@@ -11087,28 +11116,28 @@
         <v>305</v>
       </c>
       <c r="J288" s="3" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="289" customFormat="1" spans="1:10">
       <c r="A289" s="3"/>
       <c r="B289" s="3" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C289" s="4">
         <v>305</v>
       </c>
       <c r="D289" s="3" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E289" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F289" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G289" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H289" s="3" t="s">
         <v>56</v>
@@ -11117,28 +11146,28 @@
         <v>305</v>
       </c>
       <c r="J289" s="3" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="291" customFormat="1" spans="1:10">
       <c r="A291" s="3"/>
       <c r="B291" s="3" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C291" s="4">
         <v>306</v>
       </c>
       <c r="D291" s="3" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E291" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F291" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G291" s="3" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H291" s="3" t="s">
         <v>28</v>
@@ -11147,28 +11176,28 @@
         <v>306</v>
       </c>
       <c r="J291" s="3" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="292" customFormat="1" spans="1:10">
       <c r="A292" s="3"/>
       <c r="B292" s="3" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C292" s="4">
         <v>306</v>
       </c>
       <c r="D292" s="3" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E292" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F292" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G292" s="3" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H292" s="3" t="s">
         <v>32</v>
@@ -11177,28 +11206,28 @@
         <v>306</v>
       </c>
       <c r="J292" s="3" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="293" customFormat="1" spans="1:10">
       <c r="A293" s="3"/>
       <c r="B293" s="3" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C293" s="4">
         <v>306</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E293" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F293" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G293" s="3" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H293" s="3" t="s">
         <v>35</v>
@@ -11207,28 +11236,28 @@
         <v>306</v>
       </c>
       <c r="J293" s="3" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="294" customFormat="1" spans="1:10">
       <c r="A294" s="3"/>
       <c r="B294" s="3" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C294" s="4">
         <v>306</v>
       </c>
       <c r="D294" s="3" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E294" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F294" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G294" s="3" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H294" s="3" t="s">
         <v>38</v>
@@ -11237,28 +11266,28 @@
         <v>306</v>
       </c>
       <c r="J294" s="3" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="295" customFormat="1" spans="1:10">
       <c r="A295" s="3"/>
       <c r="B295" s="3" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C295" s="4">
         <v>306</v>
       </c>
       <c r="D295" s="3" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E295" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F295" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G295" s="3" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H295" s="3" t="s">
         <v>41</v>
@@ -11267,28 +11296,28 @@
         <v>306</v>
       </c>
       <c r="J295" s="3" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="296" customFormat="1" spans="1:10">
       <c r="A296" s="3"/>
       <c r="B296" s="3" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C296" s="4">
         <v>306</v>
       </c>
       <c r="D296" s="3" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E296" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F296" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G296" s="3" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H296" s="3" t="s">
         <v>44</v>
@@ -11297,28 +11326,28 @@
         <v>306</v>
       </c>
       <c r="J296" s="3" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="297" customFormat="1" spans="1:10">
       <c r="A297" s="3"/>
       <c r="B297" s="3" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C297" s="4">
         <v>306</v>
       </c>
       <c r="D297" s="3" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E297" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F297" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G297" s="3" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H297" s="3" t="s">
         <v>47</v>
@@ -11327,28 +11356,28 @@
         <v>306</v>
       </c>
       <c r="J297" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="298" customFormat="1" spans="1:10">
       <c r="A298" s="3"/>
       <c r="B298" s="3" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C298" s="4">
         <v>306</v>
       </c>
       <c r="D298" s="3" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E298" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F298" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G298" s="3" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H298" s="3" t="s">
         <v>50</v>
@@ -11357,28 +11386,28 @@
         <v>306</v>
       </c>
       <c r="J298" s="3" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="299" customFormat="1" spans="1:10">
       <c r="A299" s="3"/>
       <c r="B299" s="3" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C299" s="4">
         <v>306</v>
       </c>
       <c r="D299" s="3" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E299" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F299" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G299" s="3" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H299" s="3" t="s">
         <v>53</v>
@@ -11387,28 +11416,28 @@
         <v>306</v>
       </c>
       <c r="J299" s="3" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="300" customFormat="1" spans="1:10">
       <c r="A300" s="3"/>
       <c r="B300" s="3" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C300" s="4">
         <v>306</v>
       </c>
       <c r="D300" s="3" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E300" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F300" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G300" s="3" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H300" s="3" t="s">
         <v>56</v>
@@ -11417,28 +11446,28 @@
         <v>306</v>
       </c>
       <c r="J300" s="3" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="302" customFormat="1" spans="1:10">
       <c r="A302" s="3"/>
       <c r="B302" s="3" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C302" s="4">
         <v>307</v>
       </c>
       <c r="D302" s="3" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="E302" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F302" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G302" s="3" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H302" s="3" t="s">
         <v>28</v>
@@ -11447,28 +11476,28 @@
         <v>307</v>
       </c>
       <c r="J302" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="303" customFormat="1" spans="1:10">
       <c r="A303" s="3"/>
       <c r="B303" s="3" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C303" s="4">
         <v>307</v>
       </c>
       <c r="D303" s="3" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="E303" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F303" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G303" s="3" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H303" s="3" t="s">
         <v>32</v>
@@ -11477,28 +11506,28 @@
         <v>307</v>
       </c>
       <c r="J303" s="3" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="304" customFormat="1" spans="1:10">
       <c r="A304" s="3"/>
       <c r="B304" s="3" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C304" s="4">
         <v>307</v>
       </c>
       <c r="D304" s="3" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="E304" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F304" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G304" s="3" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H304" s="3" t="s">
         <v>35</v>
@@ -11507,28 +11536,28 @@
         <v>307</v>
       </c>
       <c r="J304" s="3" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="305" customFormat="1" spans="1:10">
       <c r="A305" s="3"/>
       <c r="B305" s="3" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C305" s="4">
         <v>307</v>
       </c>
       <c r="D305" s="3" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="E305" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F305" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G305" s="3" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H305" s="3" t="s">
         <v>38</v>
@@ -11537,28 +11566,28 @@
         <v>307</v>
       </c>
       <c r="J305" s="3" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="306" customFormat="1" spans="1:10">
       <c r="A306" s="3"/>
       <c r="B306" s="3" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C306" s="4">
         <v>307</v>
       </c>
       <c r="D306" s="3" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="E306" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F306" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G306" s="3" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H306" s="3" t="s">
         <v>41</v>
@@ -11567,28 +11596,28 @@
         <v>307</v>
       </c>
       <c r="J306" s="3" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="307" customFormat="1" spans="1:10">
       <c r="A307" s="3"/>
       <c r="B307" s="3" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C307" s="4">
         <v>307</v>
       </c>
       <c r="D307" s="3" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="E307" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F307" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G307" s="3" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H307" s="3" t="s">
         <v>44</v>
@@ -11597,28 +11626,28 @@
         <v>307</v>
       </c>
       <c r="J307" s="3" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="308" customFormat="1" spans="1:10">
       <c r="A308" s="3"/>
       <c r="B308" s="3" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C308" s="4">
         <v>307</v>
       </c>
       <c r="D308" s="3" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="E308" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F308" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G308" s="3" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H308" s="3" t="s">
         <v>47</v>
@@ -11627,28 +11656,28 @@
         <v>307</v>
       </c>
       <c r="J308" s="3" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="309" customFormat="1" spans="1:10">
       <c r="A309" s="3"/>
       <c r="B309" s="3" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C309" s="4">
         <v>307</v>
       </c>
       <c r="D309" s="3" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="E309" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F309" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G309" s="3" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H309" s="3" t="s">
         <v>50</v>
@@ -11657,28 +11686,28 @@
         <v>307</v>
       </c>
       <c r="J309" s="3" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="310" customFormat="1" spans="1:10">
       <c r="A310" s="3"/>
       <c r="B310" s="3" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C310" s="4">
         <v>307</v>
       </c>
       <c r="D310" s="3" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="E310" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F310" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G310" s="3" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H310" s="3" t="s">
         <v>53</v>
@@ -11687,28 +11716,28 @@
         <v>307</v>
       </c>
       <c r="J310" s="3" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="311" customFormat="1" spans="1:10">
       <c r="A311" s="3"/>
       <c r="B311" s="3" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C311" s="4">
         <v>307</v>
       </c>
       <c r="D311" s="3" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="E311" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F311" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G311" s="3" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H311" s="3" t="s">
         <v>56</v>
@@ -11717,28 +11746,28 @@
         <v>307</v>
       </c>
       <c r="J311" s="3" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="313" customFormat="1" spans="1:10">
       <c r="A313" s="3"/>
       <c r="B313" s="3" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C313" s="4">
         <v>308</v>
       </c>
       <c r="D313" s="3" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E313" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F313" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G313" s="3" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H313" s="3" t="s">
         <v>28</v>
@@ -11747,28 +11776,28 @@
         <v>308</v>
       </c>
       <c r="J313" s="3" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="314" customFormat="1" spans="1:10">
       <c r="A314" s="3"/>
       <c r="B314" s="3" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C314" s="4">
         <v>308</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E314" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F314" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G314" s="3" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H314" s="3" t="s">
         <v>32</v>
@@ -11777,28 +11806,28 @@
         <v>308</v>
       </c>
       <c r="J314" s="3" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="315" customFormat="1" spans="1:10">
       <c r="A315" s="3"/>
       <c r="B315" s="3" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C315" s="4">
         <v>308</v>
       </c>
       <c r="D315" s="3" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E315" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F315" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G315" s="3" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H315" s="3" t="s">
         <v>35</v>
@@ -11807,28 +11836,28 @@
         <v>308</v>
       </c>
       <c r="J315" s="3" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="316" customFormat="1" spans="1:10">
       <c r="A316" s="3"/>
       <c r="B316" s="3" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C316" s="4">
         <v>308</v>
       </c>
       <c r="D316" s="3" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E316" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F316" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G316" s="3" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H316" s="3" t="s">
         <v>38</v>
@@ -11837,28 +11866,28 @@
         <v>308</v>
       </c>
       <c r="J316" s="3" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="317" customFormat="1" spans="1:10">
       <c r="A317" s="3"/>
       <c r="B317" s="3" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C317" s="4">
         <v>308</v>
       </c>
       <c r="D317" s="3" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E317" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F317" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G317" s="3" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H317" s="3" t="s">
         <v>41</v>
@@ -11867,28 +11896,28 @@
         <v>308</v>
       </c>
       <c r="J317" s="3" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="318" customFormat="1" spans="1:10">
       <c r="A318" s="3"/>
       <c r="B318" s="3" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C318" s="4">
         <v>308</v>
       </c>
       <c r="D318" s="3" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E318" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F318" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G318" s="3" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H318" s="3" t="s">
         <v>44</v>
@@ -11897,28 +11926,28 @@
         <v>308</v>
       </c>
       <c r="J318" s="3" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="319" customFormat="1" spans="1:10">
       <c r="A319" s="3"/>
       <c r="B319" s="3" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C319" s="4">
         <v>308</v>
       </c>
       <c r="D319" s="3" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E319" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F319" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G319" s="3" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H319" s="3" t="s">
         <v>47</v>
@@ -11927,28 +11956,28 @@
         <v>308</v>
       </c>
       <c r="J319" s="3" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="320" customFormat="1" spans="1:10">
       <c r="A320" s="3"/>
       <c r="B320" s="3" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C320" s="4">
         <v>308</v>
       </c>
       <c r="D320" s="3" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E320" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F320" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G320" s="3" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H320" s="3" t="s">
         <v>50</v>
@@ -11957,28 +11986,28 @@
         <v>308</v>
       </c>
       <c r="J320" s="3" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="321" customFormat="1" spans="1:11">
       <c r="A321" s="3"/>
       <c r="B321" s="3" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C321" s="4">
         <v>308</v>
       </c>
       <c r="D321" s="3" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E321" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F321" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G321" s="3" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H321" s="3" t="s">
         <v>53</v>
@@ -11987,28 +12016,28 @@
         <v>308</v>
       </c>
       <c r="J321" s="3" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="322" customFormat="1" spans="1:11">
       <c r="A322" s="3"/>
       <c r="B322" s="3" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C322" s="4">
         <v>308</v>
       </c>
       <c r="D322" s="3" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E322" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F322" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G322" s="3" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H322" s="3" t="s">
         <v>56</v>
@@ -12017,27 +12046,29 @@
         <v>308</v>
       </c>
       <c r="J322" s="3" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="324" s="1" customFormat="1" spans="1:11">
       <c r="A324" s="2"/>
       <c r="B324" s="2" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C324" s="5">
         <v>309</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E324" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F324" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="G324" s="2"/>
+        <v>507</v>
+      </c>
+      <c r="G324" s="2" t="s">
+        <v>684</v>
+      </c>
       <c r="H324" s="2" t="s">
         <v>28</v>
       </c>
@@ -12045,27 +12076,29 @@
         <v>309</v>
       </c>
       <c r="J324" s="1" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="325" s="1" customFormat="1" spans="1:11">
       <c r="A325" s="2"/>
       <c r="B325" s="2" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="C325" s="5">
         <v>309</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E325" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F325" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="G325" s="2"/>
+        <v>507</v>
+      </c>
+      <c r="G325" s="2" t="s">
+        <v>684</v>
+      </c>
       <c r="H325" s="2" t="s">
         <v>32</v>
       </c>
@@ -12073,27 +12106,29 @@
         <v>309</v>
       </c>
       <c r="J325" s="1" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="326" s="1" customFormat="1" spans="1:11">
       <c r="A326" s="2"/>
       <c r="B326" s="2" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="C326" s="5">
         <v>309</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E326" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F326" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="G326" s="2"/>
+        <v>507</v>
+      </c>
+      <c r="G326" s="2" t="s">
+        <v>684</v>
+      </c>
       <c r="H326" s="2" t="s">
         <v>35</v>
       </c>
@@ -12101,27 +12136,29 @@
         <v>309</v>
       </c>
       <c r="J326" s="1" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="327" s="1" customFormat="1" spans="1:11">
       <c r="A327" s="2"/>
       <c r="B327" s="2" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="C327" s="5">
         <v>309</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E327" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F327" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="G327" s="2"/>
+        <v>507</v>
+      </c>
+      <c r="G327" s="2" t="s">
+        <v>684</v>
+      </c>
       <c r="H327" s="2" t="s">
         <v>38</v>
       </c>
@@ -12129,27 +12166,29 @@
         <v>309</v>
       </c>
       <c r="J327" s="1" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="328" s="1" customFormat="1" spans="1:11">
       <c r="A328" s="2"/>
       <c r="B328" s="2" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="C328" s="5">
         <v>309</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F328" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="G328" s="2"/>
+        <v>507</v>
+      </c>
+      <c r="G328" s="2" t="s">
+        <v>684</v>
+      </c>
       <c r="H328" s="2" t="s">
         <v>41</v>
       </c>
@@ -12157,27 +12196,29 @@
         <v>309</v>
       </c>
       <c r="J328" s="1" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="329" s="1" customFormat="1" spans="1:11">
       <c r="A329" s="2"/>
       <c r="B329" s="2" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="C329" s="5">
         <v>309</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E329" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F329" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="G329" s="2"/>
+        <v>507</v>
+      </c>
+      <c r="G329" s="2" t="s">
+        <v>684</v>
+      </c>
       <c r="H329" s="2" t="s">
         <v>44</v>
       </c>
@@ -12185,27 +12226,29 @@
         <v>309</v>
       </c>
       <c r="J329" s="1" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="330" s="1" customFormat="1" spans="1:11">
       <c r="A330" s="2"/>
       <c r="B330" s="2" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="C330" s="5">
         <v>309</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E330" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F330" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="G330" s="2"/>
+        <v>507</v>
+      </c>
+      <c r="G330" s="2" t="s">
+        <v>684</v>
+      </c>
       <c r="H330" s="2" t="s">
         <v>47</v>
       </c>
@@ -12213,27 +12256,29 @@
         <v>309</v>
       </c>
       <c r="J330" s="1" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="331" s="1" customFormat="1" spans="1:11">
       <c r="A331" s="2"/>
       <c r="B331" s="2" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="C331" s="5">
         <v>309</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E331" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F331" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="G331" s="2"/>
+        <v>507</v>
+      </c>
+      <c r="G331" s="2" t="s">
+        <v>684</v>
+      </c>
       <c r="H331" s="2" t="s">
         <v>50</v>
       </c>
@@ -12241,27 +12286,29 @@
         <v>309</v>
       </c>
       <c r="J331" s="1" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="332" s="1" customFormat="1" spans="1:11">
       <c r="A332" s="2"/>
       <c r="B332" s="2" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C332" s="5">
         <v>309</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E332" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F332" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="G332" s="2"/>
+        <v>507</v>
+      </c>
+      <c r="G332" s="2" t="s">
+        <v>684</v>
+      </c>
       <c r="H332" s="2" t="s">
         <v>53</v>
       </c>
@@ -12269,27 +12316,29 @@
         <v>309</v>
       </c>
       <c r="J332" s="1" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="333" s="1" customFormat="1" spans="1:11">
       <c r="A333" s="2"/>
       <c r="B333" s="2" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C333" s="5">
         <v>309</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E333" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F333" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="G333" s="2"/>
+        <v>507</v>
+      </c>
+      <c r="G333" s="2" t="s">
+        <v>684</v>
+      </c>
       <c r="H333" s="2" t="s">
         <v>56</v>
       </c>
@@ -12297,7 +12346,7 @@
         <v>309</v>
       </c>
       <c r="J333" s="1" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="334" s="2" customFormat="1" spans="1:11">
@@ -12314,21 +12363,23 @@
     <row r="335" s="1" customFormat="1" spans="1:11">
       <c r="A335" s="2"/>
       <c r="B335" s="2" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="C335" s="5">
         <v>310</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="E335" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F335" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="G335" s="2"/>
+        <v>507</v>
+      </c>
+      <c r="G335" s="2" t="s">
+        <v>706</v>
+      </c>
       <c r="H335" s="2" t="s">
         <v>28</v>
       </c>
@@ -12336,27 +12387,29 @@
         <v>310</v>
       </c>
       <c r="J335" s="1" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
     </row>
     <row r="336" s="1" customFormat="1" spans="1:11">
       <c r="A336" s="2"/>
       <c r="B336" s="2" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="C336" s="5">
         <v>310</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="E336" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F336" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="G336" s="2"/>
+        <v>507</v>
+      </c>
+      <c r="G336" s="2" t="s">
+        <v>706</v>
+      </c>
       <c r="H336" s="2" t="s">
         <v>32</v>
       </c>
@@ -12364,27 +12417,29 @@
         <v>310</v>
       </c>
       <c r="J336" s="1" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
     </row>
     <row r="337" s="1" customFormat="1" spans="1:10">
       <c r="A337" s="2"/>
       <c r="B337" s="2" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="C337" s="5">
         <v>310</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="E337" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F337" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="G337" s="2"/>
+        <v>507</v>
+      </c>
+      <c r="G337" s="2" t="s">
+        <v>706</v>
+      </c>
       <c r="H337" s="2" t="s">
         <v>35</v>
       </c>
@@ -12392,27 +12447,29 @@
         <v>310</v>
       </c>
       <c r="J337" s="1" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
     </row>
     <row r="338" s="1" customFormat="1" spans="1:10">
       <c r="A338" s="2"/>
       <c r="B338" s="2" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="C338" s="5">
         <v>310</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="E338" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F338" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="G338" s="2"/>
+        <v>507</v>
+      </c>
+      <c r="G338" s="2" t="s">
+        <v>706</v>
+      </c>
       <c r="H338" s="2" t="s">
         <v>38</v>
       </c>
@@ -12420,27 +12477,29 @@
         <v>310</v>
       </c>
       <c r="J338" s="1" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
     </row>
     <row r="339" s="1" customFormat="1" spans="1:10">
       <c r="A339" s="2"/>
       <c r="B339" s="2" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="C339" s="5">
         <v>310</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="E339" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F339" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="G339" s="2"/>
+        <v>507</v>
+      </c>
+      <c r="G339" s="2" t="s">
+        <v>706</v>
+      </c>
       <c r="H339" s="2" t="s">
         <v>41</v>
       </c>
@@ -12448,27 +12507,29 @@
         <v>310</v>
       </c>
       <c r="J339" s="1" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
     </row>
     <row r="340" s="1" customFormat="1" spans="1:10">
       <c r="A340" s="2"/>
       <c r="B340" s="2" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="C340" s="5">
         <v>310</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="E340" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F340" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="G340" s="2"/>
+        <v>507</v>
+      </c>
+      <c r="G340" s="2" t="s">
+        <v>706</v>
+      </c>
       <c r="H340" s="2" t="s">
         <v>44</v>
       </c>
@@ -12476,27 +12537,29 @@
         <v>310</v>
       </c>
       <c r="J340" s="1" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
     </row>
     <row r="341" s="1" customFormat="1" spans="1:10">
       <c r="A341" s="2"/>
       <c r="B341" s="2" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="C341" s="5">
         <v>310</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="E341" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F341" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="G341" s="2"/>
+        <v>507</v>
+      </c>
+      <c r="G341" s="2" t="s">
+        <v>706</v>
+      </c>
       <c r="H341" s="2" t="s">
         <v>47</v>
       </c>
@@ -12504,27 +12567,29 @@
         <v>310</v>
       </c>
       <c r="J341" s="1" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
     </row>
     <row r="342" s="1" customFormat="1" spans="1:10">
       <c r="A342" s="2"/>
       <c r="B342" s="2" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="C342" s="5">
         <v>310</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="E342" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F342" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="G342" s="2"/>
+        <v>507</v>
+      </c>
+      <c r="G342" s="2" t="s">
+        <v>706</v>
+      </c>
       <c r="H342" s="2" t="s">
         <v>50</v>
       </c>
@@ -12532,27 +12597,29 @@
         <v>310</v>
       </c>
       <c r="J342" s="1" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
     </row>
     <row r="343" s="1" customFormat="1" spans="1:10">
       <c r="A343" s="2"/>
       <c r="B343" s="2" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="C343" s="5">
         <v>310</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="E343" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F343" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="G343" s="2"/>
+        <v>507</v>
+      </c>
+      <c r="G343" s="2" t="s">
+        <v>706</v>
+      </c>
       <c r="H343" s="2" t="s">
         <v>53</v>
       </c>
@@ -12560,27 +12627,29 @@
         <v>310</v>
       </c>
       <c r="J343" s="1" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
     </row>
     <row r="344" s="1" customFormat="1" spans="1:10">
       <c r="A344" s="2"/>
       <c r="B344" s="2" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="C344" s="5">
         <v>310</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="E344" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F344" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="G344" s="2"/>
+        <v>507</v>
+      </c>
+      <c r="G344" s="2" t="s">
+        <v>706</v>
+      </c>
       <c r="H344" s="2" t="s">
         <v>56</v>
       </c>
@@ -12588,7 +12657,7 @@
         <v>310</v>
       </c>
       <c r="J344" s="1" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
     </row>
   </sheetData>
